--- a/activity/M03A05/M03A05_AnalisisResultado.xlsx
+++ b/activity/M03A05/M03A05_AnalisisResultado.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M03A05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DC06489-1111-426B-8471-3A9F00ECABFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84656724-F635-4E24-93D9-7E9FD946A89E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Calificacion" sheetId="12" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="CumpleTolerancia" sheetId="13" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Detalle!$B$1:$H$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Detalle!$B$1:$H$21</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">Detalle!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="47">
   <si>
     <t>Observaciones</t>
   </si>
@@ -72,9 +72,6 @@
     <t>Energía máxima: para cada periodo de retorno evaluado, presentar el perfil de cada río con la línea de energía obtenida y presentar un análisis descriptivo.</t>
   </si>
   <si>
-    <t>Crear un único reporte en Adobe Acrobat que muestre capturas de pantalla detalladas para todos los parámetros indicados, tablas detalladas de resultados obtenidos en cada sección transversal, incluir análisis y si se cumplió o no con las condiciones de diseño y los valores admisibles definidos para el proyecto. Incluir portada, tabla de contenido, numeración de páginas, separadores de página para cada grupo de análisis y observaciones detalladas; nombrar como HCMC0025_HECRAS.pdf. En análisis de flujo permanente y no permanente deberá ser presentado en dos capítulos independientes.</t>
-  </si>
-  <si>
     <t>Valor límite</t>
   </si>
   <si>
@@ -85,9 +82,6 @@
   </si>
   <si>
     <t>Tipo</t>
-  </si>
-  <si>
-    <t>Reporte</t>
   </si>
   <si>
     <t>Profundidad crítica (opcional): evaluar la profundidad crítica e indicar el tipo de perfil hidráulico obtenido, indicar posiciones de Yc que se crucen con la profundidad de lámina o que esté por encima. Plantear soluciones para obtener profundidades críticas siempre por debajo de la profundidad normal y/o de lámina de agua en la zona prismática diseñada y modelada. Realizar el análisis en condiciones de flujo subcrítico y mixto.</t>
@@ -181,6 +175,15 @@
     <t>## N/m²
 ## N/m²</t>
   </si>
+  <si>
+    <t>Informe técnico mostrando las actividades desarrolladas en el orden presentado en esta actividad, junto con los análisis y recomendaciones realizadas, convierta a Adobe Acrobat (.pdf) y guarde en la carpeta /report del repositorio de datos del proyecto.</t>
+  </si>
+  <si>
+    <t>En caso de haber realizado ajustes en las condiciones de frontera para flujo permanente y no permanente, comprimir como HECRAS_v1_aaaammdd.zip.</t>
+  </si>
+  <si>
+    <t>Reporte &amp; .zip</t>
+  </si>
 </sst>
 </file>
 
@@ -191,7 +194,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -251,21 +254,8 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FFC00000"/>
-      <name val="Segoe UI Light"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF0070C0"/>
-      <name val="Segoe UI Light"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color rgb="FFC00000"/>
       <name val="Segoe UI Light"/>
       <family val="2"/>
     </font>
@@ -315,7 +305,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -684,15 +674,55 @@
     </border>
     <border>
       <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
       <top style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
+        <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -705,7 +735,7 @@
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
@@ -745,9 +775,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -767,14 +794,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
@@ -783,16 +802,10 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" textRotation="90"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -825,211 +838,211 @@
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="6" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="5" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="15" fillId="0" borderId="5" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="7" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="15" fillId="0" borderId="7" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" textRotation="90"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" textRotation="90"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -1241,19 +1254,19 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>2.5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2.5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2450,297 +2463,297 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="F1" s="61" t="s">
-        <v>33</v>
+      <c r="F1" s="53" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
+      <c r="B2" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
     </row>
     <row r="3" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
     </row>
     <row r="4" spans="2:6" ht="33" x14ac:dyDescent="0.45">
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="42" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="35" t="s">
+      <c r="C4" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="36" t="s">
         <v>22</v>
+      </c>
+      <c r="E4" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="65">
+        <v>25</v>
+      </c>
+      <c r="C5" s="57">
         <v>5</v>
       </c>
-      <c r="D5" s="36">
-        <f>Detalle!D20*C5/5</f>
-        <v>2.5</v>
-      </c>
-      <c r="E5" s="67"/>
-      <c r="F5" s="37">
+      <c r="D5" s="31">
+        <f>Detalle!D21*C5/5</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="59"/>
+      <c r="F5" s="32">
         <f>AVERAGE(D5:E5)</f>
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="65">
+        <v>26</v>
+      </c>
+      <c r="C6" s="57">
         <v>5</v>
       </c>
-      <c r="D6" s="36">
-        <f>Detalle!I20*C6/5</f>
-        <v>2.5</v>
-      </c>
-      <c r="E6" s="67"/>
-      <c r="F6" s="37">
+      <c r="D6" s="31">
+        <f>Detalle!I21*C6/5</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="59"/>
+      <c r="F6" s="32">
         <f t="shared" ref="F6:F18" si="0">AVERAGE(D6:E6)</f>
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B7" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="65">
+        <v>27</v>
+      </c>
+      <c r="C7" s="57">
         <v>5</v>
       </c>
-      <c r="D7" s="36">
-        <f>Detalle!N20*C7/5</f>
-        <v>2.5</v>
-      </c>
-      <c r="E7" s="67"/>
-      <c r="F7" s="37">
+      <c r="D7" s="31">
+        <f>Detalle!N21*C7/5</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="59"/>
+      <c r="F7" s="32">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B8" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="65">
+        <v>28</v>
+      </c>
+      <c r="C8" s="57">
         <v>5</v>
       </c>
-      <c r="D8" s="36">
-        <f>Detalle!S20*C8/5</f>
+      <c r="D8" s="31">
+        <f>Detalle!S21*C8/5</f>
         <v>0</v>
       </c>
-      <c r="E8" s="67"/>
-      <c r="F8" s="37">
+      <c r="E8" s="59"/>
+      <c r="F8" s="32">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="65">
+        <v>29</v>
+      </c>
+      <c r="C9" s="57">
         <v>5</v>
       </c>
-      <c r="D9" s="36">
-        <f>Detalle!X20*C9/5</f>
-        <v>2.5</v>
-      </c>
-      <c r="E9" s="67"/>
-      <c r="F9" s="37">
+      <c r="D9" s="31">
+        <f>Detalle!X21*C9/5</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="59"/>
+      <c r="F9" s="32">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B10" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="65">
+        <v>32</v>
+      </c>
+      <c r="C10" s="57">
         <v>5</v>
       </c>
-      <c r="D10" s="36">
-        <f>Detalle!AC20*C10/5</f>
+      <c r="D10" s="31">
+        <f>Detalle!AC21*C10/5</f>
         <v>0</v>
       </c>
-      <c r="E10" s="67"/>
-      <c r="F10" s="37">
+      <c r="E10" s="59"/>
+      <c r="F10" s="32">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B11" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" s="65">
+        <v>33</v>
+      </c>
+      <c r="C11" s="57">
         <v>5</v>
       </c>
-      <c r="D11" s="36">
-        <f>Detalle!AH20*C11/5</f>
+      <c r="D11" s="31">
+        <f>Detalle!AH21*C11/5</f>
         <v>0</v>
       </c>
-      <c r="E11" s="67"/>
-      <c r="F11" s="37">
+      <c r="E11" s="59"/>
+      <c r="F11" s="32">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B12" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="65">
+        <v>34</v>
+      </c>
+      <c r="C12" s="57">
         <v>5</v>
       </c>
-      <c r="D12" s="36">
-        <f>Detalle!AM20*C12/5</f>
+      <c r="D12" s="31">
+        <f>Detalle!AM21*C12/5</f>
         <v>0</v>
       </c>
-      <c r="E12" s="67"/>
-      <c r="F12" s="37">
+      <c r="E12" s="59"/>
+      <c r="F12" s="32">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B13" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="65">
+        <v>35</v>
+      </c>
+      <c r="C13" s="57">
         <v>5</v>
       </c>
-      <c r="D13" s="36">
-        <f>Detalle!AR20*C13/5</f>
+      <c r="D13" s="31">
+        <f>Detalle!AR21*C13/5</f>
         <v>0</v>
       </c>
-      <c r="E13" s="67"/>
-      <c r="F13" s="37">
+      <c r="E13" s="59"/>
+      <c r="F13" s="32">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B14" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" s="65">
+        <v>36</v>
+      </c>
+      <c r="C14" s="57">
         <v>5</v>
       </c>
-      <c r="D14" s="36">
-        <f>Detalle!AW20*C14/5</f>
+      <c r="D14" s="31">
+        <f>Detalle!AW21*C14/5</f>
         <v>0</v>
       </c>
-      <c r="E14" s="67"/>
-      <c r="F14" s="37">
+      <c r="E14" s="59"/>
+      <c r="F14" s="32">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B15" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="65">
+        <v>37</v>
+      </c>
+      <c r="C15" s="57">
         <v>5</v>
       </c>
-      <c r="D15" s="36">
-        <f>Detalle!BB20*C15/5</f>
+      <c r="D15" s="31">
+        <f>Detalle!BB21*C15/5</f>
         <v>0</v>
       </c>
-      <c r="E15" s="67"/>
-      <c r="F15" s="37">
+      <c r="E15" s="59"/>
+      <c r="F15" s="32">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B16" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" s="65">
+        <v>38</v>
+      </c>
+      <c r="C16" s="57">
         <v>5</v>
       </c>
-      <c r="D16" s="36">
-        <f>Detalle!BG20*C16/5</f>
+      <c r="D16" s="31">
+        <f>Detalle!BG21*C16/5</f>
         <v>0</v>
       </c>
-      <c r="E16" s="67"/>
-      <c r="F16" s="37">
+      <c r="E16" s="59"/>
+      <c r="F16" s="32">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B17" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C17" s="65">
+        <v>39</v>
+      </c>
+      <c r="C17" s="57">
         <v>5</v>
       </c>
-      <c r="D17" s="36">
-        <f>Detalle!BL20*C17/5</f>
+      <c r="D17" s="31">
+        <f>Detalle!BL21*C17/5</f>
         <v>0</v>
       </c>
-      <c r="E17" s="67"/>
-      <c r="F17" s="37">
+      <c r="E17" s="59"/>
+      <c r="F17" s="32">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B18" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" s="66">
+      <c r="B18" s="54" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="58">
         <v>5</v>
       </c>
-      <c r="D18" s="63">
-        <f>Detalle!BQ20*C18/5</f>
+      <c r="D18" s="55">
+        <f>Detalle!BQ21*C18/5</f>
         <v>0</v>
       </c>
-      <c r="E18" s="68"/>
-      <c r="F18" s="64">
+      <c r="E18" s="60"/>
+      <c r="F18" s="56">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="60" t="str">
+      <c r="B19" s="52" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F1,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",F1," en GitHub."))</f>
         <v>Ir a actividad M03A05 en GitHub.</v>
       </c>
-      <c r="C19" s="60"/>
-      <c r="D19" s="60"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="60"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="52"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B20" s="60"/>
-      <c r="C20" s="60"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
+      <c r="B20" s="52"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
+      <c r="F20" s="52"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B21" s="8"/>
@@ -2755,7 +2768,7 @@
     <mergeCell ref="B19:F19"/>
     <mergeCell ref="B20:F20"/>
   </mergeCells>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -2765,7 +2778,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A17987CE-896A-4E26-83D1-1610B3259376}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:BU56"/>
+  <dimension ref="A1:BU57"/>
   <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="2.6640625" style="9" customWidth="1"/>
@@ -2818,7 +2831,7 @@
   <sheetData>
     <row r="1" spans="1:73" x14ac:dyDescent="0.45">
       <c r="A1" s="6"/>
-      <c r="B1" s="43" t="str">
+      <c r="B1" s="37" t="str">
         <f>Calificacion!B2</f>
         <v>Calificación: 3.5. Análisis de resultados (perfil de flujo, línea de energía, esfuerzo cortante, velocidad, borde libre)</v>
       </c>
@@ -2831,7 +2844,7 @@
       <c r="G1" s="11">
         <v>24</v>
       </c>
-      <c r="H1" s="40">
+      <c r="H1" s="35">
         <f>(1-(F1/G1))</f>
         <v>0.16666666666666663</v>
       </c>
@@ -2843,7 +2856,7 @@
       <c r="L1" s="11">
         <v>50</v>
       </c>
-      <c r="M1" s="38">
+      <c r="M1" s="33">
         <f>(1-(K1/L1))</f>
         <v>0.6</v>
       </c>
@@ -2855,7 +2868,7 @@
       <c r="Q1" s="11">
         <v>2.5</v>
       </c>
-      <c r="R1" s="39">
+      <c r="R1" s="34">
         <f>(1-(P1/Q1))</f>
         <v>-0.19999999999999996</v>
       </c>
@@ -2867,7 +2880,7 @@
       <c r="V1" s="11">
         <v>2.5</v>
       </c>
-      <c r="W1" s="39">
+      <c r="W1" s="34">
         <f>(1-(U1/V1))</f>
         <v>-0.19999999999999996</v>
       </c>
@@ -2926,1975 +2939,1952 @@
     </row>
     <row r="2" spans="1:73" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="9"/>
-      <c r="B2" s="55" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" s="53" t="s">
+      <c r="B2" s="47" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="48" t="str">
+      <c r="D2" s="40" t="str">
         <f>Calificacion!$B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="52" t="str">
+      <c r="E2" s="41"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="44" t="str">
         <f>Calificacion!$B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="48"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="52" t="str">
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="43"/>
+      <c r="N2" s="44" t="str">
         <f>Calificacion!$B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="O2" s="48"/>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="52" t="str">
+      <c r="O2" s="40"/>
+      <c r="P2" s="40"/>
+      <c r="Q2" s="40"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="44" t="str">
         <f>Calificacion!$B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="T2" s="48"/>
-      <c r="U2" s="48"/>
-      <c r="V2" s="48"/>
-      <c r="W2" s="51"/>
-      <c r="X2" s="52" t="str">
+      <c r="T2" s="40"/>
+      <c r="U2" s="40"/>
+      <c r="V2" s="40"/>
+      <c r="W2" s="43"/>
+      <c r="X2" s="44" t="str">
         <f>Calificacion!$B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="Y2" s="48"/>
-      <c r="Z2" s="48"/>
-      <c r="AA2" s="48"/>
-      <c r="AB2" s="51"/>
-      <c r="AC2" s="52" t="str">
+      <c r="Y2" s="40"/>
+      <c r="Z2" s="40"/>
+      <c r="AA2" s="40"/>
+      <c r="AB2" s="43"/>
+      <c r="AC2" s="44" t="str">
         <f>Calificacion!$B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="AD2" s="48"/>
-      <c r="AE2" s="48"/>
-      <c r="AF2" s="48"/>
-      <c r="AG2" s="51"/>
-      <c r="AH2" s="52" t="str">
+      <c r="AD2" s="40"/>
+      <c r="AE2" s="40"/>
+      <c r="AF2" s="40"/>
+      <c r="AG2" s="43"/>
+      <c r="AH2" s="44" t="str">
         <f>Calificacion!$B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="AI2" s="48"/>
-      <c r="AJ2" s="48"/>
-      <c r="AK2" s="48"/>
-      <c r="AL2" s="51"/>
-      <c r="AM2" s="52" t="str">
+      <c r="AI2" s="40"/>
+      <c r="AJ2" s="40"/>
+      <c r="AK2" s="40"/>
+      <c r="AL2" s="43"/>
+      <c r="AM2" s="44" t="str">
         <f>Calificacion!$B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="AN2" s="48"/>
-      <c r="AO2" s="48"/>
-      <c r="AP2" s="48"/>
-      <c r="AQ2" s="51"/>
-      <c r="AR2" s="52" t="str">
+      <c r="AN2" s="40"/>
+      <c r="AO2" s="40"/>
+      <c r="AP2" s="40"/>
+      <c r="AQ2" s="43"/>
+      <c r="AR2" s="44" t="str">
         <f>Calificacion!$B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="AS2" s="48"/>
-      <c r="AT2" s="48"/>
-      <c r="AU2" s="48"/>
-      <c r="AV2" s="51"/>
-      <c r="AW2" s="52" t="str">
+      <c r="AS2" s="40"/>
+      <c r="AT2" s="40"/>
+      <c r="AU2" s="40"/>
+      <c r="AV2" s="43"/>
+      <c r="AW2" s="44" t="str">
         <f>Calificacion!$B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="AX2" s="48"/>
-      <c r="AY2" s="48"/>
-      <c r="AZ2" s="48"/>
-      <c r="BA2" s="51"/>
-      <c r="BB2" s="52" t="str">
+      <c r="AX2" s="40"/>
+      <c r="AY2" s="40"/>
+      <c r="AZ2" s="40"/>
+      <c r="BA2" s="43"/>
+      <c r="BB2" s="44" t="str">
         <f>Calificacion!$B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="BC2" s="48"/>
-      <c r="BD2" s="48"/>
-      <c r="BE2" s="48"/>
-      <c r="BF2" s="51"/>
-      <c r="BG2" s="52" t="str">
+      <c r="BC2" s="40"/>
+      <c r="BD2" s="40"/>
+      <c r="BE2" s="40"/>
+      <c r="BF2" s="43"/>
+      <c r="BG2" s="44" t="str">
         <f>Calificacion!$B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="BH2" s="48"/>
-      <c r="BI2" s="48"/>
-      <c r="BJ2" s="48"/>
-      <c r="BK2" s="51"/>
-      <c r="BL2" s="52" t="str">
+      <c r="BH2" s="40"/>
+      <c r="BI2" s="40"/>
+      <c r="BJ2" s="40"/>
+      <c r="BK2" s="43"/>
+      <c r="BL2" s="44" t="str">
         <f>Calificacion!$B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="BM2" s="48"/>
-      <c r="BN2" s="48"/>
-      <c r="BO2" s="48"/>
-      <c r="BP2" s="51"/>
-      <c r="BQ2" s="52" t="str">
+      <c r="BM2" s="40"/>
+      <c r="BN2" s="40"/>
+      <c r="BO2" s="40"/>
+      <c r="BP2" s="43"/>
+      <c r="BQ2" s="44" t="str">
         <f>Calificacion!$B18</f>
         <v>Grupo 14</v>
       </c>
-      <c r="BR2" s="48"/>
-      <c r="BS2" s="48"/>
-      <c r="BT2" s="48"/>
-      <c r="BU2" s="51"/>
+      <c r="BR2" s="40"/>
+      <c r="BS2" s="40"/>
+      <c r="BT2" s="40"/>
+      <c r="BU2" s="43"/>
     </row>
     <row r="3" spans="1:73" ht="30.75" x14ac:dyDescent="0.45">
-      <c r="B3" s="56"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="15" t="s">
+      <c r="B3" s="48"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="G3" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="I3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="L3" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="N3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="O3" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="P3" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q3" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="R3" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="S3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="U3" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="V3" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="W3" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="X3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z3" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA3" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="AB3" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD3" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE3" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF3" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="AG3" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="AI3" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ3" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK3" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="AL3" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="AN3" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO3" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="AP3" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="AQ3" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="AR3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="AS3" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="AT3" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="AU3" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="AV3" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="AW3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="AX3" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="AY3" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="AZ3" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="BA3" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="BB3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="BC3" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="BD3" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="BE3" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="BF3" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="BG3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="BH3" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="BI3" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="BJ3" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="BK3" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="BL3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="BM3" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="BN3" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="BO3" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="BP3" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="BQ3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="BR3" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="BS3" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="BT3" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="BU3" s="17" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:73" ht="112.15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B4" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="18" t="s">
+      <c r="C4" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="61">
         <v>0</v>
       </c>
-      <c r="I3" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="K3" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="L3" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3" s="18" t="s">
+      <c r="E4" s="62"/>
+      <c r="F4" s="62"/>
+      <c r="G4" s="63"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="61">
         <v>0</v>
       </c>
-      <c r="N3" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="O3" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="P3" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q3" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="R3" s="18" t="s">
+      <c r="J4" s="62"/>
+      <c r="K4" s="62"/>
+      <c r="L4" s="63"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="61">
         <v>0</v>
       </c>
-      <c r="S3" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="T3" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="U3" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="V3" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="W3" s="18" t="s">
+      <c r="O4" s="62"/>
+      <c r="P4" s="62"/>
+      <c r="Q4" s="63"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="61">
         <v>0</v>
       </c>
-      <c r="X3" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y3" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z3" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="AA3" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="AB3" s="18" t="s">
+      <c r="T4" s="62"/>
+      <c r="U4" s="62"/>
+      <c r="V4" s="63"/>
+      <c r="W4" s="64"/>
+      <c r="X4" s="61">
         <v>0</v>
       </c>
-      <c r="AC3" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD3" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="AE3" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="AF3" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="AG3" s="18" t="s">
+      <c r="Y4" s="62"/>
+      <c r="Z4" s="62"/>
+      <c r="AA4" s="63"/>
+      <c r="AB4" s="64"/>
+      <c r="AC4" s="61">
         <v>0</v>
       </c>
-      <c r="AH3" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="AI3" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="AJ3" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="AK3" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="AL3" s="18" t="s">
+      <c r="AD4" s="62"/>
+      <c r="AE4" s="62"/>
+      <c r="AF4" s="63"/>
+      <c r="AG4" s="64"/>
+      <c r="AH4" s="61">
         <v>0</v>
       </c>
-      <c r="AM3" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="AN3" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="AO3" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="AP3" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="AQ3" s="18" t="s">
+      <c r="AI4" s="62"/>
+      <c r="AJ4" s="62"/>
+      <c r="AK4" s="63"/>
+      <c r="AL4" s="64"/>
+      <c r="AM4" s="61">
         <v>0</v>
       </c>
-      <c r="AR3" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="AS3" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="AT3" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="AU3" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="AV3" s="18" t="s">
+      <c r="AN4" s="62"/>
+      <c r="AO4" s="62"/>
+      <c r="AP4" s="63"/>
+      <c r="AQ4" s="64"/>
+      <c r="AR4" s="61">
         <v>0</v>
       </c>
-      <c r="AW3" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="AX3" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="AY3" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="AZ3" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="BA3" s="18" t="s">
+      <c r="AS4" s="62"/>
+      <c r="AT4" s="62"/>
+      <c r="AU4" s="63"/>
+      <c r="AV4" s="64"/>
+      <c r="AW4" s="61">
         <v>0</v>
       </c>
-      <c r="BB3" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="BC3" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="BD3" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="BE3" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="BF3" s="18" t="s">
+      <c r="AX4" s="62"/>
+      <c r="AY4" s="62"/>
+      <c r="AZ4" s="63"/>
+      <c r="BA4" s="64"/>
+      <c r="BB4" s="61">
         <v>0</v>
       </c>
-      <c r="BG3" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="BH3" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="BI3" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="BJ3" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="BK3" s="18" t="s">
+      <c r="BC4" s="62"/>
+      <c r="BD4" s="62"/>
+      <c r="BE4" s="63"/>
+      <c r="BF4" s="64"/>
+      <c r="BG4" s="61">
         <v>0</v>
       </c>
-      <c r="BL3" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="BM3" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="BN3" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="BO3" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="BP3" s="18" t="s">
+      <c r="BH4" s="62"/>
+      <c r="BI4" s="62"/>
+      <c r="BJ4" s="63"/>
+      <c r="BK4" s="64"/>
+      <c r="BL4" s="61">
         <v>0</v>
       </c>
-      <c r="BQ3" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="BR3" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="BS3" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="BT3" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="BU3" s="18" t="s">
+      <c r="BM4" s="62"/>
+      <c r="BN4" s="62"/>
+      <c r="BO4" s="63"/>
+      <c r="BP4" s="64"/>
+      <c r="BQ4" s="61">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:73" ht="112.15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="69">
-        <v>0</v>
-      </c>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="71"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="69">
-        <v>0</v>
-      </c>
-      <c r="J4" s="70"/>
-      <c r="K4" s="70"/>
-      <c r="L4" s="71"/>
-      <c r="M4" s="72"/>
-      <c r="N4" s="69">
-        <v>0</v>
-      </c>
-      <c r="O4" s="70"/>
-      <c r="P4" s="70"/>
-      <c r="Q4" s="71"/>
-      <c r="R4" s="72"/>
-      <c r="S4" s="69">
-        <v>0</v>
-      </c>
-      <c r="T4" s="70"/>
-      <c r="U4" s="70"/>
-      <c r="V4" s="71"/>
-      <c r="W4" s="72"/>
-      <c r="X4" s="69">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="70"/>
-      <c r="Z4" s="70"/>
-      <c r="AA4" s="71"/>
-      <c r="AB4" s="72"/>
-      <c r="AC4" s="69">
-        <v>0</v>
-      </c>
-      <c r="AD4" s="70"/>
-      <c r="AE4" s="70"/>
-      <c r="AF4" s="71"/>
-      <c r="AG4" s="72"/>
-      <c r="AH4" s="69">
-        <v>0</v>
-      </c>
-      <c r="AI4" s="70"/>
-      <c r="AJ4" s="70"/>
-      <c r="AK4" s="71"/>
-      <c r="AL4" s="72"/>
-      <c r="AM4" s="69">
-        <v>0</v>
-      </c>
-      <c r="AN4" s="70"/>
-      <c r="AO4" s="70"/>
-      <c r="AP4" s="71"/>
-      <c r="AQ4" s="72"/>
-      <c r="AR4" s="69">
-        <v>0</v>
-      </c>
-      <c r="AS4" s="70"/>
-      <c r="AT4" s="70"/>
-      <c r="AU4" s="71"/>
-      <c r="AV4" s="72"/>
-      <c r="AW4" s="69">
-        <v>0</v>
-      </c>
-      <c r="AX4" s="70"/>
-      <c r="AY4" s="70"/>
-      <c r="AZ4" s="71"/>
-      <c r="BA4" s="72"/>
-      <c r="BB4" s="69">
-        <v>0</v>
-      </c>
-      <c r="BC4" s="70"/>
-      <c r="BD4" s="70"/>
-      <c r="BE4" s="71"/>
-      <c r="BF4" s="72"/>
-      <c r="BG4" s="69">
-        <v>0</v>
-      </c>
-      <c r="BH4" s="70"/>
-      <c r="BI4" s="70"/>
-      <c r="BJ4" s="71"/>
-      <c r="BK4" s="72"/>
-      <c r="BL4" s="69">
-        <v>0</v>
-      </c>
-      <c r="BM4" s="70"/>
-      <c r="BN4" s="70"/>
-      <c r="BO4" s="71"/>
-      <c r="BP4" s="72"/>
-      <c r="BQ4" s="69">
-        <v>0</v>
-      </c>
-      <c r="BR4" s="70"/>
-      <c r="BS4" s="70"/>
-      <c r="BT4" s="71"/>
-      <c r="BU4" s="72"/>
+      <c r="BR4" s="62"/>
+      <c r="BS4" s="62"/>
+      <c r="BT4" s="63"/>
+      <c r="BU4" s="64"/>
     </row>
     <row r="5" spans="1:73" ht="93.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="57"/>
+      <c r="B5" s="49"/>
       <c r="C5" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="73"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="73"/>
-      <c r="J5" s="74"/>
-      <c r="K5" s="74"/>
-      <c r="L5" s="75"/>
-      <c r="M5" s="76"/>
-      <c r="N5" s="73"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="75"/>
-      <c r="R5" s="76"/>
-      <c r="S5" s="73"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="75"/>
-      <c r="W5" s="76"/>
-      <c r="X5" s="73"/>
-      <c r="Y5" s="74"/>
-      <c r="Z5" s="74"/>
-      <c r="AA5" s="75"/>
-      <c r="AB5" s="76"/>
-      <c r="AC5" s="73"/>
-      <c r="AD5" s="74"/>
-      <c r="AE5" s="74"/>
-      <c r="AF5" s="75"/>
-      <c r="AG5" s="76"/>
-      <c r="AH5" s="73"/>
-      <c r="AI5" s="74"/>
-      <c r="AJ5" s="74"/>
-      <c r="AK5" s="75"/>
-      <c r="AL5" s="76"/>
-      <c r="AM5" s="73"/>
-      <c r="AN5" s="74"/>
-      <c r="AO5" s="74"/>
-      <c r="AP5" s="75"/>
-      <c r="AQ5" s="76"/>
-      <c r="AR5" s="73"/>
-      <c r="AS5" s="74"/>
-      <c r="AT5" s="74"/>
-      <c r="AU5" s="75"/>
-      <c r="AV5" s="76"/>
-      <c r="AW5" s="73"/>
-      <c r="AX5" s="74"/>
-      <c r="AY5" s="74"/>
-      <c r="AZ5" s="75"/>
-      <c r="BA5" s="76"/>
-      <c r="BB5" s="73"/>
-      <c r="BC5" s="74"/>
-      <c r="BD5" s="74"/>
-      <c r="BE5" s="75"/>
-      <c r="BF5" s="76"/>
-      <c r="BG5" s="73"/>
-      <c r="BH5" s="74"/>
-      <c r="BI5" s="74"/>
-      <c r="BJ5" s="75"/>
-      <c r="BK5" s="76"/>
-      <c r="BL5" s="73"/>
-      <c r="BM5" s="74"/>
-      <c r="BN5" s="74"/>
-      <c r="BO5" s="75"/>
-      <c r="BP5" s="76"/>
-      <c r="BQ5" s="73"/>
-      <c r="BR5" s="74"/>
-      <c r="BS5" s="74"/>
-      <c r="BT5" s="75"/>
-      <c r="BU5" s="76"/>
+        <v>15</v>
+      </c>
+      <c r="D5" s="65"/>
+      <c r="E5" s="66"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="66"/>
+      <c r="K5" s="66"/>
+      <c r="L5" s="67"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="65"/>
+      <c r="O5" s="66"/>
+      <c r="P5" s="66"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="66"/>
+      <c r="U5" s="66"/>
+      <c r="V5" s="67"/>
+      <c r="W5" s="68"/>
+      <c r="X5" s="65"/>
+      <c r="Y5" s="66"/>
+      <c r="Z5" s="66"/>
+      <c r="AA5" s="67"/>
+      <c r="AB5" s="68"/>
+      <c r="AC5" s="65"/>
+      <c r="AD5" s="66"/>
+      <c r="AE5" s="66"/>
+      <c r="AF5" s="67"/>
+      <c r="AG5" s="68"/>
+      <c r="AH5" s="65"/>
+      <c r="AI5" s="66"/>
+      <c r="AJ5" s="66"/>
+      <c r="AK5" s="67"/>
+      <c r="AL5" s="68"/>
+      <c r="AM5" s="65"/>
+      <c r="AN5" s="66"/>
+      <c r="AO5" s="66"/>
+      <c r="AP5" s="67"/>
+      <c r="AQ5" s="68"/>
+      <c r="AR5" s="65"/>
+      <c r="AS5" s="66"/>
+      <c r="AT5" s="66"/>
+      <c r="AU5" s="67"/>
+      <c r="AV5" s="68"/>
+      <c r="AW5" s="65"/>
+      <c r="AX5" s="66"/>
+      <c r="AY5" s="66"/>
+      <c r="AZ5" s="67"/>
+      <c r="BA5" s="68"/>
+      <c r="BB5" s="65"/>
+      <c r="BC5" s="66"/>
+      <c r="BD5" s="66"/>
+      <c r="BE5" s="67"/>
+      <c r="BF5" s="68"/>
+      <c r="BG5" s="65"/>
+      <c r="BH5" s="66"/>
+      <c r="BI5" s="66"/>
+      <c r="BJ5" s="67"/>
+      <c r="BK5" s="68"/>
+      <c r="BL5" s="65"/>
+      <c r="BM5" s="66"/>
+      <c r="BN5" s="66"/>
+      <c r="BO5" s="67"/>
+      <c r="BP5" s="68"/>
+      <c r="BQ5" s="65"/>
+      <c r="BR5" s="66"/>
+      <c r="BS5" s="66"/>
+      <c r="BT5" s="67"/>
+      <c r="BU5" s="68"/>
     </row>
     <row r="6" spans="1:73" ht="93.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="57"/>
+      <c r="B6" s="49"/>
       <c r="C6" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="73"/>
-      <c r="E6" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="G6" s="75"/>
-      <c r="H6" s="77"/>
-      <c r="I6" s="73"/>
-      <c r="J6" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="K6" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="L6" s="75"/>
-      <c r="M6" s="77"/>
-      <c r="N6" s="73"/>
-      <c r="O6" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="P6" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="77"/>
-      <c r="S6" s="73"/>
-      <c r="T6" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="U6" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="V6" s="75"/>
-      <c r="W6" s="77"/>
-      <c r="X6" s="73"/>
-      <c r="Y6" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="Z6" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="AA6" s="75"/>
-      <c r="AB6" s="77"/>
-      <c r="AC6" s="73"/>
-      <c r="AD6" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="AE6" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="AF6" s="75"/>
-      <c r="AG6" s="77"/>
-      <c r="AH6" s="73"/>
-      <c r="AI6" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="AJ6" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="AK6" s="75"/>
-      <c r="AL6" s="77"/>
-      <c r="AM6" s="73"/>
-      <c r="AN6" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="AO6" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="AP6" s="75"/>
-      <c r="AQ6" s="77"/>
-      <c r="AR6" s="73"/>
-      <c r="AS6" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="AT6" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="AU6" s="75"/>
-      <c r="AV6" s="77"/>
-      <c r="AW6" s="73"/>
-      <c r="AX6" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="AY6" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="AZ6" s="75"/>
-      <c r="BA6" s="77"/>
-      <c r="BB6" s="73"/>
-      <c r="BC6" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="BD6" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="BE6" s="75"/>
-      <c r="BF6" s="77"/>
-      <c r="BG6" s="73"/>
-      <c r="BH6" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="BI6" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="BJ6" s="75"/>
-      <c r="BK6" s="77"/>
-      <c r="BL6" s="73"/>
-      <c r="BM6" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="BN6" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="BO6" s="75"/>
-      <c r="BP6" s="77"/>
-      <c r="BQ6" s="73"/>
-      <c r="BR6" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="BS6" s="74" t="s">
-        <v>43</v>
-      </c>
-      <c r="BT6" s="75"/>
-      <c r="BU6" s="77"/>
+      <c r="D6" s="65"/>
+      <c r="E6" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" s="67"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="65"/>
+      <c r="J6" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="K6" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="L6" s="67"/>
+      <c r="M6" s="69"/>
+      <c r="N6" s="65"/>
+      <c r="O6" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="P6" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q6" s="67"/>
+      <c r="R6" s="69"/>
+      <c r="S6" s="65"/>
+      <c r="T6" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="U6" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="V6" s="67"/>
+      <c r="W6" s="69"/>
+      <c r="X6" s="65"/>
+      <c r="Y6" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z6" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA6" s="67"/>
+      <c r="AB6" s="69"/>
+      <c r="AC6" s="65"/>
+      <c r="AD6" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="AE6" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF6" s="67"/>
+      <c r="AG6" s="69"/>
+      <c r="AH6" s="65"/>
+      <c r="AI6" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="AJ6" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="AK6" s="67"/>
+      <c r="AL6" s="69"/>
+      <c r="AM6" s="65"/>
+      <c r="AN6" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="AO6" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="AP6" s="67"/>
+      <c r="AQ6" s="69"/>
+      <c r="AR6" s="65"/>
+      <c r="AS6" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="AT6" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="AU6" s="67"/>
+      <c r="AV6" s="69"/>
+      <c r="AW6" s="65"/>
+      <c r="AX6" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="AY6" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="AZ6" s="67"/>
+      <c r="BA6" s="69"/>
+      <c r="BB6" s="65"/>
+      <c r="BC6" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="BD6" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="BE6" s="67"/>
+      <c r="BF6" s="69"/>
+      <c r="BG6" s="65"/>
+      <c r="BH6" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="BI6" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="BJ6" s="67"/>
+      <c r="BK6" s="69"/>
+      <c r="BL6" s="65"/>
+      <c r="BM6" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="BN6" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="BO6" s="67"/>
+      <c r="BP6" s="69"/>
+      <c r="BQ6" s="65"/>
+      <c r="BR6" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="BS6" s="66" t="s">
+        <v>41</v>
+      </c>
+      <c r="BT6" s="67"/>
+      <c r="BU6" s="69"/>
     </row>
     <row r="7" spans="1:73" ht="66.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B7" s="57"/>
+      <c r="B7" s="49"/>
       <c r="C7" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="73"/>
-      <c r="E7" s="74"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="75"/>
-      <c r="H7" s="76"/>
-      <c r="I7" s="73"/>
-      <c r="J7" s="74"/>
-      <c r="K7" s="78"/>
-      <c r="L7" s="75"/>
-      <c r="M7" s="76"/>
-      <c r="N7" s="73"/>
-      <c r="O7" s="74"/>
-      <c r="P7" s="78"/>
-      <c r="Q7" s="75"/>
-      <c r="R7" s="76"/>
-      <c r="S7" s="73"/>
-      <c r="T7" s="74"/>
-      <c r="U7" s="78"/>
-      <c r="V7" s="75"/>
-      <c r="W7" s="76"/>
-      <c r="X7" s="73"/>
-      <c r="Y7" s="74"/>
-      <c r="Z7" s="78"/>
-      <c r="AA7" s="75"/>
-      <c r="AB7" s="76"/>
-      <c r="AC7" s="73"/>
-      <c r="AD7" s="74"/>
-      <c r="AE7" s="78"/>
-      <c r="AF7" s="75"/>
-      <c r="AG7" s="76"/>
-      <c r="AH7" s="73"/>
-      <c r="AI7" s="74"/>
-      <c r="AJ7" s="78"/>
-      <c r="AK7" s="75"/>
-      <c r="AL7" s="76"/>
-      <c r="AM7" s="73"/>
-      <c r="AN7" s="74"/>
-      <c r="AO7" s="78"/>
-      <c r="AP7" s="75"/>
-      <c r="AQ7" s="76"/>
-      <c r="AR7" s="73"/>
-      <c r="AS7" s="74"/>
-      <c r="AT7" s="78"/>
-      <c r="AU7" s="75"/>
-      <c r="AV7" s="76"/>
-      <c r="AW7" s="73"/>
-      <c r="AX7" s="74"/>
-      <c r="AY7" s="78"/>
-      <c r="AZ7" s="75"/>
-      <c r="BA7" s="76"/>
-      <c r="BB7" s="73"/>
-      <c r="BC7" s="74"/>
-      <c r="BD7" s="78"/>
-      <c r="BE7" s="75"/>
-      <c r="BF7" s="76"/>
-      <c r="BG7" s="73"/>
-      <c r="BH7" s="74"/>
-      <c r="BI7" s="78"/>
-      <c r="BJ7" s="75"/>
-      <c r="BK7" s="76"/>
-      <c r="BL7" s="73"/>
-      <c r="BM7" s="74"/>
-      <c r="BN7" s="78"/>
-      <c r="BO7" s="75"/>
-      <c r="BP7" s="76"/>
-      <c r="BQ7" s="73"/>
-      <c r="BR7" s="74"/>
-      <c r="BS7" s="78"/>
-      <c r="BT7" s="75"/>
-      <c r="BU7" s="76"/>
+      <c r="D7" s="65"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="70"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="65"/>
+      <c r="J7" s="66"/>
+      <c r="K7" s="70"/>
+      <c r="L7" s="67"/>
+      <c r="M7" s="68"/>
+      <c r="N7" s="65"/>
+      <c r="O7" s="66"/>
+      <c r="P7" s="70"/>
+      <c r="Q7" s="67"/>
+      <c r="R7" s="68"/>
+      <c r="S7" s="65"/>
+      <c r="T7" s="66"/>
+      <c r="U7" s="70"/>
+      <c r="V7" s="67"/>
+      <c r="W7" s="68"/>
+      <c r="X7" s="65"/>
+      <c r="Y7" s="66"/>
+      <c r="Z7" s="70"/>
+      <c r="AA7" s="67"/>
+      <c r="AB7" s="68"/>
+      <c r="AC7" s="65"/>
+      <c r="AD7" s="66"/>
+      <c r="AE7" s="70"/>
+      <c r="AF7" s="67"/>
+      <c r="AG7" s="68"/>
+      <c r="AH7" s="65"/>
+      <c r="AI7" s="66"/>
+      <c r="AJ7" s="70"/>
+      <c r="AK7" s="67"/>
+      <c r="AL7" s="68"/>
+      <c r="AM7" s="65"/>
+      <c r="AN7" s="66"/>
+      <c r="AO7" s="70"/>
+      <c r="AP7" s="67"/>
+      <c r="AQ7" s="68"/>
+      <c r="AR7" s="65"/>
+      <c r="AS7" s="66"/>
+      <c r="AT7" s="70"/>
+      <c r="AU7" s="67"/>
+      <c r="AV7" s="68"/>
+      <c r="AW7" s="65"/>
+      <c r="AX7" s="66"/>
+      <c r="AY7" s="70"/>
+      <c r="AZ7" s="67"/>
+      <c r="BA7" s="68"/>
+      <c r="BB7" s="65"/>
+      <c r="BC7" s="66"/>
+      <c r="BD7" s="70"/>
+      <c r="BE7" s="67"/>
+      <c r="BF7" s="68"/>
+      <c r="BG7" s="65"/>
+      <c r="BH7" s="66"/>
+      <c r="BI7" s="70"/>
+      <c r="BJ7" s="67"/>
+      <c r="BK7" s="68"/>
+      <c r="BL7" s="65"/>
+      <c r="BM7" s="66"/>
+      <c r="BN7" s="70"/>
+      <c r="BO7" s="67"/>
+      <c r="BP7" s="68"/>
+      <c r="BQ7" s="65"/>
+      <c r="BR7" s="66"/>
+      <c r="BS7" s="70"/>
+      <c r="BT7" s="67"/>
+      <c r="BU7" s="68"/>
     </row>
     <row r="8" spans="1:73" ht="79.349999999999994" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B8" s="57"/>
+      <c r="B8" s="49"/>
       <c r="C8" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="73"/>
-      <c r="E8" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8" s="75"/>
-      <c r="H8" s="76"/>
-      <c r="I8" s="73"/>
-      <c r="J8" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="K8" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="L8" s="75"/>
-      <c r="M8" s="76"/>
-      <c r="N8" s="73"/>
-      <c r="O8" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="P8" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q8" s="75"/>
-      <c r="R8" s="76"/>
-      <c r="S8" s="73"/>
-      <c r="T8" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="U8" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="V8" s="75"/>
-      <c r="W8" s="76"/>
-      <c r="X8" s="73"/>
-      <c r="Y8" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z8" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA8" s="75"/>
-      <c r="AB8" s="76"/>
-      <c r="AC8" s="73"/>
-      <c r="AD8" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE8" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF8" s="75"/>
-      <c r="AG8" s="76"/>
-      <c r="AH8" s="73"/>
-      <c r="AI8" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="AJ8" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="AK8" s="75"/>
-      <c r="AL8" s="76"/>
-      <c r="AM8" s="73"/>
-      <c r="AN8" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="AO8" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="AP8" s="75"/>
-      <c r="AQ8" s="76"/>
-      <c r="AR8" s="73"/>
-      <c r="AS8" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT8" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="AU8" s="75"/>
-      <c r="AV8" s="76"/>
-      <c r="AW8" s="73"/>
-      <c r="AX8" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="AY8" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="AZ8" s="75"/>
-      <c r="BA8" s="76"/>
-      <c r="BB8" s="73"/>
-      <c r="BC8" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="BD8" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="BE8" s="75"/>
-      <c r="BF8" s="76"/>
-      <c r="BG8" s="73"/>
-      <c r="BH8" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="BI8" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="BJ8" s="75"/>
-      <c r="BK8" s="76"/>
-      <c r="BL8" s="73"/>
-      <c r="BM8" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="BN8" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="BO8" s="75"/>
-      <c r="BP8" s="76"/>
-      <c r="BQ8" s="73"/>
-      <c r="BR8" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="BS8" s="74" t="s">
-        <v>44</v>
-      </c>
-      <c r="BT8" s="75"/>
-      <c r="BU8" s="76"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="67"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="65"/>
+      <c r="J8" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="K8" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="L8" s="67"/>
+      <c r="M8" s="68"/>
+      <c r="N8" s="65"/>
+      <c r="O8" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="P8" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q8" s="67"/>
+      <c r="R8" s="68"/>
+      <c r="S8" s="65"/>
+      <c r="T8" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="U8" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="V8" s="67"/>
+      <c r="W8" s="68"/>
+      <c r="X8" s="65"/>
+      <c r="Y8" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z8" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA8" s="67"/>
+      <c r="AB8" s="68"/>
+      <c r="AC8" s="65"/>
+      <c r="AD8" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE8" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF8" s="67"/>
+      <c r="AG8" s="68"/>
+      <c r="AH8" s="65"/>
+      <c r="AI8" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="AJ8" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK8" s="67"/>
+      <c r="AL8" s="68"/>
+      <c r="AM8" s="65"/>
+      <c r="AN8" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="AO8" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP8" s="67"/>
+      <c r="AQ8" s="68"/>
+      <c r="AR8" s="65"/>
+      <c r="AS8" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="AT8" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="AU8" s="67"/>
+      <c r="AV8" s="68"/>
+      <c r="AW8" s="65"/>
+      <c r="AX8" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="AY8" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="AZ8" s="67"/>
+      <c r="BA8" s="68"/>
+      <c r="BB8" s="65"/>
+      <c r="BC8" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="BD8" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="BE8" s="67"/>
+      <c r="BF8" s="68"/>
+      <c r="BG8" s="65"/>
+      <c r="BH8" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="BI8" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="BJ8" s="67"/>
+      <c r="BK8" s="68"/>
+      <c r="BL8" s="65"/>
+      <c r="BM8" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="BN8" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="BO8" s="67"/>
+      <c r="BP8" s="68"/>
+      <c r="BQ8" s="65"/>
+      <c r="BR8" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="BS8" s="66" t="s">
+        <v>42</v>
+      </c>
+      <c r="BT8" s="67"/>
+      <c r="BU8" s="68"/>
     </row>
     <row r="9" spans="1:73" ht="95.2" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="57"/>
+      <c r="B9" s="49"/>
       <c r="C9" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="73"/>
-      <c r="E9" s="74" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" s="74" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="75"/>
-      <c r="H9" s="76"/>
-      <c r="I9" s="73"/>
-      <c r="J9" s="74" t="s">
-        <v>45</v>
-      </c>
-      <c r="K9" s="74" t="s">
-        <v>45</v>
-      </c>
-      <c r="L9" s="75"/>
-      <c r="M9" s="76"/>
-      <c r="N9" s="73"/>
-      <c r="O9" s="74" t="s">
-        <v>45</v>
-      </c>
-      <c r="P9" s="74" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q9" s="75"/>
-      <c r="R9" s="76"/>
-      <c r="S9" s="73"/>
-      <c r="T9" s="74" t="s">
-        <v>45</v>
-      </c>
-      <c r="U9" s="74" t="s">
-        <v>45</v>
-      </c>
-      <c r="V9" s="75"/>
-      <c r="W9" s="76"/>
-      <c r="X9" s="73"/>
-      <c r="Y9" s="74" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z9" s="74" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA9" s="75"/>
-      <c r="AB9" s="76"/>
-      <c r="AC9" s="73"/>
-      <c r="AD9" s="74" t="s">
-        <v>45</v>
-      </c>
-      <c r="AE9" s="74" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF9" s="75"/>
-      <c r="AG9" s="76"/>
-      <c r="AH9" s="73"/>
-      <c r="AI9" s="74" t="s">
-        <v>45</v>
-      </c>
-      <c r="AJ9" s="74" t="s">
-        <v>45</v>
-      </c>
-      <c r="AK9" s="75"/>
-      <c r="AL9" s="76"/>
-      <c r="AM9" s="73"/>
-      <c r="AN9" s="74" t="s">
-        <v>45</v>
-      </c>
-      <c r="AO9" s="74" t="s">
-        <v>45</v>
-      </c>
-      <c r="AP9" s="75"/>
-      <c r="AQ9" s="76"/>
-      <c r="AR9" s="73"/>
-      <c r="AS9" s="74" t="s">
-        <v>45</v>
-      </c>
-      <c r="AT9" s="74" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU9" s="75"/>
-      <c r="AV9" s="76"/>
-      <c r="AW9" s="73"/>
-      <c r="AX9" s="74" t="s">
-        <v>45</v>
-      </c>
-      <c r="AY9" s="74" t="s">
-        <v>45</v>
-      </c>
-      <c r="AZ9" s="75"/>
-      <c r="BA9" s="76"/>
-      <c r="BB9" s="73"/>
-      <c r="BC9" s="74" t="s">
-        <v>45</v>
-      </c>
-      <c r="BD9" s="74" t="s">
-        <v>45</v>
-      </c>
-      <c r="BE9" s="75"/>
-      <c r="BF9" s="76"/>
-      <c r="BG9" s="73"/>
-      <c r="BH9" s="74" t="s">
-        <v>45</v>
-      </c>
-      <c r="BI9" s="74" t="s">
-        <v>45</v>
-      </c>
-      <c r="BJ9" s="75"/>
-      <c r="BK9" s="76"/>
-      <c r="BL9" s="73"/>
-      <c r="BM9" s="74" t="s">
-        <v>45</v>
-      </c>
-      <c r="BN9" s="74" t="s">
-        <v>45</v>
-      </c>
-      <c r="BO9" s="75"/>
-      <c r="BP9" s="76"/>
-      <c r="BQ9" s="73"/>
-      <c r="BR9" s="74" t="s">
-        <v>45</v>
-      </c>
-      <c r="BS9" s="74" t="s">
-        <v>45</v>
-      </c>
-      <c r="BT9" s="75"/>
-      <c r="BU9" s="76"/>
+      <c r="D9" s="65"/>
+      <c r="E9" s="66" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" s="66" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="67"/>
+      <c r="H9" s="68"/>
+      <c r="I9" s="65"/>
+      <c r="J9" s="66" t="s">
+        <v>43</v>
+      </c>
+      <c r="K9" s="66" t="s">
+        <v>43</v>
+      </c>
+      <c r="L9" s="67"/>
+      <c r="M9" s="68"/>
+      <c r="N9" s="65"/>
+      <c r="O9" s="66" t="s">
+        <v>43</v>
+      </c>
+      <c r="P9" s="66" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q9" s="67"/>
+      <c r="R9" s="68"/>
+      <c r="S9" s="65"/>
+      <c r="T9" s="66" t="s">
+        <v>43</v>
+      </c>
+      <c r="U9" s="66" t="s">
+        <v>43</v>
+      </c>
+      <c r="V9" s="67"/>
+      <c r="W9" s="68"/>
+      <c r="X9" s="65"/>
+      <c r="Y9" s="66" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z9" s="66" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA9" s="67"/>
+      <c r="AB9" s="68"/>
+      <c r="AC9" s="65"/>
+      <c r="AD9" s="66" t="s">
+        <v>43</v>
+      </c>
+      <c r="AE9" s="66" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF9" s="67"/>
+      <c r="AG9" s="68"/>
+      <c r="AH9" s="65"/>
+      <c r="AI9" s="66" t="s">
+        <v>43</v>
+      </c>
+      <c r="AJ9" s="66" t="s">
+        <v>43</v>
+      </c>
+      <c r="AK9" s="67"/>
+      <c r="AL9" s="68"/>
+      <c r="AM9" s="65"/>
+      <c r="AN9" s="66" t="s">
+        <v>43</v>
+      </c>
+      <c r="AO9" s="66" t="s">
+        <v>43</v>
+      </c>
+      <c r="AP9" s="67"/>
+      <c r="AQ9" s="68"/>
+      <c r="AR9" s="65"/>
+      <c r="AS9" s="66" t="s">
+        <v>43</v>
+      </c>
+      <c r="AT9" s="66" t="s">
+        <v>43</v>
+      </c>
+      <c r="AU9" s="67"/>
+      <c r="AV9" s="68"/>
+      <c r="AW9" s="65"/>
+      <c r="AX9" s="66" t="s">
+        <v>43</v>
+      </c>
+      <c r="AY9" s="66" t="s">
+        <v>43</v>
+      </c>
+      <c r="AZ9" s="67"/>
+      <c r="BA9" s="68"/>
+      <c r="BB9" s="65"/>
+      <c r="BC9" s="66" t="s">
+        <v>43</v>
+      </c>
+      <c r="BD9" s="66" t="s">
+        <v>43</v>
+      </c>
+      <c r="BE9" s="67"/>
+      <c r="BF9" s="68"/>
+      <c r="BG9" s="65"/>
+      <c r="BH9" s="66" t="s">
+        <v>43</v>
+      </c>
+      <c r="BI9" s="66" t="s">
+        <v>43</v>
+      </c>
+      <c r="BJ9" s="67"/>
+      <c r="BK9" s="68"/>
+      <c r="BL9" s="65"/>
+      <c r="BM9" s="66" t="s">
+        <v>43</v>
+      </c>
+      <c r="BN9" s="66" t="s">
+        <v>43</v>
+      </c>
+      <c r="BO9" s="67"/>
+      <c r="BP9" s="68"/>
+      <c r="BQ9" s="65"/>
+      <c r="BR9" s="66" t="s">
+        <v>43</v>
+      </c>
+      <c r="BS9" s="66" t="s">
+        <v>43</v>
+      </c>
+      <c r="BT9" s="67"/>
+      <c r="BU9" s="68"/>
     </row>
     <row r="10" spans="1:73" ht="70.900000000000006" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="58"/>
-      <c r="C10" s="24" t="s">
+      <c r="B10" s="50"/>
+      <c r="C10" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="79"/>
-      <c r="E10" s="80"/>
-      <c r="F10" s="80"/>
-      <c r="G10" s="81"/>
-      <c r="H10" s="82"/>
-      <c r="I10" s="79"/>
-      <c r="J10" s="80"/>
-      <c r="K10" s="80"/>
-      <c r="L10" s="81"/>
-      <c r="M10" s="82"/>
-      <c r="N10" s="79"/>
-      <c r="O10" s="80"/>
-      <c r="P10" s="80"/>
-      <c r="Q10" s="81"/>
-      <c r="R10" s="82"/>
-      <c r="S10" s="79"/>
-      <c r="T10" s="80"/>
-      <c r="U10" s="80"/>
-      <c r="V10" s="81"/>
-      <c r="W10" s="82"/>
-      <c r="X10" s="79"/>
-      <c r="Y10" s="80"/>
-      <c r="Z10" s="80"/>
-      <c r="AA10" s="81"/>
-      <c r="AB10" s="82"/>
-      <c r="AC10" s="79"/>
-      <c r="AD10" s="80"/>
-      <c r="AE10" s="80"/>
-      <c r="AF10" s="81"/>
-      <c r="AG10" s="82"/>
-      <c r="AH10" s="79"/>
-      <c r="AI10" s="80"/>
-      <c r="AJ10" s="80"/>
-      <c r="AK10" s="81"/>
-      <c r="AL10" s="82"/>
-      <c r="AM10" s="79"/>
-      <c r="AN10" s="80"/>
-      <c r="AO10" s="80"/>
-      <c r="AP10" s="81"/>
-      <c r="AQ10" s="82"/>
-      <c r="AR10" s="79"/>
-      <c r="AS10" s="80"/>
-      <c r="AT10" s="80"/>
-      <c r="AU10" s="81"/>
-      <c r="AV10" s="82"/>
-      <c r="AW10" s="79"/>
-      <c r="AX10" s="80"/>
-      <c r="AY10" s="80"/>
-      <c r="AZ10" s="81"/>
-      <c r="BA10" s="82"/>
-      <c r="BB10" s="79"/>
-      <c r="BC10" s="80"/>
-      <c r="BD10" s="80"/>
-      <c r="BE10" s="81"/>
-      <c r="BF10" s="82"/>
-      <c r="BG10" s="79"/>
-      <c r="BH10" s="80"/>
-      <c r="BI10" s="80"/>
-      <c r="BJ10" s="81"/>
-      <c r="BK10" s="82"/>
-      <c r="BL10" s="79"/>
-      <c r="BM10" s="80"/>
-      <c r="BN10" s="80"/>
-      <c r="BO10" s="81"/>
-      <c r="BP10" s="82"/>
-      <c r="BQ10" s="79"/>
-      <c r="BR10" s="80"/>
-      <c r="BS10" s="80"/>
-      <c r="BT10" s="81"/>
-      <c r="BU10" s="82"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="72"/>
+      <c r="F10" s="72"/>
+      <c r="G10" s="73"/>
+      <c r="H10" s="74"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="72"/>
+      <c r="K10" s="72"/>
+      <c r="L10" s="73"/>
+      <c r="M10" s="74"/>
+      <c r="N10" s="71"/>
+      <c r="O10" s="72"/>
+      <c r="P10" s="72"/>
+      <c r="Q10" s="73"/>
+      <c r="R10" s="74"/>
+      <c r="S10" s="71"/>
+      <c r="T10" s="72"/>
+      <c r="U10" s="72"/>
+      <c r="V10" s="73"/>
+      <c r="W10" s="74"/>
+      <c r="X10" s="71"/>
+      <c r="Y10" s="72"/>
+      <c r="Z10" s="72"/>
+      <c r="AA10" s="73"/>
+      <c r="AB10" s="74"/>
+      <c r="AC10" s="71"/>
+      <c r="AD10" s="72"/>
+      <c r="AE10" s="72"/>
+      <c r="AF10" s="73"/>
+      <c r="AG10" s="74"/>
+      <c r="AH10" s="71"/>
+      <c r="AI10" s="72"/>
+      <c r="AJ10" s="72"/>
+      <c r="AK10" s="73"/>
+      <c r="AL10" s="74"/>
+      <c r="AM10" s="71"/>
+      <c r="AN10" s="72"/>
+      <c r="AO10" s="72"/>
+      <c r="AP10" s="73"/>
+      <c r="AQ10" s="74"/>
+      <c r="AR10" s="71"/>
+      <c r="AS10" s="72"/>
+      <c r="AT10" s="72"/>
+      <c r="AU10" s="73"/>
+      <c r="AV10" s="74"/>
+      <c r="AW10" s="71"/>
+      <c r="AX10" s="72"/>
+      <c r="AY10" s="72"/>
+      <c r="AZ10" s="73"/>
+      <c r="BA10" s="74"/>
+      <c r="BB10" s="71"/>
+      <c r="BC10" s="72"/>
+      <c r="BD10" s="72"/>
+      <c r="BE10" s="73"/>
+      <c r="BF10" s="74"/>
+      <c r="BG10" s="71"/>
+      <c r="BH10" s="72"/>
+      <c r="BI10" s="72"/>
+      <c r="BJ10" s="73"/>
+      <c r="BK10" s="74"/>
+      <c r="BL10" s="71"/>
+      <c r="BM10" s="72"/>
+      <c r="BN10" s="72"/>
+      <c r="BO10" s="73"/>
+      <c r="BP10" s="74"/>
+      <c r="BQ10" s="71"/>
+      <c r="BR10" s="72"/>
+      <c r="BS10" s="72"/>
+      <c r="BT10" s="73"/>
+      <c r="BU10" s="74"/>
     </row>
     <row r="11" spans="1:73" ht="48" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B11" s="55" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="23" t="s">
+      <c r="B11" s="47" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="69"/>
-      <c r="E11" s="70"/>
-      <c r="F11" s="70"/>
-      <c r="G11" s="71"/>
-      <c r="H11" s="72"/>
-      <c r="I11" s="69"/>
-      <c r="J11" s="70"/>
-      <c r="K11" s="70"/>
-      <c r="L11" s="71"/>
-      <c r="M11" s="72"/>
-      <c r="N11" s="69"/>
-      <c r="O11" s="70"/>
-      <c r="P11" s="70"/>
-      <c r="Q11" s="71"/>
-      <c r="R11" s="72"/>
-      <c r="S11" s="69"/>
-      <c r="T11" s="70"/>
-      <c r="U11" s="70"/>
-      <c r="V11" s="71"/>
-      <c r="W11" s="72"/>
-      <c r="X11" s="69"/>
-      <c r="Y11" s="70"/>
-      <c r="Z11" s="70"/>
-      <c r="AA11" s="71"/>
-      <c r="AB11" s="72"/>
-      <c r="AC11" s="69"/>
-      <c r="AD11" s="70"/>
-      <c r="AE11" s="70"/>
-      <c r="AF11" s="71"/>
-      <c r="AG11" s="72"/>
-      <c r="AH11" s="69"/>
-      <c r="AI11" s="70"/>
-      <c r="AJ11" s="70"/>
-      <c r="AK11" s="71"/>
-      <c r="AL11" s="72"/>
-      <c r="AM11" s="69"/>
-      <c r="AN11" s="70"/>
-      <c r="AO11" s="70"/>
-      <c r="AP11" s="71"/>
-      <c r="AQ11" s="72"/>
-      <c r="AR11" s="69"/>
-      <c r="AS11" s="70"/>
-      <c r="AT11" s="70"/>
-      <c r="AU11" s="71"/>
-      <c r="AV11" s="72"/>
-      <c r="AW11" s="69"/>
-      <c r="AX11" s="70"/>
-      <c r="AY11" s="70"/>
-      <c r="AZ11" s="71"/>
-      <c r="BA11" s="72"/>
-      <c r="BB11" s="69"/>
-      <c r="BC11" s="70"/>
-      <c r="BD11" s="70"/>
-      <c r="BE11" s="71"/>
-      <c r="BF11" s="72"/>
-      <c r="BG11" s="69"/>
-      <c r="BH11" s="70"/>
-      <c r="BI11" s="70"/>
-      <c r="BJ11" s="71"/>
-      <c r="BK11" s="72"/>
-      <c r="BL11" s="69"/>
-      <c r="BM11" s="70"/>
-      <c r="BN11" s="70"/>
-      <c r="BO11" s="71"/>
-      <c r="BP11" s="72"/>
-      <c r="BQ11" s="69"/>
-      <c r="BR11" s="70"/>
-      <c r="BS11" s="70"/>
-      <c r="BT11" s="71"/>
-      <c r="BU11" s="72"/>
+      <c r="D11" s="61"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
+      <c r="G11" s="63"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="62"/>
+      <c r="K11" s="62"/>
+      <c r="L11" s="63"/>
+      <c r="M11" s="64"/>
+      <c r="N11" s="61"/>
+      <c r="O11" s="62"/>
+      <c r="P11" s="62"/>
+      <c r="Q11" s="63"/>
+      <c r="R11" s="64"/>
+      <c r="S11" s="61"/>
+      <c r="T11" s="62"/>
+      <c r="U11" s="62"/>
+      <c r="V11" s="63"/>
+      <c r="W11" s="64"/>
+      <c r="X11" s="61"/>
+      <c r="Y11" s="62"/>
+      <c r="Z11" s="62"/>
+      <c r="AA11" s="63"/>
+      <c r="AB11" s="64"/>
+      <c r="AC11" s="61"/>
+      <c r="AD11" s="62"/>
+      <c r="AE11" s="62"/>
+      <c r="AF11" s="63"/>
+      <c r="AG11" s="64"/>
+      <c r="AH11" s="61"/>
+      <c r="AI11" s="62"/>
+      <c r="AJ11" s="62"/>
+      <c r="AK11" s="63"/>
+      <c r="AL11" s="64"/>
+      <c r="AM11" s="61"/>
+      <c r="AN11" s="62"/>
+      <c r="AO11" s="62"/>
+      <c r="AP11" s="63"/>
+      <c r="AQ11" s="64"/>
+      <c r="AR11" s="61"/>
+      <c r="AS11" s="62"/>
+      <c r="AT11" s="62"/>
+      <c r="AU11" s="63"/>
+      <c r="AV11" s="64"/>
+      <c r="AW11" s="61"/>
+      <c r="AX11" s="62"/>
+      <c r="AY11" s="62"/>
+      <c r="AZ11" s="63"/>
+      <c r="BA11" s="64"/>
+      <c r="BB11" s="61"/>
+      <c r="BC11" s="62"/>
+      <c r="BD11" s="62"/>
+      <c r="BE11" s="63"/>
+      <c r="BF11" s="64"/>
+      <c r="BG11" s="61"/>
+      <c r="BH11" s="62"/>
+      <c r="BI11" s="62"/>
+      <c r="BJ11" s="63"/>
+      <c r="BK11" s="64"/>
+      <c r="BL11" s="61"/>
+      <c r="BM11" s="62"/>
+      <c r="BN11" s="62"/>
+      <c r="BO11" s="63"/>
+      <c r="BP11" s="64"/>
+      <c r="BQ11" s="61"/>
+      <c r="BR11" s="62"/>
+      <c r="BS11" s="62"/>
+      <c r="BT11" s="63"/>
+      <c r="BU11" s="64"/>
     </row>
     <row r="12" spans="1:73" ht="93.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="59"/>
+      <c r="B12" s="51"/>
       <c r="C12" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="73"/>
-      <c r="E12" s="74"/>
-      <c r="F12" s="74"/>
-      <c r="G12" s="75"/>
-      <c r="H12" s="76"/>
-      <c r="I12" s="73"/>
-      <c r="J12" s="74"/>
-      <c r="K12" s="74"/>
-      <c r="L12" s="75"/>
-      <c r="M12" s="76"/>
-      <c r="N12" s="73"/>
-      <c r="O12" s="74"/>
-      <c r="P12" s="74"/>
-      <c r="Q12" s="75"/>
-      <c r="R12" s="76"/>
-      <c r="S12" s="73"/>
-      <c r="T12" s="74"/>
-      <c r="U12" s="74"/>
-      <c r="V12" s="75"/>
-      <c r="W12" s="76"/>
-      <c r="X12" s="73"/>
-      <c r="Y12" s="74"/>
-      <c r="Z12" s="74"/>
-      <c r="AA12" s="75"/>
-      <c r="AB12" s="76"/>
-      <c r="AC12" s="73"/>
-      <c r="AD12" s="74"/>
-      <c r="AE12" s="74"/>
-      <c r="AF12" s="75"/>
-      <c r="AG12" s="76"/>
-      <c r="AH12" s="73"/>
-      <c r="AI12" s="74"/>
-      <c r="AJ12" s="74"/>
-      <c r="AK12" s="75"/>
-      <c r="AL12" s="76"/>
-      <c r="AM12" s="73"/>
-      <c r="AN12" s="74"/>
-      <c r="AO12" s="74"/>
-      <c r="AP12" s="75"/>
-      <c r="AQ12" s="76"/>
-      <c r="AR12" s="73"/>
-      <c r="AS12" s="74"/>
-      <c r="AT12" s="74"/>
-      <c r="AU12" s="75"/>
-      <c r="AV12" s="76"/>
-      <c r="AW12" s="73"/>
-      <c r="AX12" s="74"/>
-      <c r="AY12" s="74"/>
-      <c r="AZ12" s="75"/>
-      <c r="BA12" s="76"/>
-      <c r="BB12" s="73"/>
-      <c r="BC12" s="74"/>
-      <c r="BD12" s="74"/>
-      <c r="BE12" s="75"/>
-      <c r="BF12" s="76"/>
-      <c r="BG12" s="73"/>
-      <c r="BH12" s="74"/>
-      <c r="BI12" s="74"/>
-      <c r="BJ12" s="75"/>
-      <c r="BK12" s="76"/>
-      <c r="BL12" s="73"/>
-      <c r="BM12" s="74"/>
-      <c r="BN12" s="74"/>
-      <c r="BO12" s="75"/>
-      <c r="BP12" s="76"/>
-      <c r="BQ12" s="73"/>
-      <c r="BR12" s="74"/>
-      <c r="BS12" s="74"/>
-      <c r="BT12" s="75"/>
-      <c r="BU12" s="76"/>
+        <v>14</v>
+      </c>
+      <c r="D12" s="65"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="68"/>
+      <c r="I12" s="65"/>
+      <c r="J12" s="66"/>
+      <c r="K12" s="66"/>
+      <c r="L12" s="67"/>
+      <c r="M12" s="68"/>
+      <c r="N12" s="65"/>
+      <c r="O12" s="66"/>
+      <c r="P12" s="66"/>
+      <c r="Q12" s="67"/>
+      <c r="R12" s="68"/>
+      <c r="S12" s="65"/>
+      <c r="T12" s="66"/>
+      <c r="U12" s="66"/>
+      <c r="V12" s="67"/>
+      <c r="W12" s="68"/>
+      <c r="X12" s="65"/>
+      <c r="Y12" s="66"/>
+      <c r="Z12" s="66"/>
+      <c r="AA12" s="67"/>
+      <c r="AB12" s="68"/>
+      <c r="AC12" s="65"/>
+      <c r="AD12" s="66"/>
+      <c r="AE12" s="66"/>
+      <c r="AF12" s="67"/>
+      <c r="AG12" s="68"/>
+      <c r="AH12" s="65"/>
+      <c r="AI12" s="66"/>
+      <c r="AJ12" s="66"/>
+      <c r="AK12" s="67"/>
+      <c r="AL12" s="68"/>
+      <c r="AM12" s="65"/>
+      <c r="AN12" s="66"/>
+      <c r="AO12" s="66"/>
+      <c r="AP12" s="67"/>
+      <c r="AQ12" s="68"/>
+      <c r="AR12" s="65"/>
+      <c r="AS12" s="66"/>
+      <c r="AT12" s="66"/>
+      <c r="AU12" s="67"/>
+      <c r="AV12" s="68"/>
+      <c r="AW12" s="65"/>
+      <c r="AX12" s="66"/>
+      <c r="AY12" s="66"/>
+      <c r="AZ12" s="67"/>
+      <c r="BA12" s="68"/>
+      <c r="BB12" s="65"/>
+      <c r="BC12" s="66"/>
+      <c r="BD12" s="66"/>
+      <c r="BE12" s="67"/>
+      <c r="BF12" s="68"/>
+      <c r="BG12" s="65"/>
+      <c r="BH12" s="66"/>
+      <c r="BI12" s="66"/>
+      <c r="BJ12" s="67"/>
+      <c r="BK12" s="68"/>
+      <c r="BL12" s="65"/>
+      <c r="BM12" s="66"/>
+      <c r="BN12" s="66"/>
+      <c r="BO12" s="67"/>
+      <c r="BP12" s="68"/>
+      <c r="BQ12" s="65"/>
+      <c r="BR12" s="66"/>
+      <c r="BS12" s="66"/>
+      <c r="BT12" s="67"/>
+      <c r="BU12" s="68"/>
     </row>
     <row r="13" spans="1:73" ht="49.35" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B13" s="57"/>
+      <c r="B13" s="49"/>
       <c r="C13" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="73"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="74"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="77"/>
-      <c r="I13" s="73"/>
-      <c r="J13" s="74"/>
-      <c r="K13" s="74"/>
-      <c r="L13" s="75"/>
-      <c r="M13" s="77"/>
-      <c r="N13" s="73"/>
-      <c r="O13" s="74"/>
-      <c r="P13" s="74"/>
-      <c r="Q13" s="75"/>
-      <c r="R13" s="77"/>
-      <c r="S13" s="73"/>
-      <c r="T13" s="74"/>
-      <c r="U13" s="74"/>
-      <c r="V13" s="75"/>
-      <c r="W13" s="77"/>
-      <c r="X13" s="73"/>
-      <c r="Y13" s="74"/>
-      <c r="Z13" s="74"/>
-      <c r="AA13" s="75"/>
-      <c r="AB13" s="77"/>
-      <c r="AC13" s="73"/>
-      <c r="AD13" s="74"/>
-      <c r="AE13" s="74"/>
-      <c r="AF13" s="75"/>
-      <c r="AG13" s="77"/>
-      <c r="AH13" s="73"/>
-      <c r="AI13" s="74"/>
-      <c r="AJ13" s="74"/>
-      <c r="AK13" s="75"/>
-      <c r="AL13" s="77"/>
-      <c r="AM13" s="73"/>
-      <c r="AN13" s="74"/>
-      <c r="AO13" s="74"/>
-      <c r="AP13" s="75"/>
-      <c r="AQ13" s="77"/>
-      <c r="AR13" s="73"/>
-      <c r="AS13" s="74"/>
-      <c r="AT13" s="74"/>
-      <c r="AU13" s="75"/>
-      <c r="AV13" s="77"/>
-      <c r="AW13" s="73"/>
-      <c r="AX13" s="74"/>
-      <c r="AY13" s="74"/>
-      <c r="AZ13" s="75"/>
-      <c r="BA13" s="77"/>
-      <c r="BB13" s="73"/>
-      <c r="BC13" s="74"/>
-      <c r="BD13" s="74"/>
-      <c r="BE13" s="75"/>
-      <c r="BF13" s="77"/>
-      <c r="BG13" s="73"/>
-      <c r="BH13" s="74"/>
-      <c r="BI13" s="74"/>
-      <c r="BJ13" s="75"/>
-      <c r="BK13" s="77"/>
-      <c r="BL13" s="73"/>
-      <c r="BM13" s="74"/>
-      <c r="BN13" s="74"/>
-      <c r="BO13" s="75"/>
-      <c r="BP13" s="77"/>
-      <c r="BQ13" s="73"/>
-      <c r="BR13" s="74"/>
-      <c r="BS13" s="74"/>
-      <c r="BT13" s="75"/>
-      <c r="BU13" s="77"/>
+      <c r="D13" s="65"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="66"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="69"/>
+      <c r="I13" s="65"/>
+      <c r="J13" s="66"/>
+      <c r="K13" s="66"/>
+      <c r="L13" s="67"/>
+      <c r="M13" s="69"/>
+      <c r="N13" s="65"/>
+      <c r="O13" s="66"/>
+      <c r="P13" s="66"/>
+      <c r="Q13" s="67"/>
+      <c r="R13" s="69"/>
+      <c r="S13" s="65"/>
+      <c r="T13" s="66"/>
+      <c r="U13" s="66"/>
+      <c r="V13" s="67"/>
+      <c r="W13" s="69"/>
+      <c r="X13" s="65"/>
+      <c r="Y13" s="66"/>
+      <c r="Z13" s="66"/>
+      <c r="AA13" s="67"/>
+      <c r="AB13" s="69"/>
+      <c r="AC13" s="65"/>
+      <c r="AD13" s="66"/>
+      <c r="AE13" s="66"/>
+      <c r="AF13" s="67"/>
+      <c r="AG13" s="69"/>
+      <c r="AH13" s="65"/>
+      <c r="AI13" s="66"/>
+      <c r="AJ13" s="66"/>
+      <c r="AK13" s="67"/>
+      <c r="AL13" s="69"/>
+      <c r="AM13" s="65"/>
+      <c r="AN13" s="66"/>
+      <c r="AO13" s="66"/>
+      <c r="AP13" s="67"/>
+      <c r="AQ13" s="69"/>
+      <c r="AR13" s="65"/>
+      <c r="AS13" s="66"/>
+      <c r="AT13" s="66"/>
+      <c r="AU13" s="67"/>
+      <c r="AV13" s="69"/>
+      <c r="AW13" s="65"/>
+      <c r="AX13" s="66"/>
+      <c r="AY13" s="66"/>
+      <c r="AZ13" s="67"/>
+      <c r="BA13" s="69"/>
+      <c r="BB13" s="65"/>
+      <c r="BC13" s="66"/>
+      <c r="BD13" s="66"/>
+      <c r="BE13" s="67"/>
+      <c r="BF13" s="69"/>
+      <c r="BG13" s="65"/>
+      <c r="BH13" s="66"/>
+      <c r="BI13" s="66"/>
+      <c r="BJ13" s="67"/>
+      <c r="BK13" s="69"/>
+      <c r="BL13" s="65"/>
+      <c r="BM13" s="66"/>
+      <c r="BN13" s="66"/>
+      <c r="BO13" s="67"/>
+      <c r="BP13" s="69"/>
+      <c r="BQ13" s="65"/>
+      <c r="BR13" s="66"/>
+      <c r="BS13" s="66"/>
+      <c r="BT13" s="67"/>
+      <c r="BU13" s="69"/>
     </row>
     <row r="14" spans="1:73" ht="62.2" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B14" s="57"/>
+      <c r="B14" s="49"/>
       <c r="C14" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="73"/>
-      <c r="E14" s="74"/>
-      <c r="F14" s="74"/>
-      <c r="G14" s="75"/>
-      <c r="H14" s="77"/>
-      <c r="I14" s="73"/>
-      <c r="J14" s="74"/>
-      <c r="K14" s="74"/>
-      <c r="L14" s="75"/>
-      <c r="M14" s="77"/>
-      <c r="N14" s="73"/>
-      <c r="O14" s="74"/>
-      <c r="P14" s="74"/>
-      <c r="Q14" s="75"/>
-      <c r="R14" s="77"/>
-      <c r="S14" s="73"/>
-      <c r="T14" s="74"/>
-      <c r="U14" s="74"/>
-      <c r="V14" s="75"/>
-      <c r="W14" s="77"/>
-      <c r="X14" s="73"/>
-      <c r="Y14" s="74"/>
-      <c r="Z14" s="74"/>
-      <c r="AA14" s="75"/>
-      <c r="AB14" s="77"/>
-      <c r="AC14" s="73"/>
-      <c r="AD14" s="74"/>
-      <c r="AE14" s="74"/>
-      <c r="AF14" s="75"/>
-      <c r="AG14" s="77"/>
-      <c r="AH14" s="73"/>
-      <c r="AI14" s="74"/>
-      <c r="AJ14" s="74"/>
-      <c r="AK14" s="75"/>
-      <c r="AL14" s="77"/>
-      <c r="AM14" s="73"/>
-      <c r="AN14" s="74"/>
-      <c r="AO14" s="74"/>
-      <c r="AP14" s="75"/>
-      <c r="AQ14" s="77"/>
-      <c r="AR14" s="73"/>
-      <c r="AS14" s="74"/>
-      <c r="AT14" s="74"/>
-      <c r="AU14" s="75"/>
-      <c r="AV14" s="77"/>
-      <c r="AW14" s="73"/>
-      <c r="AX14" s="74"/>
-      <c r="AY14" s="74"/>
-      <c r="AZ14" s="75"/>
-      <c r="BA14" s="77"/>
-      <c r="BB14" s="73"/>
-      <c r="BC14" s="74"/>
-      <c r="BD14" s="74"/>
-      <c r="BE14" s="75"/>
-      <c r="BF14" s="77"/>
-      <c r="BG14" s="73"/>
-      <c r="BH14" s="74"/>
-      <c r="BI14" s="74"/>
-      <c r="BJ14" s="75"/>
-      <c r="BK14" s="77"/>
-      <c r="BL14" s="73"/>
-      <c r="BM14" s="74"/>
-      <c r="BN14" s="74"/>
-      <c r="BO14" s="75"/>
-      <c r="BP14" s="77"/>
-      <c r="BQ14" s="73"/>
-      <c r="BR14" s="74"/>
-      <c r="BS14" s="74"/>
-      <c r="BT14" s="75"/>
-      <c r="BU14" s="77"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="66"/>
+      <c r="G14" s="67"/>
+      <c r="H14" s="69"/>
+      <c r="I14" s="65"/>
+      <c r="J14" s="66"/>
+      <c r="K14" s="66"/>
+      <c r="L14" s="67"/>
+      <c r="M14" s="69"/>
+      <c r="N14" s="65"/>
+      <c r="O14" s="66"/>
+      <c r="P14" s="66"/>
+      <c r="Q14" s="67"/>
+      <c r="R14" s="69"/>
+      <c r="S14" s="65"/>
+      <c r="T14" s="66"/>
+      <c r="U14" s="66"/>
+      <c r="V14" s="67"/>
+      <c r="W14" s="69"/>
+      <c r="X14" s="65"/>
+      <c r="Y14" s="66"/>
+      <c r="Z14" s="66"/>
+      <c r="AA14" s="67"/>
+      <c r="AB14" s="69"/>
+      <c r="AC14" s="65"/>
+      <c r="AD14" s="66"/>
+      <c r="AE14" s="66"/>
+      <c r="AF14" s="67"/>
+      <c r="AG14" s="69"/>
+      <c r="AH14" s="65"/>
+      <c r="AI14" s="66"/>
+      <c r="AJ14" s="66"/>
+      <c r="AK14" s="67"/>
+      <c r="AL14" s="69"/>
+      <c r="AM14" s="65"/>
+      <c r="AN14" s="66"/>
+      <c r="AO14" s="66"/>
+      <c r="AP14" s="67"/>
+      <c r="AQ14" s="69"/>
+      <c r="AR14" s="65"/>
+      <c r="AS14" s="66"/>
+      <c r="AT14" s="66"/>
+      <c r="AU14" s="67"/>
+      <c r="AV14" s="69"/>
+      <c r="AW14" s="65"/>
+      <c r="AX14" s="66"/>
+      <c r="AY14" s="66"/>
+      <c r="AZ14" s="67"/>
+      <c r="BA14" s="69"/>
+      <c r="BB14" s="65"/>
+      <c r="BC14" s="66"/>
+      <c r="BD14" s="66"/>
+      <c r="BE14" s="67"/>
+      <c r="BF14" s="69"/>
+      <c r="BG14" s="65"/>
+      <c r="BH14" s="66"/>
+      <c r="BI14" s="66"/>
+      <c r="BJ14" s="67"/>
+      <c r="BK14" s="69"/>
+      <c r="BL14" s="65"/>
+      <c r="BM14" s="66"/>
+      <c r="BN14" s="66"/>
+      <c r="BO14" s="67"/>
+      <c r="BP14" s="69"/>
+      <c r="BQ14" s="65"/>
+      <c r="BR14" s="66"/>
+      <c r="BS14" s="66"/>
+      <c r="BT14" s="67"/>
+      <c r="BU14" s="69"/>
     </row>
     <row r="15" spans="1:73" ht="81" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B15" s="57"/>
+      <c r="B15" s="49"/>
       <c r="C15" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="73"/>
-      <c r="E15" s="74"/>
-      <c r="F15" s="74"/>
-      <c r="G15" s="75"/>
-      <c r="H15" s="77"/>
-      <c r="I15" s="73"/>
-      <c r="J15" s="74"/>
-      <c r="K15" s="74"/>
-      <c r="L15" s="75"/>
-      <c r="M15" s="77"/>
-      <c r="N15" s="73"/>
-      <c r="O15" s="74"/>
-      <c r="P15" s="74"/>
-      <c r="Q15" s="75"/>
-      <c r="R15" s="77"/>
-      <c r="S15" s="73"/>
-      <c r="T15" s="74"/>
-      <c r="U15" s="74"/>
-      <c r="V15" s="75"/>
-      <c r="W15" s="77"/>
-      <c r="X15" s="73"/>
-      <c r="Y15" s="74"/>
-      <c r="Z15" s="74"/>
-      <c r="AA15" s="75"/>
-      <c r="AB15" s="77"/>
-      <c r="AC15" s="73"/>
-      <c r="AD15" s="74"/>
-      <c r="AE15" s="74"/>
-      <c r="AF15" s="75"/>
-      <c r="AG15" s="77"/>
-      <c r="AH15" s="73"/>
-      <c r="AI15" s="74"/>
-      <c r="AJ15" s="74"/>
-      <c r="AK15" s="75"/>
-      <c r="AL15" s="77"/>
-      <c r="AM15" s="73"/>
-      <c r="AN15" s="74"/>
-      <c r="AO15" s="74"/>
-      <c r="AP15" s="75"/>
-      <c r="AQ15" s="77"/>
-      <c r="AR15" s="73"/>
-      <c r="AS15" s="74"/>
-      <c r="AT15" s="74"/>
-      <c r="AU15" s="75"/>
-      <c r="AV15" s="77"/>
-      <c r="AW15" s="73"/>
-      <c r="AX15" s="74"/>
-      <c r="AY15" s="74"/>
-      <c r="AZ15" s="75"/>
-      <c r="BA15" s="77"/>
-      <c r="BB15" s="73"/>
-      <c r="BC15" s="74"/>
-      <c r="BD15" s="74"/>
-      <c r="BE15" s="75"/>
-      <c r="BF15" s="77"/>
-      <c r="BG15" s="73"/>
-      <c r="BH15" s="74"/>
-      <c r="BI15" s="74"/>
-      <c r="BJ15" s="75"/>
-      <c r="BK15" s="77"/>
-      <c r="BL15" s="73"/>
-      <c r="BM15" s="74"/>
-      <c r="BN15" s="74"/>
-      <c r="BO15" s="75"/>
-      <c r="BP15" s="77"/>
-      <c r="BQ15" s="73"/>
-      <c r="BR15" s="74"/>
-      <c r="BS15" s="74"/>
-      <c r="BT15" s="75"/>
-      <c r="BU15" s="77"/>
+      <c r="D15" s="65"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="66"/>
+      <c r="G15" s="67"/>
+      <c r="H15" s="69"/>
+      <c r="I15" s="65"/>
+      <c r="J15" s="66"/>
+      <c r="K15" s="66"/>
+      <c r="L15" s="67"/>
+      <c r="M15" s="69"/>
+      <c r="N15" s="65"/>
+      <c r="O15" s="66"/>
+      <c r="P15" s="66"/>
+      <c r="Q15" s="67"/>
+      <c r="R15" s="69"/>
+      <c r="S15" s="65"/>
+      <c r="T15" s="66"/>
+      <c r="U15" s="66"/>
+      <c r="V15" s="67"/>
+      <c r="W15" s="69"/>
+      <c r="X15" s="65"/>
+      <c r="Y15" s="66"/>
+      <c r="Z15" s="66"/>
+      <c r="AA15" s="67"/>
+      <c r="AB15" s="69"/>
+      <c r="AC15" s="65"/>
+      <c r="AD15" s="66"/>
+      <c r="AE15" s="66"/>
+      <c r="AF15" s="67"/>
+      <c r="AG15" s="69"/>
+      <c r="AH15" s="65"/>
+      <c r="AI15" s="66"/>
+      <c r="AJ15" s="66"/>
+      <c r="AK15" s="67"/>
+      <c r="AL15" s="69"/>
+      <c r="AM15" s="65"/>
+      <c r="AN15" s="66"/>
+      <c r="AO15" s="66"/>
+      <c r="AP15" s="67"/>
+      <c r="AQ15" s="69"/>
+      <c r="AR15" s="65"/>
+      <c r="AS15" s="66"/>
+      <c r="AT15" s="66"/>
+      <c r="AU15" s="67"/>
+      <c r="AV15" s="69"/>
+      <c r="AW15" s="65"/>
+      <c r="AX15" s="66"/>
+      <c r="AY15" s="66"/>
+      <c r="AZ15" s="67"/>
+      <c r="BA15" s="69"/>
+      <c r="BB15" s="65"/>
+      <c r="BC15" s="66"/>
+      <c r="BD15" s="66"/>
+      <c r="BE15" s="67"/>
+      <c r="BF15" s="69"/>
+      <c r="BG15" s="65"/>
+      <c r="BH15" s="66"/>
+      <c r="BI15" s="66"/>
+      <c r="BJ15" s="67"/>
+      <c r="BK15" s="69"/>
+      <c r="BL15" s="65"/>
+      <c r="BM15" s="66"/>
+      <c r="BN15" s="66"/>
+      <c r="BO15" s="67"/>
+      <c r="BP15" s="69"/>
+      <c r="BQ15" s="65"/>
+      <c r="BR15" s="66"/>
+      <c r="BS15" s="66"/>
+      <c r="BT15" s="67"/>
+      <c r="BU15" s="69"/>
     </row>
     <row r="16" spans="1:73" ht="91.8" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B16" s="57"/>
+      <c r="B16" s="49"/>
       <c r="C16" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D16" s="73"/>
-      <c r="E16" s="74"/>
-      <c r="F16" s="74"/>
-      <c r="G16" s="75"/>
-      <c r="H16" s="77"/>
-      <c r="I16" s="73"/>
-      <c r="J16" s="74"/>
-      <c r="K16" s="74"/>
-      <c r="L16" s="75"/>
-      <c r="M16" s="77"/>
-      <c r="N16" s="73"/>
-      <c r="O16" s="74"/>
-      <c r="P16" s="74"/>
-      <c r="Q16" s="75"/>
-      <c r="R16" s="77"/>
-      <c r="S16" s="73"/>
-      <c r="T16" s="74"/>
-      <c r="U16" s="74"/>
-      <c r="V16" s="75"/>
-      <c r="W16" s="77"/>
-      <c r="X16" s="73"/>
-      <c r="Y16" s="74"/>
-      <c r="Z16" s="74"/>
-      <c r="AA16" s="75"/>
-      <c r="AB16" s="77"/>
-      <c r="AC16" s="73"/>
-      <c r="AD16" s="74"/>
-      <c r="AE16" s="74"/>
-      <c r="AF16" s="75"/>
-      <c r="AG16" s="77"/>
-      <c r="AH16" s="73"/>
-      <c r="AI16" s="74"/>
-      <c r="AJ16" s="74"/>
-      <c r="AK16" s="75"/>
-      <c r="AL16" s="77"/>
-      <c r="AM16" s="73"/>
-      <c r="AN16" s="74"/>
-      <c r="AO16" s="74"/>
-      <c r="AP16" s="75"/>
-      <c r="AQ16" s="77"/>
-      <c r="AR16" s="73"/>
-      <c r="AS16" s="74"/>
-      <c r="AT16" s="74"/>
-      <c r="AU16" s="75"/>
-      <c r="AV16" s="77"/>
-      <c r="AW16" s="73"/>
-      <c r="AX16" s="74"/>
-      <c r="AY16" s="74"/>
-      <c r="AZ16" s="75"/>
-      <c r="BA16" s="77"/>
-      <c r="BB16" s="73"/>
-      <c r="BC16" s="74"/>
-      <c r="BD16" s="74"/>
-      <c r="BE16" s="75"/>
-      <c r="BF16" s="77"/>
-      <c r="BG16" s="73"/>
-      <c r="BH16" s="74"/>
-      <c r="BI16" s="74"/>
-      <c r="BJ16" s="75"/>
-      <c r="BK16" s="77"/>
-      <c r="BL16" s="73"/>
-      <c r="BM16" s="74"/>
-      <c r="BN16" s="74"/>
-      <c r="BO16" s="75"/>
-      <c r="BP16" s="77"/>
-      <c r="BQ16" s="73"/>
-      <c r="BR16" s="74"/>
-      <c r="BS16" s="74"/>
-      <c r="BT16" s="75"/>
-      <c r="BU16" s="77"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="66"/>
+      <c r="F16" s="66"/>
+      <c r="G16" s="67"/>
+      <c r="H16" s="69"/>
+      <c r="I16" s="65"/>
+      <c r="J16" s="66"/>
+      <c r="K16" s="66"/>
+      <c r="L16" s="67"/>
+      <c r="M16" s="69"/>
+      <c r="N16" s="65"/>
+      <c r="O16" s="66"/>
+      <c r="P16" s="66"/>
+      <c r="Q16" s="67"/>
+      <c r="R16" s="69"/>
+      <c r="S16" s="65"/>
+      <c r="T16" s="66"/>
+      <c r="U16" s="66"/>
+      <c r="V16" s="67"/>
+      <c r="W16" s="69"/>
+      <c r="X16" s="65"/>
+      <c r="Y16" s="66"/>
+      <c r="Z16" s="66"/>
+      <c r="AA16" s="67"/>
+      <c r="AB16" s="69"/>
+      <c r="AC16" s="65"/>
+      <c r="AD16" s="66"/>
+      <c r="AE16" s="66"/>
+      <c r="AF16" s="67"/>
+      <c r="AG16" s="69"/>
+      <c r="AH16" s="65"/>
+      <c r="AI16" s="66"/>
+      <c r="AJ16" s="66"/>
+      <c r="AK16" s="67"/>
+      <c r="AL16" s="69"/>
+      <c r="AM16" s="65"/>
+      <c r="AN16" s="66"/>
+      <c r="AO16" s="66"/>
+      <c r="AP16" s="67"/>
+      <c r="AQ16" s="69"/>
+      <c r="AR16" s="65"/>
+      <c r="AS16" s="66"/>
+      <c r="AT16" s="66"/>
+      <c r="AU16" s="67"/>
+      <c r="AV16" s="69"/>
+      <c r="AW16" s="65"/>
+      <c r="AX16" s="66"/>
+      <c r="AY16" s="66"/>
+      <c r="AZ16" s="67"/>
+      <c r="BA16" s="69"/>
+      <c r="BB16" s="65"/>
+      <c r="BC16" s="66"/>
+      <c r="BD16" s="66"/>
+      <c r="BE16" s="67"/>
+      <c r="BF16" s="69"/>
+      <c r="BG16" s="65"/>
+      <c r="BH16" s="66"/>
+      <c r="BI16" s="66"/>
+      <c r="BJ16" s="67"/>
+      <c r="BK16" s="69"/>
+      <c r="BL16" s="65"/>
+      <c r="BM16" s="66"/>
+      <c r="BN16" s="66"/>
+      <c r="BO16" s="67"/>
+      <c r="BP16" s="69"/>
+      <c r="BQ16" s="65"/>
+      <c r="BR16" s="66"/>
+      <c r="BS16" s="66"/>
+      <c r="BT16" s="67"/>
+      <c r="BU16" s="69"/>
     </row>
     <row r="17" spans="1:73" ht="31.35" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B17" s="58"/>
-      <c r="C17" s="24" t="s">
+      <c r="B17" s="50"/>
+      <c r="C17" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="79"/>
-      <c r="E17" s="80"/>
-      <c r="F17" s="80"/>
-      <c r="G17" s="81"/>
-      <c r="H17" s="83"/>
-      <c r="I17" s="79"/>
-      <c r="J17" s="80"/>
-      <c r="K17" s="80"/>
-      <c r="L17" s="81"/>
-      <c r="M17" s="83"/>
-      <c r="N17" s="79"/>
-      <c r="O17" s="80"/>
-      <c r="P17" s="80"/>
-      <c r="Q17" s="81"/>
-      <c r="R17" s="83"/>
-      <c r="S17" s="79"/>
-      <c r="T17" s="80"/>
-      <c r="U17" s="80"/>
-      <c r="V17" s="81"/>
-      <c r="W17" s="83"/>
-      <c r="X17" s="79"/>
-      <c r="Y17" s="80"/>
-      <c r="Z17" s="80"/>
-      <c r="AA17" s="81"/>
-      <c r="AB17" s="83"/>
-      <c r="AC17" s="79"/>
-      <c r="AD17" s="80"/>
-      <c r="AE17" s="80"/>
-      <c r="AF17" s="81"/>
-      <c r="AG17" s="83"/>
-      <c r="AH17" s="79"/>
-      <c r="AI17" s="80"/>
-      <c r="AJ17" s="80"/>
-      <c r="AK17" s="81"/>
-      <c r="AL17" s="83"/>
-      <c r="AM17" s="79"/>
-      <c r="AN17" s="80"/>
-      <c r="AO17" s="80"/>
-      <c r="AP17" s="81"/>
-      <c r="AQ17" s="83"/>
-      <c r="AR17" s="79"/>
-      <c r="AS17" s="80"/>
-      <c r="AT17" s="80"/>
-      <c r="AU17" s="81"/>
-      <c r="AV17" s="83"/>
-      <c r="AW17" s="79"/>
-      <c r="AX17" s="80"/>
-      <c r="AY17" s="80"/>
-      <c r="AZ17" s="81"/>
-      <c r="BA17" s="83"/>
-      <c r="BB17" s="79"/>
-      <c r="BC17" s="80"/>
-      <c r="BD17" s="80"/>
-      <c r="BE17" s="81"/>
-      <c r="BF17" s="83"/>
-      <c r="BG17" s="79"/>
-      <c r="BH17" s="80"/>
-      <c r="BI17" s="80"/>
-      <c r="BJ17" s="81"/>
-      <c r="BK17" s="83"/>
-      <c r="BL17" s="79"/>
-      <c r="BM17" s="80"/>
-      <c r="BN17" s="80"/>
-      <c r="BO17" s="81"/>
-      <c r="BP17" s="83"/>
-      <c r="BQ17" s="79"/>
-      <c r="BR17" s="80"/>
-      <c r="BS17" s="80"/>
-      <c r="BT17" s="81"/>
-      <c r="BU17" s="83"/>
-    </row>
-    <row r="18" spans="1:73" ht="125.2" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B18" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="41">
-        <v>5</v>
-      </c>
-      <c r="E18" s="21"/>
-      <c r="F18" s="45"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="44"/>
-      <c r="I18" s="41">
-        <v>5</v>
-      </c>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="22"/>
-      <c r="M18" s="26"/>
-      <c r="N18" s="41">
-        <v>5</v>
-      </c>
-      <c r="O18" s="21"/>
-      <c r="P18" s="21"/>
-      <c r="Q18" s="22"/>
-      <c r="R18" s="26"/>
-      <c r="S18" s="84"/>
-      <c r="T18" s="85"/>
-      <c r="U18" s="85"/>
-      <c r="V18" s="86"/>
-      <c r="W18" s="87"/>
-      <c r="X18" s="41">
-        <v>5</v>
-      </c>
-      <c r="Y18" s="21"/>
-      <c r="Z18" s="21"/>
-      <c r="AA18" s="22"/>
-      <c r="AB18" s="26"/>
-      <c r="AC18" s="41">
+      <c r="D17" s="71"/>
+      <c r="E17" s="72"/>
+      <c r="F17" s="72"/>
+      <c r="G17" s="73"/>
+      <c r="H17" s="75"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="72"/>
+      <c r="K17" s="72"/>
+      <c r="L17" s="73"/>
+      <c r="M17" s="75"/>
+      <c r="N17" s="71"/>
+      <c r="O17" s="72"/>
+      <c r="P17" s="72"/>
+      <c r="Q17" s="73"/>
+      <c r="R17" s="75"/>
+      <c r="S17" s="71"/>
+      <c r="T17" s="72"/>
+      <c r="U17" s="72"/>
+      <c r="V17" s="73"/>
+      <c r="W17" s="75"/>
+      <c r="X17" s="71"/>
+      <c r="Y17" s="72"/>
+      <c r="Z17" s="72"/>
+      <c r="AA17" s="73"/>
+      <c r="AB17" s="75"/>
+      <c r="AC17" s="71"/>
+      <c r="AD17" s="72"/>
+      <c r="AE17" s="72"/>
+      <c r="AF17" s="73"/>
+      <c r="AG17" s="75"/>
+      <c r="AH17" s="71"/>
+      <c r="AI17" s="72"/>
+      <c r="AJ17" s="72"/>
+      <c r="AK17" s="73"/>
+      <c r="AL17" s="75"/>
+      <c r="AM17" s="71"/>
+      <c r="AN17" s="72"/>
+      <c r="AO17" s="72"/>
+      <c r="AP17" s="73"/>
+      <c r="AQ17" s="75"/>
+      <c r="AR17" s="71"/>
+      <c r="AS17" s="72"/>
+      <c r="AT17" s="72"/>
+      <c r="AU17" s="73"/>
+      <c r="AV17" s="75"/>
+      <c r="AW17" s="71"/>
+      <c r="AX17" s="72"/>
+      <c r="AY17" s="72"/>
+      <c r="AZ17" s="73"/>
+      <c r="BA17" s="75"/>
+      <c r="BB17" s="71"/>
+      <c r="BC17" s="72"/>
+      <c r="BD17" s="72"/>
+      <c r="BE17" s="73"/>
+      <c r="BF17" s="75"/>
+      <c r="BG17" s="71"/>
+      <c r="BH17" s="72"/>
+      <c r="BI17" s="72"/>
+      <c r="BJ17" s="73"/>
+      <c r="BK17" s="75"/>
+      <c r="BL17" s="71"/>
+      <c r="BM17" s="72"/>
+      <c r="BN17" s="72"/>
+      <c r="BO17" s="73"/>
+      <c r="BP17" s="75"/>
+      <c r="BQ17" s="71"/>
+      <c r="BR17" s="72"/>
+      <c r="BS17" s="72"/>
+      <c r="BT17" s="73"/>
+      <c r="BU17" s="75"/>
+    </row>
+    <row r="18" spans="1:73" ht="30.75" x14ac:dyDescent="0.45">
+      <c r="B18" s="89" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="85" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="86"/>
+      <c r="E18" s="87"/>
+      <c r="F18" s="92"/>
+      <c r="G18" s="88"/>
+      <c r="H18" s="93"/>
+      <c r="I18" s="86"/>
+      <c r="J18" s="87"/>
+      <c r="K18" s="92"/>
+      <c r="L18" s="88"/>
+      <c r="M18" s="93"/>
+      <c r="N18" s="86"/>
+      <c r="O18" s="87"/>
+      <c r="P18" s="92"/>
+      <c r="Q18" s="88"/>
+      <c r="R18" s="93"/>
+      <c r="S18" s="86"/>
+      <c r="T18" s="87"/>
+      <c r="U18" s="92"/>
+      <c r="V18" s="88"/>
+      <c r="W18" s="93"/>
+      <c r="X18" s="86"/>
+      <c r="Y18" s="87"/>
+      <c r="Z18" s="92"/>
+      <c r="AA18" s="88"/>
+      <c r="AB18" s="93"/>
+      <c r="AC18" s="86"/>
+      <c r="AD18" s="87"/>
+      <c r="AE18" s="92"/>
+      <c r="AF18" s="88"/>
+      <c r="AG18" s="93"/>
+      <c r="AH18" s="86"/>
+      <c r="AI18" s="87"/>
+      <c r="AJ18" s="92"/>
+      <c r="AK18" s="88"/>
+      <c r="AL18" s="93"/>
+      <c r="AM18" s="86"/>
+      <c r="AN18" s="87"/>
+      <c r="AO18" s="92"/>
+      <c r="AP18" s="88"/>
+      <c r="AQ18" s="93"/>
+      <c r="AR18" s="86"/>
+      <c r="AS18" s="87"/>
+      <c r="AT18" s="92"/>
+      <c r="AU18" s="88"/>
+      <c r="AV18" s="93"/>
+      <c r="AW18" s="86"/>
+      <c r="AX18" s="87"/>
+      <c r="AY18" s="92"/>
+      <c r="AZ18" s="88"/>
+      <c r="BA18" s="93"/>
+      <c r="BB18" s="86"/>
+      <c r="BC18" s="87"/>
+      <c r="BD18" s="92"/>
+      <c r="BE18" s="88"/>
+      <c r="BF18" s="93"/>
+      <c r="BG18" s="86"/>
+      <c r="BH18" s="87"/>
+      <c r="BI18" s="92"/>
+      <c r="BJ18" s="88"/>
+      <c r="BK18" s="93"/>
+      <c r="BL18" s="86"/>
+      <c r="BM18" s="87"/>
+      <c r="BN18" s="92"/>
+      <c r="BO18" s="88"/>
+      <c r="BP18" s="93"/>
+      <c r="BQ18" s="86"/>
+      <c r="BR18" s="87"/>
+      <c r="BS18" s="92"/>
+      <c r="BT18" s="88"/>
+      <c r="BU18" s="93"/>
+    </row>
+    <row r="19" spans="1:73" ht="61.5" x14ac:dyDescent="0.45">
+      <c r="B19" s="51"/>
+      <c r="C19" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="76"/>
+      <c r="E19" s="77"/>
+      <c r="F19" s="94"/>
+      <c r="G19" s="78"/>
+      <c r="H19" s="95"/>
+      <c r="I19" s="76"/>
+      <c r="J19" s="77"/>
+      <c r="K19" s="94"/>
+      <c r="L19" s="78"/>
+      <c r="M19" s="95"/>
+      <c r="N19" s="76"/>
+      <c r="O19" s="77"/>
+      <c r="P19" s="94"/>
+      <c r="Q19" s="78"/>
+      <c r="R19" s="95"/>
+      <c r="S19" s="76"/>
+      <c r="T19" s="77"/>
+      <c r="U19" s="94"/>
+      <c r="V19" s="78"/>
+      <c r="W19" s="95"/>
+      <c r="X19" s="76"/>
+      <c r="Y19" s="77"/>
+      <c r="Z19" s="94"/>
+      <c r="AA19" s="78"/>
+      <c r="AB19" s="95"/>
+      <c r="AC19" s="76"/>
+      <c r="AD19" s="77"/>
+      <c r="AE19" s="94"/>
+      <c r="AF19" s="78"/>
+      <c r="AG19" s="95"/>
+      <c r="AH19" s="76"/>
+      <c r="AI19" s="77"/>
+      <c r="AJ19" s="94"/>
+      <c r="AK19" s="78"/>
+      <c r="AL19" s="95"/>
+      <c r="AM19" s="76"/>
+      <c r="AN19" s="77"/>
+      <c r="AO19" s="94"/>
+      <c r="AP19" s="78"/>
+      <c r="AQ19" s="95"/>
+      <c r="AR19" s="76"/>
+      <c r="AS19" s="77"/>
+      <c r="AT19" s="94"/>
+      <c r="AU19" s="78"/>
+      <c r="AV19" s="95"/>
+      <c r="AW19" s="76"/>
+      <c r="AX19" s="77"/>
+      <c r="AY19" s="94"/>
+      <c r="AZ19" s="78"/>
+      <c r="BA19" s="95"/>
+      <c r="BB19" s="76"/>
+      <c r="BC19" s="77"/>
+      <c r="BD19" s="94"/>
+      <c r="BE19" s="78"/>
+      <c r="BF19" s="95"/>
+      <c r="BG19" s="76"/>
+      <c r="BH19" s="77"/>
+      <c r="BI19" s="94"/>
+      <c r="BJ19" s="78"/>
+      <c r="BK19" s="95"/>
+      <c r="BL19" s="76"/>
+      <c r="BM19" s="77"/>
+      <c r="BN19" s="94"/>
+      <c r="BO19" s="78"/>
+      <c r="BP19" s="95"/>
+      <c r="BQ19" s="76"/>
+      <c r="BR19" s="77"/>
+      <c r="BS19" s="94"/>
+      <c r="BT19" s="78"/>
+      <c r="BU19" s="95"/>
+    </row>
+    <row r="20" spans="1:73" x14ac:dyDescent="0.45">
+      <c r="B20" s="90"/>
+      <c r="C20" s="79"/>
+      <c r="D20" s="96"/>
+      <c r="E20" s="80"/>
+      <c r="F20" s="80"/>
+      <c r="G20" s="81"/>
+      <c r="H20" s="82"/>
+      <c r="I20" s="96"/>
+      <c r="J20" s="80"/>
+      <c r="K20" s="80"/>
+      <c r="L20" s="81"/>
+      <c r="M20" s="82"/>
+      <c r="N20" s="96"/>
+      <c r="O20" s="80"/>
+      <c r="P20" s="80"/>
+      <c r="Q20" s="81"/>
+      <c r="R20" s="82"/>
+      <c r="S20" s="96"/>
+      <c r="T20" s="80"/>
+      <c r="U20" s="80"/>
+      <c r="V20" s="81"/>
+      <c r="W20" s="82"/>
+      <c r="X20" s="96"/>
+      <c r="Y20" s="80"/>
+      <c r="Z20" s="80"/>
+      <c r="AA20" s="81"/>
+      <c r="AB20" s="82"/>
+      <c r="AC20" s="96"/>
+      <c r="AD20" s="80"/>
+      <c r="AE20" s="80"/>
+      <c r="AF20" s="81"/>
+      <c r="AG20" s="82"/>
+      <c r="AH20" s="96"/>
+      <c r="AI20" s="80"/>
+      <c r="AJ20" s="80"/>
+      <c r="AK20" s="81"/>
+      <c r="AL20" s="82"/>
+      <c r="AM20" s="96"/>
+      <c r="AN20" s="80"/>
+      <c r="AO20" s="80"/>
+      <c r="AP20" s="81"/>
+      <c r="AQ20" s="82"/>
+      <c r="AR20" s="96"/>
+      <c r="AS20" s="80"/>
+      <c r="AT20" s="80"/>
+      <c r="AU20" s="81"/>
+      <c r="AV20" s="82"/>
+      <c r="AW20" s="96"/>
+      <c r="AX20" s="80"/>
+      <c r="AY20" s="80"/>
+      <c r="AZ20" s="81"/>
+      <c r="BA20" s="82"/>
+      <c r="BB20" s="96"/>
+      <c r="BC20" s="80"/>
+      <c r="BD20" s="80"/>
+      <c r="BE20" s="81"/>
+      <c r="BF20" s="82"/>
+      <c r="BG20" s="96"/>
+      <c r="BH20" s="80"/>
+      <c r="BI20" s="80"/>
+      <c r="BJ20" s="81"/>
+      <c r="BK20" s="82"/>
+      <c r="BL20" s="96"/>
+      <c r="BM20" s="80"/>
+      <c r="BN20" s="80"/>
+      <c r="BO20" s="81"/>
+      <c r="BP20" s="82"/>
+      <c r="BQ20" s="96"/>
+      <c r="BR20" s="80"/>
+      <c r="BS20" s="80"/>
+      <c r="BT20" s="81"/>
+      <c r="BU20" s="82"/>
+    </row>
+    <row r="21" spans="1:73" s="3" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="2"/>
+      <c r="B21" s="91" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="91"/>
+      <c r="D21" s="83">
+        <f>AVERAGE(D4:D20)</f>
         <v>0</v>
       </c>
-      <c r="AD18" s="21"/>
-      <c r="AE18" s="21"/>
-      <c r="AF18" s="22"/>
-      <c r="AG18" s="26"/>
-      <c r="AH18" s="41">
+      <c r="E21" s="83"/>
+      <c r="F21" s="83"/>
+      <c r="G21" s="83"/>
+      <c r="H21" s="84"/>
+      <c r="I21" s="83">
+        <f>AVERAGE(I4:I20)</f>
         <v>0</v>
       </c>
-      <c r="AI18" s="21"/>
-      <c r="AJ18" s="21"/>
-      <c r="AK18" s="22"/>
-      <c r="AL18" s="26"/>
-      <c r="AM18" s="41">
+      <c r="J21" s="83"/>
+      <c r="K21" s="83"/>
+      <c r="L21" s="83"/>
+      <c r="M21" s="84"/>
+      <c r="N21" s="83">
+        <f>AVERAGE(N4:N20)</f>
         <v>0</v>
       </c>
-      <c r="AN18" s="21"/>
-      <c r="AO18" s="21"/>
-      <c r="AP18" s="22"/>
-      <c r="AQ18" s="26"/>
-      <c r="AR18" s="41">
+      <c r="O21" s="83"/>
+      <c r="P21" s="83"/>
+      <c r="Q21" s="83"/>
+      <c r="R21" s="84"/>
+      <c r="S21" s="83">
+        <f>AVERAGE(S4:S20)</f>
         <v>0</v>
       </c>
-      <c r="AS18" s="21"/>
-      <c r="AT18" s="21"/>
-      <c r="AU18" s="22"/>
-      <c r="AV18" s="26"/>
-      <c r="AW18" s="41">
+      <c r="T21" s="83"/>
+      <c r="U21" s="83"/>
+      <c r="V21" s="83"/>
+      <c r="W21" s="84"/>
+      <c r="X21" s="83">
+        <f>AVERAGE(X4:X20)</f>
         <v>0</v>
       </c>
-      <c r="AX18" s="21"/>
-      <c r="AY18" s="21"/>
-      <c r="AZ18" s="22"/>
-      <c r="BA18" s="26"/>
-      <c r="BB18" s="41">
+      <c r="Y21" s="83"/>
+      <c r="Z21" s="83"/>
+      <c r="AA21" s="83"/>
+      <c r="AB21" s="84"/>
+      <c r="AC21" s="83">
+        <f>AVERAGE(AC4:AC20)</f>
         <v>0</v>
       </c>
-      <c r="BC18" s="21"/>
-      <c r="BD18" s="21"/>
-      <c r="BE18" s="22"/>
-      <c r="BF18" s="26"/>
-      <c r="BG18" s="41">
+      <c r="AD21" s="83"/>
+      <c r="AE21" s="83"/>
+      <c r="AF21" s="83"/>
+      <c r="AG21" s="84"/>
+      <c r="AH21" s="83">
+        <f>AVERAGE(AH4:AH20)</f>
         <v>0</v>
       </c>
-      <c r="BH18" s="21"/>
-      <c r="BI18" s="21"/>
-      <c r="BJ18" s="22"/>
-      <c r="BK18" s="26"/>
-      <c r="BL18" s="41">
+      <c r="AI21" s="83"/>
+      <c r="AJ21" s="83"/>
+      <c r="AK21" s="83"/>
+      <c r="AL21" s="84"/>
+      <c r="AM21" s="83">
+        <f>AVERAGE(AM4:AM20)</f>
         <v>0</v>
       </c>
-      <c r="BM18" s="21"/>
-      <c r="BN18" s="21"/>
-      <c r="BO18" s="22"/>
-      <c r="BP18" s="26"/>
-      <c r="BQ18" s="41">
+      <c r="AN21" s="83"/>
+      <c r="AO21" s="83"/>
+      <c r="AP21" s="83"/>
+      <c r="AQ21" s="84"/>
+      <c r="AR21" s="83">
+        <f>AVERAGE(AR4:AR20)</f>
         <v>0</v>
       </c>
-      <c r="BR18" s="21"/>
-      <c r="BS18" s="21"/>
-      <c r="BT18" s="22"/>
-      <c r="BU18" s="26"/>
-    </row>
-    <row r="19" spans="1:73" x14ac:dyDescent="0.45">
-      <c r="B19" s="14"/>
-      <c r="C19" s="89"/>
-      <c r="D19" s="90"/>
-      <c r="E19" s="91"/>
-      <c r="F19" s="91"/>
-      <c r="G19" s="92"/>
-      <c r="H19" s="93"/>
-      <c r="I19" s="94"/>
-      <c r="J19" s="91"/>
-      <c r="K19" s="91"/>
-      <c r="L19" s="92"/>
-      <c r="M19" s="93"/>
-      <c r="N19" s="94"/>
-      <c r="O19" s="91"/>
-      <c r="P19" s="91"/>
-      <c r="Q19" s="92"/>
-      <c r="R19" s="93"/>
-      <c r="S19" s="95"/>
-      <c r="T19" s="96"/>
-      <c r="U19" s="96"/>
-      <c r="V19" s="97"/>
-      <c r="W19" s="98"/>
-      <c r="X19" s="94"/>
-      <c r="Y19" s="91"/>
-      <c r="Z19" s="91"/>
-      <c r="AA19" s="92"/>
-      <c r="AB19" s="93"/>
-      <c r="AC19" s="94"/>
-      <c r="AD19" s="91"/>
-      <c r="AE19" s="91"/>
-      <c r="AF19" s="92"/>
-      <c r="AG19" s="93"/>
-      <c r="AH19" s="94"/>
-      <c r="AI19" s="91"/>
-      <c r="AJ19" s="91"/>
-      <c r="AK19" s="92"/>
-      <c r="AL19" s="93"/>
-      <c r="AM19" s="94"/>
-      <c r="AN19" s="91"/>
-      <c r="AO19" s="91"/>
-      <c r="AP19" s="92"/>
-      <c r="AQ19" s="93"/>
-      <c r="AR19" s="94"/>
-      <c r="AS19" s="91"/>
-      <c r="AT19" s="91"/>
-      <c r="AU19" s="92"/>
-      <c r="AV19" s="93"/>
-      <c r="AW19" s="94"/>
-      <c r="AX19" s="91"/>
-      <c r="AY19" s="91"/>
-      <c r="AZ19" s="92"/>
-      <c r="BA19" s="93"/>
-      <c r="BB19" s="94"/>
-      <c r="BC19" s="91"/>
-      <c r="BD19" s="91"/>
-      <c r="BE19" s="92"/>
-      <c r="BF19" s="93"/>
-      <c r="BG19" s="94"/>
-      <c r="BH19" s="91"/>
-      <c r="BI19" s="91"/>
-      <c r="BJ19" s="92"/>
-      <c r="BK19" s="93"/>
-      <c r="BL19" s="94"/>
-      <c r="BM19" s="91"/>
-      <c r="BN19" s="91"/>
-      <c r="BO19" s="92"/>
-      <c r="BP19" s="93"/>
-      <c r="BQ19" s="94"/>
-      <c r="BR19" s="91"/>
-      <c r="BS19" s="91"/>
-      <c r="BT19" s="92"/>
-      <c r="BU19" s="93"/>
-    </row>
-    <row r="20" spans="1:73" s="3" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="2"/>
-      <c r="B20" s="88"/>
-      <c r="C20" s="99" t="s">
-        <v>1</v>
-      </c>
-      <c r="D20" s="100">
-        <f>AVERAGE(D4:D19)</f>
-        <v>2.5</v>
-      </c>
-      <c r="E20" s="100"/>
-      <c r="F20" s="100"/>
-      <c r="G20" s="100"/>
-      <c r="H20" s="101"/>
-      <c r="I20" s="100">
-        <f>AVERAGE(I4:I19)</f>
-        <v>2.5</v>
-      </c>
-      <c r="J20" s="100"/>
-      <c r="K20" s="100"/>
-      <c r="L20" s="100"/>
-      <c r="M20" s="101"/>
-      <c r="N20" s="100">
-        <f>AVERAGE(N4:N19)</f>
-        <v>2.5</v>
-      </c>
-      <c r="O20" s="100"/>
-      <c r="P20" s="100"/>
-      <c r="Q20" s="100"/>
-      <c r="R20" s="101"/>
-      <c r="S20" s="100">
-        <f>AVERAGE(S4:S19)</f>
+      <c r="AS21" s="83"/>
+      <c r="AT21" s="83"/>
+      <c r="AU21" s="83"/>
+      <c r="AV21" s="84"/>
+      <c r="AW21" s="83">
+        <f>AVERAGE(AW4:AW20)</f>
         <v>0</v>
       </c>
-      <c r="T20" s="100"/>
-      <c r="U20" s="100"/>
-      <c r="V20" s="100"/>
-      <c r="W20" s="101"/>
-      <c r="X20" s="100">
-        <f>AVERAGE(X4:X19)</f>
-        <v>2.5</v>
-      </c>
-      <c r="Y20" s="100"/>
-      <c r="Z20" s="100"/>
-      <c r="AA20" s="100"/>
-      <c r="AB20" s="101"/>
-      <c r="AC20" s="100">
-        <f>AVERAGE(AC4:AC19)</f>
+      <c r="AX21" s="83"/>
+      <c r="AY21" s="83"/>
+      <c r="AZ21" s="83"/>
+      <c r="BA21" s="84"/>
+      <c r="BB21" s="83">
+        <f>AVERAGE(BB4:BB20)</f>
         <v>0</v>
       </c>
-      <c r="AD20" s="100"/>
-      <c r="AE20" s="100"/>
-      <c r="AF20" s="100"/>
-      <c r="AG20" s="101"/>
-      <c r="AH20" s="100">
-        <f>AVERAGE(AH4:AH19)</f>
+      <c r="BC21" s="83"/>
+      <c r="BD21" s="83"/>
+      <c r="BE21" s="83"/>
+      <c r="BF21" s="84"/>
+      <c r="BG21" s="83">
+        <f>AVERAGE(BG4:BG20)</f>
         <v>0</v>
       </c>
-      <c r="AI20" s="100"/>
-      <c r="AJ20" s="100"/>
-      <c r="AK20" s="100"/>
-      <c r="AL20" s="101"/>
-      <c r="AM20" s="100">
-        <f>AVERAGE(AM4:AM19)</f>
+      <c r="BH21" s="83"/>
+      <c r="BI21" s="83"/>
+      <c r="BJ21" s="83"/>
+      <c r="BK21" s="84"/>
+      <c r="BL21" s="83">
+        <f>AVERAGE(BL4:BL20)</f>
         <v>0</v>
       </c>
-      <c r="AN20" s="100"/>
-      <c r="AO20" s="100"/>
-      <c r="AP20" s="100"/>
-      <c r="AQ20" s="101"/>
-      <c r="AR20" s="100">
-        <f>AVERAGE(AR4:AR19)</f>
+      <c r="BM21" s="83"/>
+      <c r="BN21" s="83"/>
+      <c r="BO21" s="83"/>
+      <c r="BP21" s="84"/>
+      <c r="BQ21" s="83">
+        <f>AVERAGE(BQ4:BQ20)</f>
         <v>0</v>
       </c>
-      <c r="AS20" s="100"/>
-      <c r="AT20" s="100"/>
-      <c r="AU20" s="100"/>
-      <c r="AV20" s="101"/>
-      <c r="AW20" s="100">
-        <f>AVERAGE(AW4:AW19)</f>
-        <v>0</v>
-      </c>
-      <c r="AX20" s="100"/>
-      <c r="AY20" s="100"/>
-      <c r="AZ20" s="100"/>
-      <c r="BA20" s="101"/>
-      <c r="BB20" s="100">
-        <f>AVERAGE(BB4:BB19)</f>
-        <v>0</v>
-      </c>
-      <c r="BC20" s="100"/>
-      <c r="BD20" s="100"/>
-      <c r="BE20" s="100"/>
-      <c r="BF20" s="101"/>
-      <c r="BG20" s="100">
-        <f>AVERAGE(BG4:BG19)</f>
-        <v>0</v>
-      </c>
-      <c r="BH20" s="100"/>
-      <c r="BI20" s="100"/>
-      <c r="BJ20" s="100"/>
-      <c r="BK20" s="101"/>
-      <c r="BL20" s="100">
-        <f>AVERAGE(BL4:BL19)</f>
-        <v>0</v>
-      </c>
-      <c r="BM20" s="100"/>
-      <c r="BN20" s="100"/>
-      <c r="BO20" s="100"/>
-      <c r="BP20" s="101"/>
-      <c r="BQ20" s="100">
-        <f>AVERAGE(BQ4:BQ19)</f>
-        <v>0</v>
-      </c>
-      <c r="BR20" s="100"/>
-      <c r="BS20" s="100"/>
-      <c r="BT20" s="100"/>
-      <c r="BU20" s="101"/>
-    </row>
-    <row r="21" spans="1:73" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="C21" s="12"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="7"/>
-      <c r="O21" s="7"/>
-      <c r="P21" s="7"/>
-      <c r="Q21" s="7"/>
-      <c r="R21" s="7"/>
-      <c r="S21" s="7"/>
-      <c r="T21" s="7"/>
-      <c r="U21" s="7"/>
-      <c r="V21" s="7"/>
-      <c r="W21" s="7"/>
-      <c r="X21" s="7"/>
-      <c r="Y21" s="7"/>
-      <c r="Z21" s="7"/>
-      <c r="AA21" s="7"/>
-      <c r="AB21" s="7"/>
-      <c r="AC21" s="7"/>
-      <c r="AD21" s="7"/>
-      <c r="AE21" s="7"/>
-      <c r="AF21" s="7"/>
-      <c r="AG21" s="7"/>
-      <c r="AH21" s="7"/>
-      <c r="AI21" s="7"/>
-      <c r="AJ21" s="7"/>
-      <c r="AK21" s="7"/>
-      <c r="AL21" s="7"/>
-      <c r="AM21" s="7"/>
-      <c r="AN21" s="7"/>
-      <c r="AO21" s="7"/>
-      <c r="AP21" s="7"/>
-      <c r="AQ21" s="7"/>
-      <c r="AR21" s="7"/>
-      <c r="AS21" s="7"/>
-      <c r="AT21" s="7"/>
-      <c r="AU21" s="7"/>
-      <c r="AV21" s="7"/>
-      <c r="AW21" s="7"/>
-      <c r="AX21" s="7"/>
-      <c r="AY21" s="7"/>
-      <c r="AZ21" s="7"/>
-      <c r="BA21" s="7"/>
-      <c r="BB21" s="7"/>
-      <c r="BC21" s="7"/>
-      <c r="BD21" s="7"/>
-      <c r="BE21" s="7"/>
-      <c r="BF21" s="7"/>
-      <c r="BG21" s="7"/>
-      <c r="BH21" s="7"/>
-      <c r="BI21" s="7"/>
-      <c r="BJ21" s="7"/>
-      <c r="BK21" s="7"/>
-      <c r="BL21" s="7"/>
-      <c r="BM21" s="7"/>
-      <c r="BN21" s="7"/>
-      <c r="BO21" s="7"/>
-      <c r="BP21" s="7"/>
-      <c r="BQ21" s="7"/>
-      <c r="BR21" s="7"/>
-      <c r="BS21" s="7"/>
-      <c r="BT21" s="7"/>
-      <c r="BU21" s="7"/>
+      <c r="BR21" s="83"/>
+      <c r="BS21" s="83"/>
+      <c r="BT21" s="83"/>
+      <c r="BU21" s="84"/>
     </row>
     <row r="22" spans="1:73" s="9" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="C22" s="8"/>
+      <c r="C22" s="12"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="F22" s="7"/>
@@ -7448,17 +7438,92 @@
       <c r="BT56" s="7"/>
       <c r="BU56" s="7"/>
     </row>
+    <row r="57" spans="3:73" s="9" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="C57" s="8"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
+      <c r="F57" s="7"/>
+      <c r="G57" s="7"/>
+      <c r="H57" s="7"/>
+      <c r="I57" s="7"/>
+      <c r="J57" s="7"/>
+      <c r="K57" s="7"/>
+      <c r="L57" s="7"/>
+      <c r="M57" s="7"/>
+      <c r="N57" s="7"/>
+      <c r="O57" s="7"/>
+      <c r="P57" s="7"/>
+      <c r="Q57" s="7"/>
+      <c r="R57" s="7"/>
+      <c r="S57" s="7"/>
+      <c r="T57" s="7"/>
+      <c r="U57" s="7"/>
+      <c r="V57" s="7"/>
+      <c r="W57" s="7"/>
+      <c r="X57" s="7"/>
+      <c r="Y57" s="7"/>
+      <c r="Z57" s="7"/>
+      <c r="AA57" s="7"/>
+      <c r="AB57" s="7"/>
+      <c r="AC57" s="7"/>
+      <c r="AD57" s="7"/>
+      <c r="AE57" s="7"/>
+      <c r="AF57" s="7"/>
+      <c r="AG57" s="7"/>
+      <c r="AH57" s="7"/>
+      <c r="AI57" s="7"/>
+      <c r="AJ57" s="7"/>
+      <c r="AK57" s="7"/>
+      <c r="AL57" s="7"/>
+      <c r="AM57" s="7"/>
+      <c r="AN57" s="7"/>
+      <c r="AO57" s="7"/>
+      <c r="AP57" s="7"/>
+      <c r="AQ57" s="7"/>
+      <c r="AR57" s="7"/>
+      <c r="AS57" s="7"/>
+      <c r="AT57" s="7"/>
+      <c r="AU57" s="7"/>
+      <c r="AV57" s="7"/>
+      <c r="AW57" s="7"/>
+      <c r="AX57" s="7"/>
+      <c r="AY57" s="7"/>
+      <c r="AZ57" s="7"/>
+      <c r="BA57" s="7"/>
+      <c r="BB57" s="7"/>
+      <c r="BC57" s="7"/>
+      <c r="BD57" s="7"/>
+      <c r="BE57" s="7"/>
+      <c r="BF57" s="7"/>
+      <c r="BG57" s="7"/>
+      <c r="BH57" s="7"/>
+      <c r="BI57" s="7"/>
+      <c r="BJ57" s="7"/>
+      <c r="BK57" s="7"/>
+      <c r="BL57" s="7"/>
+      <c r="BM57" s="7"/>
+      <c r="BN57" s="7"/>
+      <c r="BO57" s="7"/>
+      <c r="BP57" s="7"/>
+      <c r="BQ57" s="7"/>
+      <c r="BR57" s="7"/>
+      <c r="BS57" s="7"/>
+      <c r="BT57" s="7"/>
+      <c r="BU57" s="7"/>
+    </row>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="34">
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="B21:C21"/>
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="B4:B10"/>
     <mergeCell ref="B11:B17"/>
     <mergeCell ref="BQ2:BU2"/>
-    <mergeCell ref="BQ20:BU20"/>
+    <mergeCell ref="BQ21:BU21"/>
     <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="I20:M20"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="I21:M21"/>
     <mergeCell ref="BG2:BK2"/>
     <mergeCell ref="BL2:BP2"/>
     <mergeCell ref="BB2:BF2"/>
@@ -7471,17 +7536,17 @@
     <mergeCell ref="AC2:AG2"/>
     <mergeCell ref="S2:W2"/>
     <mergeCell ref="N2:R2"/>
-    <mergeCell ref="N20:R20"/>
-    <mergeCell ref="S20:W20"/>
-    <mergeCell ref="X20:AB20"/>
-    <mergeCell ref="AC20:AG20"/>
-    <mergeCell ref="AH20:AL20"/>
-    <mergeCell ref="BL20:BP20"/>
-    <mergeCell ref="AM20:AQ20"/>
-    <mergeCell ref="AR20:AV20"/>
-    <mergeCell ref="AW20:BA20"/>
-    <mergeCell ref="BB20:BF20"/>
-    <mergeCell ref="BG20:BK20"/>
+    <mergeCell ref="N21:R21"/>
+    <mergeCell ref="S21:W21"/>
+    <mergeCell ref="X21:AB21"/>
+    <mergeCell ref="AC21:AG21"/>
+    <mergeCell ref="AH21:AL21"/>
+    <mergeCell ref="BL21:BP21"/>
+    <mergeCell ref="AM21:AQ21"/>
+    <mergeCell ref="AR21:AV21"/>
+    <mergeCell ref="AW21:BA21"/>
+    <mergeCell ref="BB21:BF21"/>
+    <mergeCell ref="BG21:BK21"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -7501,34 +7566,34 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="22">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B3" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="23">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B4" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="23">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B5" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="27">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B3" s="31" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="28">
-        <v>17.5</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B4" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" s="28">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B5" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="29">
+      <c r="C5" s="24">
         <f>ABS(1-(C2/C3))*100</f>
         <v>14.285714285714279</v>
       </c>

--- a/activity/M03A05/M03A05_AnalisisResultado.xlsx
+++ b/activity/M03A05/M03A05_AnalisisResultado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M03A05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84656724-F635-4E24-93D9-7E9FD946A89E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3422653F-1CFA-4390-94B6-C9E7A14AF32B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
@@ -844,51 +844,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -995,12 +950,6 @@
     <xf numFmtId="2" fontId="13" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
@@ -1017,14 +966,8 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="90"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" textRotation="90"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="14" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1043,6 +986,63 @@
     <xf numFmtId="2" fontId="14" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="32" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="16" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -1161,7 +1161,7 @@
           <c:spPr>
             <a:solidFill>
               <a:schemeClr val="bg1">
-                <a:lumMod val="65000"/>
+                <a:lumMod val="85000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:ln>
@@ -2463,25 +2463,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="F1" s="53" t="s">
+      <c r="F1" s="38" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
+      <c r="E2" s="78"/>
+      <c r="F2" s="78"/>
     </row>
     <row r="3" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
     </row>
     <row r="4" spans="2:6" ht="33" x14ac:dyDescent="0.45">
       <c r="B4" s="28" t="s">
@@ -2504,14 +2504,14 @@
       <c r="B5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="57">
+      <c r="C5" s="42">
         <v>5</v>
       </c>
       <c r="D5" s="31">
         <f>Detalle!D21*C5/5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="59"/>
+      <c r="E5" s="44"/>
       <c r="F5" s="32">
         <f>AVERAGE(D5:E5)</f>
         <v>0</v>
@@ -2521,14 +2521,14 @@
       <c r="B6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="57">
+      <c r="C6" s="42">
         <v>5</v>
       </c>
       <c r="D6" s="31">
         <f>Detalle!I21*C6/5</f>
         <v>0</v>
       </c>
-      <c r="E6" s="59"/>
+      <c r="E6" s="44"/>
       <c r="F6" s="32">
         <f t="shared" ref="F6:F18" si="0">AVERAGE(D6:E6)</f>
         <v>0</v>
@@ -2538,14 +2538,14 @@
       <c r="B7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="57">
+      <c r="C7" s="42">
         <v>5</v>
       </c>
       <c r="D7" s="31">
         <f>Detalle!N21*C7/5</f>
         <v>0</v>
       </c>
-      <c r="E7" s="59"/>
+      <c r="E7" s="44"/>
       <c r="F7" s="32">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2555,14 +2555,14 @@
       <c r="B8" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="57">
+      <c r="C8" s="42">
         <v>5</v>
       </c>
       <c r="D8" s="31">
         <f>Detalle!S21*C8/5</f>
         <v>0</v>
       </c>
-      <c r="E8" s="59"/>
+      <c r="E8" s="44"/>
       <c r="F8" s="32">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2572,14 +2572,14 @@
       <c r="B9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="57">
+      <c r="C9" s="42">
         <v>5</v>
       </c>
       <c r="D9" s="31">
         <f>Detalle!X21*C9/5</f>
         <v>0</v>
       </c>
-      <c r="E9" s="59"/>
+      <c r="E9" s="44"/>
       <c r="F9" s="32">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2589,14 +2589,14 @@
       <c r="B10" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="57">
+      <c r="C10" s="42">
         <v>5</v>
       </c>
       <c r="D10" s="31">
         <f>Detalle!AC21*C10/5</f>
         <v>0</v>
       </c>
-      <c r="E10" s="59"/>
+      <c r="E10" s="44"/>
       <c r="F10" s="32">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2606,14 +2606,14 @@
       <c r="B11" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="57">
+      <c r="C11" s="42">
         <v>5</v>
       </c>
       <c r="D11" s="31">
         <f>Detalle!AH21*C11/5</f>
         <v>0</v>
       </c>
-      <c r="E11" s="59"/>
+      <c r="E11" s="44"/>
       <c r="F11" s="32">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2623,14 +2623,14 @@
       <c r="B12" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="57">
+      <c r="C12" s="42">
         <v>5</v>
       </c>
       <c r="D12" s="31">
         <f>Detalle!AM21*C12/5</f>
         <v>0</v>
       </c>
-      <c r="E12" s="59"/>
+      <c r="E12" s="44"/>
       <c r="F12" s="32">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2640,14 +2640,14 @@
       <c r="B13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="57">
+      <c r="C13" s="42">
         <v>5</v>
       </c>
       <c r="D13" s="31">
         <f>Detalle!AR21*C13/5</f>
         <v>0</v>
       </c>
-      <c r="E13" s="59"/>
+      <c r="E13" s="44"/>
       <c r="F13" s="32">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2657,14 +2657,14 @@
       <c r="B14" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="57">
+      <c r="C14" s="42">
         <v>5</v>
       </c>
       <c r="D14" s="31">
         <f>Detalle!AW21*C14/5</f>
         <v>0</v>
       </c>
-      <c r="E14" s="59"/>
+      <c r="E14" s="44"/>
       <c r="F14" s="32">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2674,14 +2674,14 @@
       <c r="B15" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="57">
+      <c r="C15" s="42">
         <v>5</v>
       </c>
       <c r="D15" s="31">
         <f>Detalle!BB21*C15/5</f>
         <v>0</v>
       </c>
-      <c r="E15" s="59"/>
+      <c r="E15" s="44"/>
       <c r="F15" s="32">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2691,14 +2691,14 @@
       <c r="B16" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="57">
+      <c r="C16" s="42">
         <v>5</v>
       </c>
       <c r="D16" s="31">
         <f>Detalle!BG21*C16/5</f>
         <v>0</v>
       </c>
-      <c r="E16" s="59"/>
+      <c r="E16" s="44"/>
       <c r="F16" s="32">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2708,52 +2708,52 @@
       <c r="B17" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="57">
+      <c r="C17" s="42">
         <v>5</v>
       </c>
       <c r="D17" s="31">
         <f>Detalle!BL21*C17/5</f>
         <v>0</v>
       </c>
-      <c r="E17" s="59"/>
+      <c r="E17" s="44"/>
       <c r="F17" s="32">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B18" s="54" t="s">
+      <c r="B18" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="58">
+      <c r="C18" s="43">
         <v>5</v>
       </c>
-      <c r="D18" s="55">
+      <c r="D18" s="40">
         <f>Detalle!BQ21*C18/5</f>
         <v>0</v>
       </c>
-      <c r="E18" s="60"/>
-      <c r="F18" s="56">
+      <c r="E18" s="45"/>
+      <c r="F18" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="52" t="str">
+      <c r="B19" s="80" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F1,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",F1," en GitHub."))</f>
         <v>Ir a actividad M03A05 en GitHub.</v>
       </c>
-      <c r="C19" s="52"/>
-      <c r="D19" s="52"/>
-      <c r="E19" s="52"/>
-      <c r="F19" s="52"/>
+      <c r="C19" s="80"/>
+      <c r="D19" s="80"/>
+      <c r="E19" s="80"/>
+      <c r="F19" s="80"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B20" s="52"/>
-      <c r="C20" s="52"/>
-      <c r="D20" s="52"/>
-      <c r="E20" s="52"/>
-      <c r="F20" s="52"/>
+      <c r="B20" s="80"/>
+      <c r="C20" s="80"/>
+      <c r="D20" s="80"/>
+      <c r="E20" s="80"/>
+      <c r="F20" s="80"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B21" s="8"/>
@@ -2939,128 +2939,128 @@
     </row>
     <row r="2" spans="1:73" s="10" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="9"/>
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="86" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="C2" s="84" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="40" t="str">
+      <c r="D2" s="91" t="str">
         <f>Calificacion!$B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="E2" s="41"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="44" t="str">
+      <c r="E2" s="95"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="96"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="90" t="str">
         <f>Calificacion!$B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="43"/>
-      <c r="N2" s="44" t="str">
+      <c r="J2" s="91"/>
+      <c r="K2" s="91"/>
+      <c r="L2" s="91"/>
+      <c r="M2" s="92"/>
+      <c r="N2" s="90" t="str">
         <f>Calificacion!$B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="O2" s="40"/>
-      <c r="P2" s="40"/>
-      <c r="Q2" s="40"/>
-      <c r="R2" s="43"/>
-      <c r="S2" s="44" t="str">
+      <c r="O2" s="91"/>
+      <c r="P2" s="91"/>
+      <c r="Q2" s="91"/>
+      <c r="R2" s="92"/>
+      <c r="S2" s="90" t="str">
         <f>Calificacion!$B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="T2" s="40"/>
-      <c r="U2" s="40"/>
-      <c r="V2" s="40"/>
-      <c r="W2" s="43"/>
-      <c r="X2" s="44" t="str">
+      <c r="T2" s="91"/>
+      <c r="U2" s="91"/>
+      <c r="V2" s="91"/>
+      <c r="W2" s="92"/>
+      <c r="X2" s="90" t="str">
         <f>Calificacion!$B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="Y2" s="40"/>
-      <c r="Z2" s="40"/>
-      <c r="AA2" s="40"/>
-      <c r="AB2" s="43"/>
-      <c r="AC2" s="44" t="str">
+      <c r="Y2" s="91"/>
+      <c r="Z2" s="91"/>
+      <c r="AA2" s="91"/>
+      <c r="AB2" s="92"/>
+      <c r="AC2" s="90" t="str">
         <f>Calificacion!$B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="AD2" s="40"/>
-      <c r="AE2" s="40"/>
-      <c r="AF2" s="40"/>
-      <c r="AG2" s="43"/>
-      <c r="AH2" s="44" t="str">
+      <c r="AD2" s="91"/>
+      <c r="AE2" s="91"/>
+      <c r="AF2" s="91"/>
+      <c r="AG2" s="92"/>
+      <c r="AH2" s="90" t="str">
         <f>Calificacion!$B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="AI2" s="40"/>
-      <c r="AJ2" s="40"/>
-      <c r="AK2" s="40"/>
-      <c r="AL2" s="43"/>
-      <c r="AM2" s="44" t="str">
+      <c r="AI2" s="91"/>
+      <c r="AJ2" s="91"/>
+      <c r="AK2" s="91"/>
+      <c r="AL2" s="92"/>
+      <c r="AM2" s="90" t="str">
         <f>Calificacion!$B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="AN2" s="40"/>
-      <c r="AO2" s="40"/>
-      <c r="AP2" s="40"/>
-      <c r="AQ2" s="43"/>
-      <c r="AR2" s="44" t="str">
+      <c r="AN2" s="91"/>
+      <c r="AO2" s="91"/>
+      <c r="AP2" s="91"/>
+      <c r="AQ2" s="92"/>
+      <c r="AR2" s="90" t="str">
         <f>Calificacion!$B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="AS2" s="40"/>
-      <c r="AT2" s="40"/>
-      <c r="AU2" s="40"/>
-      <c r="AV2" s="43"/>
-      <c r="AW2" s="44" t="str">
+      <c r="AS2" s="91"/>
+      <c r="AT2" s="91"/>
+      <c r="AU2" s="91"/>
+      <c r="AV2" s="92"/>
+      <c r="AW2" s="90" t="str">
         <f>Calificacion!$B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="AX2" s="40"/>
-      <c r="AY2" s="40"/>
-      <c r="AZ2" s="40"/>
-      <c r="BA2" s="43"/>
-      <c r="BB2" s="44" t="str">
+      <c r="AX2" s="91"/>
+      <c r="AY2" s="91"/>
+      <c r="AZ2" s="91"/>
+      <c r="BA2" s="92"/>
+      <c r="BB2" s="90" t="str">
         <f>Calificacion!$B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="BC2" s="40"/>
-      <c r="BD2" s="40"/>
-      <c r="BE2" s="40"/>
-      <c r="BF2" s="43"/>
-      <c r="BG2" s="44" t="str">
+      <c r="BC2" s="91"/>
+      <c r="BD2" s="91"/>
+      <c r="BE2" s="91"/>
+      <c r="BF2" s="92"/>
+      <c r="BG2" s="90" t="str">
         <f>Calificacion!$B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="BH2" s="40"/>
-      <c r="BI2" s="40"/>
-      <c r="BJ2" s="40"/>
-      <c r="BK2" s="43"/>
-      <c r="BL2" s="44" t="str">
+      <c r="BH2" s="91"/>
+      <c r="BI2" s="91"/>
+      <c r="BJ2" s="91"/>
+      <c r="BK2" s="92"/>
+      <c r="BL2" s="90" t="str">
         <f>Calificacion!$B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="BM2" s="40"/>
-      <c r="BN2" s="40"/>
-      <c r="BO2" s="40"/>
-      <c r="BP2" s="43"/>
-      <c r="BQ2" s="44" t="str">
+      <c r="BM2" s="91"/>
+      <c r="BN2" s="91"/>
+      <c r="BO2" s="91"/>
+      <c r="BP2" s="92"/>
+      <c r="BQ2" s="90" t="str">
         <f>Calificacion!$B18</f>
         <v>Grupo 14</v>
       </c>
-      <c r="BR2" s="40"/>
-      <c r="BS2" s="40"/>
-      <c r="BT2" s="40"/>
-      <c r="BU2" s="43"/>
+      <c r="BR2" s="91"/>
+      <c r="BS2" s="91"/>
+      <c r="BT2" s="91"/>
+      <c r="BU2" s="92"/>
     </row>
     <row r="3" spans="1:73" ht="30.75" x14ac:dyDescent="0.45">
-      <c r="B3" s="48"/>
-      <c r="C3" s="46"/>
+      <c r="B3" s="87"/>
+      <c r="C3" s="85"/>
       <c r="D3" s="14" t="s">
         <v>1</v>
       </c>
@@ -3273,1615 +3273,1615 @@
       </c>
     </row>
     <row r="4" spans="1:73" ht="112.15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="47" t="s">
+      <c r="B4" s="86" t="s">
         <v>12</v>
       </c>
       <c r="C4" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="61">
+      <c r="D4" s="46">
         <v>0</v>
       </c>
-      <c r="E4" s="62"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="61">
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="46">
         <v>0</v>
       </c>
-      <c r="J4" s="62"/>
-      <c r="K4" s="62"/>
-      <c r="L4" s="63"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="61">
+      <c r="J4" s="47"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="48"/>
+      <c r="M4" s="49"/>
+      <c r="N4" s="46">
         <v>0</v>
       </c>
-      <c r="O4" s="62"/>
-      <c r="P4" s="62"/>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="61">
+      <c r="O4" s="47"/>
+      <c r="P4" s="47"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="49"/>
+      <c r="S4" s="46">
         <v>0</v>
       </c>
-      <c r="T4" s="62"/>
-      <c r="U4" s="62"/>
-      <c r="V4" s="63"/>
-      <c r="W4" s="64"/>
-      <c r="X4" s="61">
+      <c r="T4" s="47"/>
+      <c r="U4" s="47"/>
+      <c r="V4" s="48"/>
+      <c r="W4" s="49"/>
+      <c r="X4" s="46">
         <v>0</v>
       </c>
-      <c r="Y4" s="62"/>
-      <c r="Z4" s="62"/>
-      <c r="AA4" s="63"/>
-      <c r="AB4" s="64"/>
-      <c r="AC4" s="61">
+      <c r="Y4" s="47"/>
+      <c r="Z4" s="47"/>
+      <c r="AA4" s="48"/>
+      <c r="AB4" s="49"/>
+      <c r="AC4" s="46">
         <v>0</v>
       </c>
-      <c r="AD4" s="62"/>
-      <c r="AE4" s="62"/>
-      <c r="AF4" s="63"/>
-      <c r="AG4" s="64"/>
-      <c r="AH4" s="61">
+      <c r="AD4" s="47"/>
+      <c r="AE4" s="47"/>
+      <c r="AF4" s="48"/>
+      <c r="AG4" s="49"/>
+      <c r="AH4" s="46">
         <v>0</v>
       </c>
-      <c r="AI4" s="62"/>
-      <c r="AJ4" s="62"/>
-      <c r="AK4" s="63"/>
-      <c r="AL4" s="64"/>
-      <c r="AM4" s="61">
+      <c r="AI4" s="47"/>
+      <c r="AJ4" s="47"/>
+      <c r="AK4" s="48"/>
+      <c r="AL4" s="49"/>
+      <c r="AM4" s="46">
         <v>0</v>
       </c>
-      <c r="AN4" s="62"/>
-      <c r="AO4" s="62"/>
-      <c r="AP4" s="63"/>
-      <c r="AQ4" s="64"/>
-      <c r="AR4" s="61">
+      <c r="AN4" s="47"/>
+      <c r="AO4" s="47"/>
+      <c r="AP4" s="48"/>
+      <c r="AQ4" s="49"/>
+      <c r="AR4" s="46">
         <v>0</v>
       </c>
-      <c r="AS4" s="62"/>
-      <c r="AT4" s="62"/>
-      <c r="AU4" s="63"/>
-      <c r="AV4" s="64"/>
-      <c r="AW4" s="61">
+      <c r="AS4" s="47"/>
+      <c r="AT4" s="47"/>
+      <c r="AU4" s="48"/>
+      <c r="AV4" s="49"/>
+      <c r="AW4" s="46">
         <v>0</v>
       </c>
-      <c r="AX4" s="62"/>
-      <c r="AY4" s="62"/>
-      <c r="AZ4" s="63"/>
-      <c r="BA4" s="64"/>
-      <c r="BB4" s="61">
+      <c r="AX4" s="47"/>
+      <c r="AY4" s="47"/>
+      <c r="AZ4" s="48"/>
+      <c r="BA4" s="49"/>
+      <c r="BB4" s="46">
         <v>0</v>
       </c>
-      <c r="BC4" s="62"/>
-      <c r="BD4" s="62"/>
-      <c r="BE4" s="63"/>
-      <c r="BF4" s="64"/>
-      <c r="BG4" s="61">
+      <c r="BC4" s="47"/>
+      <c r="BD4" s="47"/>
+      <c r="BE4" s="48"/>
+      <c r="BF4" s="49"/>
+      <c r="BG4" s="46">
         <v>0</v>
       </c>
-      <c r="BH4" s="62"/>
-      <c r="BI4" s="62"/>
-      <c r="BJ4" s="63"/>
-      <c r="BK4" s="64"/>
-      <c r="BL4" s="61">
+      <c r="BH4" s="47"/>
+      <c r="BI4" s="47"/>
+      <c r="BJ4" s="48"/>
+      <c r="BK4" s="49"/>
+      <c r="BL4" s="46">
         <v>0</v>
       </c>
-      <c r="BM4" s="62"/>
-      <c r="BN4" s="62"/>
-      <c r="BO4" s="63"/>
-      <c r="BP4" s="64"/>
-      <c r="BQ4" s="61">
+      <c r="BM4" s="47"/>
+      <c r="BN4" s="47"/>
+      <c r="BO4" s="48"/>
+      <c r="BP4" s="49"/>
+      <c r="BQ4" s="46">
         <v>0</v>
       </c>
-      <c r="BR4" s="62"/>
-      <c r="BS4" s="62"/>
-      <c r="BT4" s="63"/>
-      <c r="BU4" s="64"/>
+      <c r="BR4" s="47"/>
+      <c r="BS4" s="47"/>
+      <c r="BT4" s="48"/>
+      <c r="BU4" s="49"/>
     </row>
     <row r="5" spans="1:73" ht="93.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="49"/>
+      <c r="B5" s="88"/>
       <c r="C5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="65"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="66"/>
-      <c r="K5" s="66"/>
-      <c r="L5" s="67"/>
-      <c r="M5" s="68"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="66"/>
-      <c r="P5" s="66"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="65"/>
-      <c r="T5" s="66"/>
-      <c r="U5" s="66"/>
-      <c r="V5" s="67"/>
-      <c r="W5" s="68"/>
-      <c r="X5" s="65"/>
-      <c r="Y5" s="66"/>
-      <c r="Z5" s="66"/>
-      <c r="AA5" s="67"/>
-      <c r="AB5" s="68"/>
-      <c r="AC5" s="65"/>
-      <c r="AD5" s="66"/>
-      <c r="AE5" s="66"/>
-      <c r="AF5" s="67"/>
-      <c r="AG5" s="68"/>
-      <c r="AH5" s="65"/>
-      <c r="AI5" s="66"/>
-      <c r="AJ5" s="66"/>
-      <c r="AK5" s="67"/>
-      <c r="AL5" s="68"/>
-      <c r="AM5" s="65"/>
-      <c r="AN5" s="66"/>
-      <c r="AO5" s="66"/>
-      <c r="AP5" s="67"/>
-      <c r="AQ5" s="68"/>
-      <c r="AR5" s="65"/>
-      <c r="AS5" s="66"/>
-      <c r="AT5" s="66"/>
-      <c r="AU5" s="67"/>
-      <c r="AV5" s="68"/>
-      <c r="AW5" s="65"/>
-      <c r="AX5" s="66"/>
-      <c r="AY5" s="66"/>
-      <c r="AZ5" s="67"/>
-      <c r="BA5" s="68"/>
-      <c r="BB5" s="65"/>
-      <c r="BC5" s="66"/>
-      <c r="BD5" s="66"/>
-      <c r="BE5" s="67"/>
-      <c r="BF5" s="68"/>
-      <c r="BG5" s="65"/>
-      <c r="BH5" s="66"/>
-      <c r="BI5" s="66"/>
-      <c r="BJ5" s="67"/>
-      <c r="BK5" s="68"/>
-      <c r="BL5" s="65"/>
-      <c r="BM5" s="66"/>
-      <c r="BN5" s="66"/>
-      <c r="BO5" s="67"/>
-      <c r="BP5" s="68"/>
-      <c r="BQ5" s="65"/>
-      <c r="BR5" s="66"/>
-      <c r="BS5" s="66"/>
-      <c r="BT5" s="67"/>
-      <c r="BU5" s="68"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="51"/>
+      <c r="K5" s="51"/>
+      <c r="L5" s="52"/>
+      <c r="M5" s="53"/>
+      <c r="N5" s="50"/>
+      <c r="O5" s="51"/>
+      <c r="P5" s="51"/>
+      <c r="Q5" s="52"/>
+      <c r="R5" s="53"/>
+      <c r="S5" s="50"/>
+      <c r="T5" s="51"/>
+      <c r="U5" s="51"/>
+      <c r="V5" s="52"/>
+      <c r="W5" s="53"/>
+      <c r="X5" s="50"/>
+      <c r="Y5" s="51"/>
+      <c r="Z5" s="51"/>
+      <c r="AA5" s="52"/>
+      <c r="AB5" s="53"/>
+      <c r="AC5" s="50"/>
+      <c r="AD5" s="51"/>
+      <c r="AE5" s="51"/>
+      <c r="AF5" s="52"/>
+      <c r="AG5" s="53"/>
+      <c r="AH5" s="50"/>
+      <c r="AI5" s="51"/>
+      <c r="AJ5" s="51"/>
+      <c r="AK5" s="52"/>
+      <c r="AL5" s="53"/>
+      <c r="AM5" s="50"/>
+      <c r="AN5" s="51"/>
+      <c r="AO5" s="51"/>
+      <c r="AP5" s="52"/>
+      <c r="AQ5" s="53"/>
+      <c r="AR5" s="50"/>
+      <c r="AS5" s="51"/>
+      <c r="AT5" s="51"/>
+      <c r="AU5" s="52"/>
+      <c r="AV5" s="53"/>
+      <c r="AW5" s="50"/>
+      <c r="AX5" s="51"/>
+      <c r="AY5" s="51"/>
+      <c r="AZ5" s="52"/>
+      <c r="BA5" s="53"/>
+      <c r="BB5" s="50"/>
+      <c r="BC5" s="51"/>
+      <c r="BD5" s="51"/>
+      <c r="BE5" s="52"/>
+      <c r="BF5" s="53"/>
+      <c r="BG5" s="50"/>
+      <c r="BH5" s="51"/>
+      <c r="BI5" s="51"/>
+      <c r="BJ5" s="52"/>
+      <c r="BK5" s="53"/>
+      <c r="BL5" s="50"/>
+      <c r="BM5" s="51"/>
+      <c r="BN5" s="51"/>
+      <c r="BO5" s="52"/>
+      <c r="BP5" s="53"/>
+      <c r="BQ5" s="50"/>
+      <c r="BR5" s="51"/>
+      <c r="BS5" s="51"/>
+      <c r="BT5" s="52"/>
+      <c r="BU5" s="53"/>
     </row>
     <row r="6" spans="1:73" ht="93.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="49"/>
+      <c r="B6" s="88"/>
       <c r="C6" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="65"/>
-      <c r="E6" s="66" t="s">
+      <c r="D6" s="50"/>
+      <c r="E6" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="F6" s="66" t="s">
+      <c r="F6" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="G6" s="67"/>
-      <c r="H6" s="69"/>
-      <c r="I6" s="65"/>
-      <c r="J6" s="66" t="s">
+      <c r="G6" s="52"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="50"/>
+      <c r="J6" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="K6" s="66" t="s">
+      <c r="K6" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="L6" s="67"/>
-      <c r="M6" s="69"/>
-      <c r="N6" s="65"/>
-      <c r="O6" s="66" t="s">
+      <c r="L6" s="52"/>
+      <c r="M6" s="54"/>
+      <c r="N6" s="50"/>
+      <c r="O6" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="P6" s="66" t="s">
+      <c r="P6" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="Q6" s="67"/>
-      <c r="R6" s="69"/>
-      <c r="S6" s="65"/>
-      <c r="T6" s="66" t="s">
+      <c r="Q6" s="52"/>
+      <c r="R6" s="54"/>
+      <c r="S6" s="50"/>
+      <c r="T6" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="U6" s="66" t="s">
+      <c r="U6" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="V6" s="67"/>
-      <c r="W6" s="69"/>
-      <c r="X6" s="65"/>
-      <c r="Y6" s="66" t="s">
+      <c r="V6" s="52"/>
+      <c r="W6" s="54"/>
+      <c r="X6" s="50"/>
+      <c r="Y6" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="Z6" s="66" t="s">
+      <c r="Z6" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="AA6" s="67"/>
-      <c r="AB6" s="69"/>
-      <c r="AC6" s="65"/>
-      <c r="AD6" s="66" t="s">
+      <c r="AA6" s="52"/>
+      <c r="AB6" s="54"/>
+      <c r="AC6" s="50"/>
+      <c r="AD6" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="AE6" s="66" t="s">
+      <c r="AE6" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="AF6" s="67"/>
-      <c r="AG6" s="69"/>
-      <c r="AH6" s="65"/>
-      <c r="AI6" s="66" t="s">
+      <c r="AF6" s="52"/>
+      <c r="AG6" s="54"/>
+      <c r="AH6" s="50"/>
+      <c r="AI6" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="AJ6" s="66" t="s">
+      <c r="AJ6" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="AK6" s="67"/>
-      <c r="AL6" s="69"/>
-      <c r="AM6" s="65"/>
-      <c r="AN6" s="66" t="s">
+      <c r="AK6" s="52"/>
+      <c r="AL6" s="54"/>
+      <c r="AM6" s="50"/>
+      <c r="AN6" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="AO6" s="66" t="s">
+      <c r="AO6" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="AP6" s="67"/>
-      <c r="AQ6" s="69"/>
-      <c r="AR6" s="65"/>
-      <c r="AS6" s="66" t="s">
+      <c r="AP6" s="52"/>
+      <c r="AQ6" s="54"/>
+      <c r="AR6" s="50"/>
+      <c r="AS6" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="AT6" s="66" t="s">
+      <c r="AT6" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="AU6" s="67"/>
-      <c r="AV6" s="69"/>
-      <c r="AW6" s="65"/>
-      <c r="AX6" s="66" t="s">
+      <c r="AU6" s="52"/>
+      <c r="AV6" s="54"/>
+      <c r="AW6" s="50"/>
+      <c r="AX6" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="AY6" s="66" t="s">
+      <c r="AY6" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="AZ6" s="67"/>
-      <c r="BA6" s="69"/>
-      <c r="BB6" s="65"/>
-      <c r="BC6" s="66" t="s">
+      <c r="AZ6" s="52"/>
+      <c r="BA6" s="54"/>
+      <c r="BB6" s="50"/>
+      <c r="BC6" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="BD6" s="66" t="s">
+      <c r="BD6" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="BE6" s="67"/>
-      <c r="BF6" s="69"/>
-      <c r="BG6" s="65"/>
-      <c r="BH6" s="66" t="s">
+      <c r="BE6" s="52"/>
+      <c r="BF6" s="54"/>
+      <c r="BG6" s="50"/>
+      <c r="BH6" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="BI6" s="66" t="s">
+      <c r="BI6" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="BJ6" s="67"/>
-      <c r="BK6" s="69"/>
-      <c r="BL6" s="65"/>
-      <c r="BM6" s="66" t="s">
+      <c r="BJ6" s="52"/>
+      <c r="BK6" s="54"/>
+      <c r="BL6" s="50"/>
+      <c r="BM6" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="BN6" s="66" t="s">
+      <c r="BN6" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="BO6" s="67"/>
-      <c r="BP6" s="69"/>
-      <c r="BQ6" s="65"/>
-      <c r="BR6" s="66" t="s">
+      <c r="BO6" s="52"/>
+      <c r="BP6" s="54"/>
+      <c r="BQ6" s="50"/>
+      <c r="BR6" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="BS6" s="66" t="s">
+      <c r="BS6" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="BT6" s="67"/>
-      <c r="BU6" s="69"/>
+      <c r="BT6" s="52"/>
+      <c r="BU6" s="54"/>
     </row>
     <row r="7" spans="1:73" ht="66.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B7" s="49"/>
+      <c r="B7" s="88"/>
       <c r="C7" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="65"/>
-      <c r="E7" s="66"/>
-      <c r="F7" s="70"/>
-      <c r="G7" s="67"/>
-      <c r="H7" s="68"/>
-      <c r="I7" s="65"/>
-      <c r="J7" s="66"/>
-      <c r="K7" s="70"/>
-      <c r="L7" s="67"/>
-      <c r="M7" s="68"/>
-      <c r="N7" s="65"/>
-      <c r="O7" s="66"/>
-      <c r="P7" s="70"/>
-      <c r="Q7" s="67"/>
-      <c r="R7" s="68"/>
-      <c r="S7" s="65"/>
-      <c r="T7" s="66"/>
-      <c r="U7" s="70"/>
-      <c r="V7" s="67"/>
-      <c r="W7" s="68"/>
-      <c r="X7" s="65"/>
-      <c r="Y7" s="66"/>
-      <c r="Z7" s="70"/>
-      <c r="AA7" s="67"/>
-      <c r="AB7" s="68"/>
-      <c r="AC7" s="65"/>
-      <c r="AD7" s="66"/>
-      <c r="AE7" s="70"/>
-      <c r="AF7" s="67"/>
-      <c r="AG7" s="68"/>
-      <c r="AH7" s="65"/>
-      <c r="AI7" s="66"/>
-      <c r="AJ7" s="70"/>
-      <c r="AK7" s="67"/>
-      <c r="AL7" s="68"/>
-      <c r="AM7" s="65"/>
-      <c r="AN7" s="66"/>
-      <c r="AO7" s="70"/>
-      <c r="AP7" s="67"/>
-      <c r="AQ7" s="68"/>
-      <c r="AR7" s="65"/>
-      <c r="AS7" s="66"/>
-      <c r="AT7" s="70"/>
-      <c r="AU7" s="67"/>
-      <c r="AV7" s="68"/>
-      <c r="AW7" s="65"/>
-      <c r="AX7" s="66"/>
-      <c r="AY7" s="70"/>
-      <c r="AZ7" s="67"/>
-      <c r="BA7" s="68"/>
-      <c r="BB7" s="65"/>
-      <c r="BC7" s="66"/>
-      <c r="BD7" s="70"/>
-      <c r="BE7" s="67"/>
-      <c r="BF7" s="68"/>
-      <c r="BG7" s="65"/>
-      <c r="BH7" s="66"/>
-      <c r="BI7" s="70"/>
-      <c r="BJ7" s="67"/>
-      <c r="BK7" s="68"/>
-      <c r="BL7" s="65"/>
-      <c r="BM7" s="66"/>
-      <c r="BN7" s="70"/>
-      <c r="BO7" s="67"/>
-      <c r="BP7" s="68"/>
-      <c r="BQ7" s="65"/>
-      <c r="BR7" s="66"/>
-      <c r="BS7" s="70"/>
-      <c r="BT7" s="67"/>
-      <c r="BU7" s="68"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="52"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="50"/>
+      <c r="J7" s="51"/>
+      <c r="K7" s="55"/>
+      <c r="L7" s="52"/>
+      <c r="M7" s="53"/>
+      <c r="N7" s="50"/>
+      <c r="O7" s="51"/>
+      <c r="P7" s="55"/>
+      <c r="Q7" s="52"/>
+      <c r="R7" s="53"/>
+      <c r="S7" s="50"/>
+      <c r="T7" s="51"/>
+      <c r="U7" s="55"/>
+      <c r="V7" s="52"/>
+      <c r="W7" s="53"/>
+      <c r="X7" s="50"/>
+      <c r="Y7" s="51"/>
+      <c r="Z7" s="55"/>
+      <c r="AA7" s="52"/>
+      <c r="AB7" s="53"/>
+      <c r="AC7" s="50"/>
+      <c r="AD7" s="51"/>
+      <c r="AE7" s="55"/>
+      <c r="AF7" s="52"/>
+      <c r="AG7" s="53"/>
+      <c r="AH7" s="50"/>
+      <c r="AI7" s="51"/>
+      <c r="AJ7" s="55"/>
+      <c r="AK7" s="52"/>
+      <c r="AL7" s="53"/>
+      <c r="AM7" s="50"/>
+      <c r="AN7" s="51"/>
+      <c r="AO7" s="55"/>
+      <c r="AP7" s="52"/>
+      <c r="AQ7" s="53"/>
+      <c r="AR7" s="50"/>
+      <c r="AS7" s="51"/>
+      <c r="AT7" s="55"/>
+      <c r="AU7" s="52"/>
+      <c r="AV7" s="53"/>
+      <c r="AW7" s="50"/>
+      <c r="AX7" s="51"/>
+      <c r="AY7" s="55"/>
+      <c r="AZ7" s="52"/>
+      <c r="BA7" s="53"/>
+      <c r="BB7" s="50"/>
+      <c r="BC7" s="51"/>
+      <c r="BD7" s="55"/>
+      <c r="BE7" s="52"/>
+      <c r="BF7" s="53"/>
+      <c r="BG7" s="50"/>
+      <c r="BH7" s="51"/>
+      <c r="BI7" s="55"/>
+      <c r="BJ7" s="52"/>
+      <c r="BK7" s="53"/>
+      <c r="BL7" s="50"/>
+      <c r="BM7" s="51"/>
+      <c r="BN7" s="55"/>
+      <c r="BO7" s="52"/>
+      <c r="BP7" s="53"/>
+      <c r="BQ7" s="50"/>
+      <c r="BR7" s="51"/>
+      <c r="BS7" s="55"/>
+      <c r="BT7" s="52"/>
+      <c r="BU7" s="53"/>
     </row>
     <row r="8" spans="1:73" ht="79.349999999999994" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B8" s="49"/>
+      <c r="B8" s="88"/>
       <c r="C8" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="65"/>
-      <c r="E8" s="66" t="s">
+      <c r="D8" s="50"/>
+      <c r="E8" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="66" t="s">
+      <c r="F8" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="G8" s="67"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="65"/>
-      <c r="J8" s="66" t="s">
+      <c r="G8" s="52"/>
+      <c r="H8" s="53"/>
+      <c r="I8" s="50"/>
+      <c r="J8" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="K8" s="66" t="s">
+      <c r="K8" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="L8" s="67"/>
-      <c r="M8" s="68"/>
-      <c r="N8" s="65"/>
-      <c r="O8" s="66" t="s">
+      <c r="L8" s="52"/>
+      <c r="M8" s="53"/>
+      <c r="N8" s="50"/>
+      <c r="O8" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="P8" s="66" t="s">
+      <c r="P8" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="Q8" s="67"/>
-      <c r="R8" s="68"/>
-      <c r="S8" s="65"/>
-      <c r="T8" s="66" t="s">
+      <c r="Q8" s="52"/>
+      <c r="R8" s="53"/>
+      <c r="S8" s="50"/>
+      <c r="T8" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="U8" s="66" t="s">
+      <c r="U8" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="V8" s="67"/>
-      <c r="W8" s="68"/>
-      <c r="X8" s="65"/>
-      <c r="Y8" s="66" t="s">
+      <c r="V8" s="52"/>
+      <c r="W8" s="53"/>
+      <c r="X8" s="50"/>
+      <c r="Y8" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="Z8" s="66" t="s">
+      <c r="Z8" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="AA8" s="67"/>
-      <c r="AB8" s="68"/>
-      <c r="AC8" s="65"/>
-      <c r="AD8" s="66" t="s">
+      <c r="AA8" s="52"/>
+      <c r="AB8" s="53"/>
+      <c r="AC8" s="50"/>
+      <c r="AD8" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="AE8" s="66" t="s">
+      <c r="AE8" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="AF8" s="67"/>
-      <c r="AG8" s="68"/>
-      <c r="AH8" s="65"/>
-      <c r="AI8" s="66" t="s">
+      <c r="AF8" s="52"/>
+      <c r="AG8" s="53"/>
+      <c r="AH8" s="50"/>
+      <c r="AI8" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="AJ8" s="66" t="s">
+      <c r="AJ8" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="AK8" s="67"/>
-      <c r="AL8" s="68"/>
-      <c r="AM8" s="65"/>
-      <c r="AN8" s="66" t="s">
+      <c r="AK8" s="52"/>
+      <c r="AL8" s="53"/>
+      <c r="AM8" s="50"/>
+      <c r="AN8" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="AO8" s="66" t="s">
+      <c r="AO8" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="AP8" s="67"/>
-      <c r="AQ8" s="68"/>
-      <c r="AR8" s="65"/>
-      <c r="AS8" s="66" t="s">
+      <c r="AP8" s="52"/>
+      <c r="AQ8" s="53"/>
+      <c r="AR8" s="50"/>
+      <c r="AS8" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="AT8" s="66" t="s">
+      <c r="AT8" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="AU8" s="67"/>
-      <c r="AV8" s="68"/>
-      <c r="AW8" s="65"/>
-      <c r="AX8" s="66" t="s">
+      <c r="AU8" s="52"/>
+      <c r="AV8" s="53"/>
+      <c r="AW8" s="50"/>
+      <c r="AX8" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="AY8" s="66" t="s">
+      <c r="AY8" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="AZ8" s="67"/>
-      <c r="BA8" s="68"/>
-      <c r="BB8" s="65"/>
-      <c r="BC8" s="66" t="s">
+      <c r="AZ8" s="52"/>
+      <c r="BA8" s="53"/>
+      <c r="BB8" s="50"/>
+      <c r="BC8" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="BD8" s="66" t="s">
+      <c r="BD8" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="BE8" s="67"/>
-      <c r="BF8" s="68"/>
-      <c r="BG8" s="65"/>
-      <c r="BH8" s="66" t="s">
+      <c r="BE8" s="52"/>
+      <c r="BF8" s="53"/>
+      <c r="BG8" s="50"/>
+      <c r="BH8" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="BI8" s="66" t="s">
+      <c r="BI8" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="BJ8" s="67"/>
-      <c r="BK8" s="68"/>
-      <c r="BL8" s="65"/>
-      <c r="BM8" s="66" t="s">
+      <c r="BJ8" s="52"/>
+      <c r="BK8" s="53"/>
+      <c r="BL8" s="50"/>
+      <c r="BM8" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="BN8" s="66" t="s">
+      <c r="BN8" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="BO8" s="67"/>
-      <c r="BP8" s="68"/>
-      <c r="BQ8" s="65"/>
-      <c r="BR8" s="66" t="s">
+      <c r="BO8" s="52"/>
+      <c r="BP8" s="53"/>
+      <c r="BQ8" s="50"/>
+      <c r="BR8" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="BS8" s="66" t="s">
+      <c r="BS8" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="BT8" s="67"/>
-      <c r="BU8" s="68"/>
+      <c r="BT8" s="52"/>
+      <c r="BU8" s="53"/>
     </row>
     <row r="9" spans="1:73" ht="95.2" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B9" s="49"/>
+      <c r="B9" s="88"/>
       <c r="C9" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="65"/>
-      <c r="E9" s="66" t="s">
+      <c r="D9" s="50"/>
+      <c r="E9" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="66" t="s">
+      <c r="F9" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="G9" s="67"/>
-      <c r="H9" s="68"/>
-      <c r="I9" s="65"/>
-      <c r="J9" s="66" t="s">
+      <c r="G9" s="52"/>
+      <c r="H9" s="53"/>
+      <c r="I9" s="50"/>
+      <c r="J9" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="K9" s="66" t="s">
+      <c r="K9" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="L9" s="67"/>
-      <c r="M9" s="68"/>
-      <c r="N9" s="65"/>
-      <c r="O9" s="66" t="s">
+      <c r="L9" s="52"/>
+      <c r="M9" s="53"/>
+      <c r="N9" s="50"/>
+      <c r="O9" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="P9" s="66" t="s">
+      <c r="P9" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="Q9" s="67"/>
-      <c r="R9" s="68"/>
-      <c r="S9" s="65"/>
-      <c r="T9" s="66" t="s">
+      <c r="Q9" s="52"/>
+      <c r="R9" s="53"/>
+      <c r="S9" s="50"/>
+      <c r="T9" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="U9" s="66" t="s">
+      <c r="U9" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="V9" s="67"/>
-      <c r="W9" s="68"/>
-      <c r="X9" s="65"/>
-      <c r="Y9" s="66" t="s">
+      <c r="V9" s="52"/>
+      <c r="W9" s="53"/>
+      <c r="X9" s="50"/>
+      <c r="Y9" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="Z9" s="66" t="s">
+      <c r="Z9" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="AA9" s="67"/>
-      <c r="AB9" s="68"/>
-      <c r="AC9" s="65"/>
-      <c r="AD9" s="66" t="s">
+      <c r="AA9" s="52"/>
+      <c r="AB9" s="53"/>
+      <c r="AC9" s="50"/>
+      <c r="AD9" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="AE9" s="66" t="s">
+      <c r="AE9" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="AF9" s="67"/>
-      <c r="AG9" s="68"/>
-      <c r="AH9" s="65"/>
-      <c r="AI9" s="66" t="s">
+      <c r="AF9" s="52"/>
+      <c r="AG9" s="53"/>
+      <c r="AH9" s="50"/>
+      <c r="AI9" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="AJ9" s="66" t="s">
+      <c r="AJ9" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="AK9" s="67"/>
-      <c r="AL9" s="68"/>
-      <c r="AM9" s="65"/>
-      <c r="AN9" s="66" t="s">
+      <c r="AK9" s="52"/>
+      <c r="AL9" s="53"/>
+      <c r="AM9" s="50"/>
+      <c r="AN9" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="AO9" s="66" t="s">
+      <c r="AO9" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="AP9" s="67"/>
-      <c r="AQ9" s="68"/>
-      <c r="AR9" s="65"/>
-      <c r="AS9" s="66" t="s">
+      <c r="AP9" s="52"/>
+      <c r="AQ9" s="53"/>
+      <c r="AR9" s="50"/>
+      <c r="AS9" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="AT9" s="66" t="s">
+      <c r="AT9" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="AU9" s="67"/>
-      <c r="AV9" s="68"/>
-      <c r="AW9" s="65"/>
-      <c r="AX9" s="66" t="s">
+      <c r="AU9" s="52"/>
+      <c r="AV9" s="53"/>
+      <c r="AW9" s="50"/>
+      <c r="AX9" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="AY9" s="66" t="s">
+      <c r="AY9" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="AZ9" s="67"/>
-      <c r="BA9" s="68"/>
-      <c r="BB9" s="65"/>
-      <c r="BC9" s="66" t="s">
+      <c r="AZ9" s="52"/>
+      <c r="BA9" s="53"/>
+      <c r="BB9" s="50"/>
+      <c r="BC9" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="BD9" s="66" t="s">
+      <c r="BD9" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="BE9" s="67"/>
-      <c r="BF9" s="68"/>
-      <c r="BG9" s="65"/>
-      <c r="BH9" s="66" t="s">
+      <c r="BE9" s="52"/>
+      <c r="BF9" s="53"/>
+      <c r="BG9" s="50"/>
+      <c r="BH9" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="BI9" s="66" t="s">
+      <c r="BI9" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="BJ9" s="67"/>
-      <c r="BK9" s="68"/>
-      <c r="BL9" s="65"/>
-      <c r="BM9" s="66" t="s">
+      <c r="BJ9" s="52"/>
+      <c r="BK9" s="53"/>
+      <c r="BL9" s="50"/>
+      <c r="BM9" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="BN9" s="66" t="s">
+      <c r="BN9" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="BO9" s="67"/>
-      <c r="BP9" s="68"/>
-      <c r="BQ9" s="65"/>
-      <c r="BR9" s="66" t="s">
+      <c r="BO9" s="52"/>
+      <c r="BP9" s="53"/>
+      <c r="BQ9" s="50"/>
+      <c r="BR9" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="BS9" s="66" t="s">
+      <c r="BS9" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="BT9" s="67"/>
-      <c r="BU9" s="68"/>
+      <c r="BT9" s="52"/>
+      <c r="BU9" s="53"/>
     </row>
     <row r="10" spans="1:73" ht="70.900000000000006" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="50"/>
+      <c r="B10" s="89"/>
       <c r="C10" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="71"/>
-      <c r="E10" s="72"/>
-      <c r="F10" s="72"/>
-      <c r="G10" s="73"/>
-      <c r="H10" s="74"/>
-      <c r="I10" s="71"/>
-      <c r="J10" s="72"/>
-      <c r="K10" s="72"/>
-      <c r="L10" s="73"/>
-      <c r="M10" s="74"/>
-      <c r="N10" s="71"/>
-      <c r="O10" s="72"/>
-      <c r="P10" s="72"/>
-      <c r="Q10" s="73"/>
-      <c r="R10" s="74"/>
-      <c r="S10" s="71"/>
-      <c r="T10" s="72"/>
-      <c r="U10" s="72"/>
-      <c r="V10" s="73"/>
-      <c r="W10" s="74"/>
-      <c r="X10" s="71"/>
-      <c r="Y10" s="72"/>
-      <c r="Z10" s="72"/>
-      <c r="AA10" s="73"/>
-      <c r="AB10" s="74"/>
-      <c r="AC10" s="71"/>
-      <c r="AD10" s="72"/>
-      <c r="AE10" s="72"/>
-      <c r="AF10" s="73"/>
-      <c r="AG10" s="74"/>
-      <c r="AH10" s="71"/>
-      <c r="AI10" s="72"/>
-      <c r="AJ10" s="72"/>
-      <c r="AK10" s="73"/>
-      <c r="AL10" s="74"/>
-      <c r="AM10" s="71"/>
-      <c r="AN10" s="72"/>
-      <c r="AO10" s="72"/>
-      <c r="AP10" s="73"/>
-      <c r="AQ10" s="74"/>
-      <c r="AR10" s="71"/>
-      <c r="AS10" s="72"/>
-      <c r="AT10" s="72"/>
-      <c r="AU10" s="73"/>
-      <c r="AV10" s="74"/>
-      <c r="AW10" s="71"/>
-      <c r="AX10" s="72"/>
-      <c r="AY10" s="72"/>
-      <c r="AZ10" s="73"/>
-      <c r="BA10" s="74"/>
-      <c r="BB10" s="71"/>
-      <c r="BC10" s="72"/>
-      <c r="BD10" s="72"/>
-      <c r="BE10" s="73"/>
-      <c r="BF10" s="74"/>
-      <c r="BG10" s="71"/>
-      <c r="BH10" s="72"/>
-      <c r="BI10" s="72"/>
-      <c r="BJ10" s="73"/>
-      <c r="BK10" s="74"/>
-      <c r="BL10" s="71"/>
-      <c r="BM10" s="72"/>
-      <c r="BN10" s="72"/>
-      <c r="BO10" s="73"/>
-      <c r="BP10" s="74"/>
-      <c r="BQ10" s="71"/>
-      <c r="BR10" s="72"/>
-      <c r="BS10" s="72"/>
-      <c r="BT10" s="73"/>
-      <c r="BU10" s="74"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="58"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="57"/>
+      <c r="K10" s="57"/>
+      <c r="L10" s="58"/>
+      <c r="M10" s="59"/>
+      <c r="N10" s="56"/>
+      <c r="O10" s="57"/>
+      <c r="P10" s="57"/>
+      <c r="Q10" s="58"/>
+      <c r="R10" s="59"/>
+      <c r="S10" s="56"/>
+      <c r="T10" s="57"/>
+      <c r="U10" s="57"/>
+      <c r="V10" s="58"/>
+      <c r="W10" s="59"/>
+      <c r="X10" s="56"/>
+      <c r="Y10" s="57"/>
+      <c r="Z10" s="57"/>
+      <c r="AA10" s="58"/>
+      <c r="AB10" s="59"/>
+      <c r="AC10" s="56"/>
+      <c r="AD10" s="57"/>
+      <c r="AE10" s="57"/>
+      <c r="AF10" s="58"/>
+      <c r="AG10" s="59"/>
+      <c r="AH10" s="56"/>
+      <c r="AI10" s="57"/>
+      <c r="AJ10" s="57"/>
+      <c r="AK10" s="58"/>
+      <c r="AL10" s="59"/>
+      <c r="AM10" s="56"/>
+      <c r="AN10" s="57"/>
+      <c r="AO10" s="57"/>
+      <c r="AP10" s="58"/>
+      <c r="AQ10" s="59"/>
+      <c r="AR10" s="56"/>
+      <c r="AS10" s="57"/>
+      <c r="AT10" s="57"/>
+      <c r="AU10" s="58"/>
+      <c r="AV10" s="59"/>
+      <c r="AW10" s="56"/>
+      <c r="AX10" s="57"/>
+      <c r="AY10" s="57"/>
+      <c r="AZ10" s="58"/>
+      <c r="BA10" s="59"/>
+      <c r="BB10" s="56"/>
+      <c r="BC10" s="57"/>
+      <c r="BD10" s="57"/>
+      <c r="BE10" s="58"/>
+      <c r="BF10" s="59"/>
+      <c r="BG10" s="56"/>
+      <c r="BH10" s="57"/>
+      <c r="BI10" s="57"/>
+      <c r="BJ10" s="58"/>
+      <c r="BK10" s="59"/>
+      <c r="BL10" s="56"/>
+      <c r="BM10" s="57"/>
+      <c r="BN10" s="57"/>
+      <c r="BO10" s="58"/>
+      <c r="BP10" s="59"/>
+      <c r="BQ10" s="56"/>
+      <c r="BR10" s="57"/>
+      <c r="BS10" s="57"/>
+      <c r="BT10" s="58"/>
+      <c r="BU10" s="59"/>
     </row>
     <row r="11" spans="1:73" ht="48" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B11" s="47" t="s">
+      <c r="B11" s="86" t="s">
         <v>24</v>
       </c>
       <c r="C11" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="D11" s="61"/>
-      <c r="E11" s="62"/>
-      <c r="F11" s="62"/>
-      <c r="G11" s="63"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="61"/>
-      <c r="J11" s="62"/>
-      <c r="K11" s="62"/>
-      <c r="L11" s="63"/>
-      <c r="M11" s="64"/>
-      <c r="N11" s="61"/>
-      <c r="O11" s="62"/>
-      <c r="P11" s="62"/>
-      <c r="Q11" s="63"/>
-      <c r="R11" s="64"/>
-      <c r="S11" s="61"/>
-      <c r="T11" s="62"/>
-      <c r="U11" s="62"/>
-      <c r="V11" s="63"/>
-      <c r="W11" s="64"/>
-      <c r="X11" s="61"/>
-      <c r="Y11" s="62"/>
-      <c r="Z11" s="62"/>
-      <c r="AA11" s="63"/>
-      <c r="AB11" s="64"/>
-      <c r="AC11" s="61"/>
-      <c r="AD11" s="62"/>
-      <c r="AE11" s="62"/>
-      <c r="AF11" s="63"/>
-      <c r="AG11" s="64"/>
-      <c r="AH11" s="61"/>
-      <c r="AI11" s="62"/>
-      <c r="AJ11" s="62"/>
-      <c r="AK11" s="63"/>
-      <c r="AL11" s="64"/>
-      <c r="AM11" s="61"/>
-      <c r="AN11" s="62"/>
-      <c r="AO11" s="62"/>
-      <c r="AP11" s="63"/>
-      <c r="AQ11" s="64"/>
-      <c r="AR11" s="61"/>
-      <c r="AS11" s="62"/>
-      <c r="AT11" s="62"/>
-      <c r="AU11" s="63"/>
-      <c r="AV11" s="64"/>
-      <c r="AW11" s="61"/>
-      <c r="AX11" s="62"/>
-      <c r="AY11" s="62"/>
-      <c r="AZ11" s="63"/>
-      <c r="BA11" s="64"/>
-      <c r="BB11" s="61"/>
-      <c r="BC11" s="62"/>
-      <c r="BD11" s="62"/>
-      <c r="BE11" s="63"/>
-      <c r="BF11" s="64"/>
-      <c r="BG11" s="61"/>
-      <c r="BH11" s="62"/>
-      <c r="BI11" s="62"/>
-      <c r="BJ11" s="63"/>
-      <c r="BK11" s="64"/>
-      <c r="BL11" s="61"/>
-      <c r="BM11" s="62"/>
-      <c r="BN11" s="62"/>
-      <c r="BO11" s="63"/>
-      <c r="BP11" s="64"/>
-      <c r="BQ11" s="61"/>
-      <c r="BR11" s="62"/>
-      <c r="BS11" s="62"/>
-      <c r="BT11" s="63"/>
-      <c r="BU11" s="64"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="49"/>
+      <c r="I11" s="46"/>
+      <c r="J11" s="47"/>
+      <c r="K11" s="47"/>
+      <c r="L11" s="48"/>
+      <c r="M11" s="49"/>
+      <c r="N11" s="46"/>
+      <c r="O11" s="47"/>
+      <c r="P11" s="47"/>
+      <c r="Q11" s="48"/>
+      <c r="R11" s="49"/>
+      <c r="S11" s="46"/>
+      <c r="T11" s="47"/>
+      <c r="U11" s="47"/>
+      <c r="V11" s="48"/>
+      <c r="W11" s="49"/>
+      <c r="X11" s="46"/>
+      <c r="Y11" s="47"/>
+      <c r="Z11" s="47"/>
+      <c r="AA11" s="48"/>
+      <c r="AB11" s="49"/>
+      <c r="AC11" s="46"/>
+      <c r="AD11" s="47"/>
+      <c r="AE11" s="47"/>
+      <c r="AF11" s="48"/>
+      <c r="AG11" s="49"/>
+      <c r="AH11" s="46"/>
+      <c r="AI11" s="47"/>
+      <c r="AJ11" s="47"/>
+      <c r="AK11" s="48"/>
+      <c r="AL11" s="49"/>
+      <c r="AM11" s="46"/>
+      <c r="AN11" s="47"/>
+      <c r="AO11" s="47"/>
+      <c r="AP11" s="48"/>
+      <c r="AQ11" s="49"/>
+      <c r="AR11" s="46"/>
+      <c r="AS11" s="47"/>
+      <c r="AT11" s="47"/>
+      <c r="AU11" s="48"/>
+      <c r="AV11" s="49"/>
+      <c r="AW11" s="46"/>
+      <c r="AX11" s="47"/>
+      <c r="AY11" s="47"/>
+      <c r="AZ11" s="48"/>
+      <c r="BA11" s="49"/>
+      <c r="BB11" s="46"/>
+      <c r="BC11" s="47"/>
+      <c r="BD11" s="47"/>
+      <c r="BE11" s="48"/>
+      <c r="BF11" s="49"/>
+      <c r="BG11" s="46"/>
+      <c r="BH11" s="47"/>
+      <c r="BI11" s="47"/>
+      <c r="BJ11" s="48"/>
+      <c r="BK11" s="49"/>
+      <c r="BL11" s="46"/>
+      <c r="BM11" s="47"/>
+      <c r="BN11" s="47"/>
+      <c r="BO11" s="48"/>
+      <c r="BP11" s="49"/>
+      <c r="BQ11" s="46"/>
+      <c r="BR11" s="47"/>
+      <c r="BS11" s="47"/>
+      <c r="BT11" s="48"/>
+      <c r="BU11" s="49"/>
     </row>
     <row r="12" spans="1:73" ht="93.95" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="51"/>
+      <c r="B12" s="82"/>
       <c r="C12" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="65"/>
-      <c r="E12" s="66"/>
-      <c r="F12" s="66"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="68"/>
-      <c r="I12" s="65"/>
-      <c r="J12" s="66"/>
-      <c r="K12" s="66"/>
-      <c r="L12" s="67"/>
-      <c r="M12" s="68"/>
-      <c r="N12" s="65"/>
-      <c r="O12" s="66"/>
-      <c r="P12" s="66"/>
-      <c r="Q12" s="67"/>
-      <c r="R12" s="68"/>
-      <c r="S12" s="65"/>
-      <c r="T12" s="66"/>
-      <c r="U12" s="66"/>
-      <c r="V12" s="67"/>
-      <c r="W12" s="68"/>
-      <c r="X12" s="65"/>
-      <c r="Y12" s="66"/>
-      <c r="Z12" s="66"/>
-      <c r="AA12" s="67"/>
-      <c r="AB12" s="68"/>
-      <c r="AC12" s="65"/>
-      <c r="AD12" s="66"/>
-      <c r="AE12" s="66"/>
-      <c r="AF12" s="67"/>
-      <c r="AG12" s="68"/>
-      <c r="AH12" s="65"/>
-      <c r="AI12" s="66"/>
-      <c r="AJ12" s="66"/>
-      <c r="AK12" s="67"/>
-      <c r="AL12" s="68"/>
-      <c r="AM12" s="65"/>
-      <c r="AN12" s="66"/>
-      <c r="AO12" s="66"/>
-      <c r="AP12" s="67"/>
-      <c r="AQ12" s="68"/>
-      <c r="AR12" s="65"/>
-      <c r="AS12" s="66"/>
-      <c r="AT12" s="66"/>
-      <c r="AU12" s="67"/>
-      <c r="AV12" s="68"/>
-      <c r="AW12" s="65"/>
-      <c r="AX12" s="66"/>
-      <c r="AY12" s="66"/>
-      <c r="AZ12" s="67"/>
-      <c r="BA12" s="68"/>
-      <c r="BB12" s="65"/>
-      <c r="BC12" s="66"/>
-      <c r="BD12" s="66"/>
-      <c r="BE12" s="67"/>
-      <c r="BF12" s="68"/>
-      <c r="BG12" s="65"/>
-      <c r="BH12" s="66"/>
-      <c r="BI12" s="66"/>
-      <c r="BJ12" s="67"/>
-      <c r="BK12" s="68"/>
-      <c r="BL12" s="65"/>
-      <c r="BM12" s="66"/>
-      <c r="BN12" s="66"/>
-      <c r="BO12" s="67"/>
-      <c r="BP12" s="68"/>
-      <c r="BQ12" s="65"/>
-      <c r="BR12" s="66"/>
-      <c r="BS12" s="66"/>
-      <c r="BT12" s="67"/>
-      <c r="BU12" s="68"/>
+      <c r="D12" s="50"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="53"/>
+      <c r="I12" s="50"/>
+      <c r="J12" s="51"/>
+      <c r="K12" s="51"/>
+      <c r="L12" s="52"/>
+      <c r="M12" s="53"/>
+      <c r="N12" s="50"/>
+      <c r="O12" s="51"/>
+      <c r="P12" s="51"/>
+      <c r="Q12" s="52"/>
+      <c r="R12" s="53"/>
+      <c r="S12" s="50"/>
+      <c r="T12" s="51"/>
+      <c r="U12" s="51"/>
+      <c r="V12" s="52"/>
+      <c r="W12" s="53"/>
+      <c r="X12" s="50"/>
+      <c r="Y12" s="51"/>
+      <c r="Z12" s="51"/>
+      <c r="AA12" s="52"/>
+      <c r="AB12" s="53"/>
+      <c r="AC12" s="50"/>
+      <c r="AD12" s="51"/>
+      <c r="AE12" s="51"/>
+      <c r="AF12" s="52"/>
+      <c r="AG12" s="53"/>
+      <c r="AH12" s="50"/>
+      <c r="AI12" s="51"/>
+      <c r="AJ12" s="51"/>
+      <c r="AK12" s="52"/>
+      <c r="AL12" s="53"/>
+      <c r="AM12" s="50"/>
+      <c r="AN12" s="51"/>
+      <c r="AO12" s="51"/>
+      <c r="AP12" s="52"/>
+      <c r="AQ12" s="53"/>
+      <c r="AR12" s="50"/>
+      <c r="AS12" s="51"/>
+      <c r="AT12" s="51"/>
+      <c r="AU12" s="52"/>
+      <c r="AV12" s="53"/>
+      <c r="AW12" s="50"/>
+      <c r="AX12" s="51"/>
+      <c r="AY12" s="51"/>
+      <c r="AZ12" s="52"/>
+      <c r="BA12" s="53"/>
+      <c r="BB12" s="50"/>
+      <c r="BC12" s="51"/>
+      <c r="BD12" s="51"/>
+      <c r="BE12" s="52"/>
+      <c r="BF12" s="53"/>
+      <c r="BG12" s="50"/>
+      <c r="BH12" s="51"/>
+      <c r="BI12" s="51"/>
+      <c r="BJ12" s="52"/>
+      <c r="BK12" s="53"/>
+      <c r="BL12" s="50"/>
+      <c r="BM12" s="51"/>
+      <c r="BN12" s="51"/>
+      <c r="BO12" s="52"/>
+      <c r="BP12" s="53"/>
+      <c r="BQ12" s="50"/>
+      <c r="BR12" s="51"/>
+      <c r="BS12" s="51"/>
+      <c r="BT12" s="52"/>
+      <c r="BU12" s="53"/>
     </row>
     <row r="13" spans="1:73" ht="49.35" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B13" s="49"/>
+      <c r="B13" s="88"/>
       <c r="C13" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="65"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="66"/>
-      <c r="G13" s="67"/>
-      <c r="H13" s="69"/>
-      <c r="I13" s="65"/>
-      <c r="J13" s="66"/>
-      <c r="K13" s="66"/>
-      <c r="L13" s="67"/>
-      <c r="M13" s="69"/>
-      <c r="N13" s="65"/>
-      <c r="O13" s="66"/>
-      <c r="P13" s="66"/>
-      <c r="Q13" s="67"/>
-      <c r="R13" s="69"/>
-      <c r="S13" s="65"/>
-      <c r="T13" s="66"/>
-      <c r="U13" s="66"/>
-      <c r="V13" s="67"/>
-      <c r="W13" s="69"/>
-      <c r="X13" s="65"/>
-      <c r="Y13" s="66"/>
-      <c r="Z13" s="66"/>
-      <c r="AA13" s="67"/>
-      <c r="AB13" s="69"/>
-      <c r="AC13" s="65"/>
-      <c r="AD13" s="66"/>
-      <c r="AE13" s="66"/>
-      <c r="AF13" s="67"/>
-      <c r="AG13" s="69"/>
-      <c r="AH13" s="65"/>
-      <c r="AI13" s="66"/>
-      <c r="AJ13" s="66"/>
-      <c r="AK13" s="67"/>
-      <c r="AL13" s="69"/>
-      <c r="AM13" s="65"/>
-      <c r="AN13" s="66"/>
-      <c r="AO13" s="66"/>
-      <c r="AP13" s="67"/>
-      <c r="AQ13" s="69"/>
-      <c r="AR13" s="65"/>
-      <c r="AS13" s="66"/>
-      <c r="AT13" s="66"/>
-      <c r="AU13" s="67"/>
-      <c r="AV13" s="69"/>
-      <c r="AW13" s="65"/>
-      <c r="AX13" s="66"/>
-      <c r="AY13" s="66"/>
-      <c r="AZ13" s="67"/>
-      <c r="BA13" s="69"/>
-      <c r="BB13" s="65"/>
-      <c r="BC13" s="66"/>
-      <c r="BD13" s="66"/>
-      <c r="BE13" s="67"/>
-      <c r="BF13" s="69"/>
-      <c r="BG13" s="65"/>
-      <c r="BH13" s="66"/>
-      <c r="BI13" s="66"/>
-      <c r="BJ13" s="67"/>
-      <c r="BK13" s="69"/>
-      <c r="BL13" s="65"/>
-      <c r="BM13" s="66"/>
-      <c r="BN13" s="66"/>
-      <c r="BO13" s="67"/>
-      <c r="BP13" s="69"/>
-      <c r="BQ13" s="65"/>
-      <c r="BR13" s="66"/>
-      <c r="BS13" s="66"/>
-      <c r="BT13" s="67"/>
-      <c r="BU13" s="69"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="54"/>
+      <c r="I13" s="50"/>
+      <c r="J13" s="51"/>
+      <c r="K13" s="51"/>
+      <c r="L13" s="52"/>
+      <c r="M13" s="54"/>
+      <c r="N13" s="50"/>
+      <c r="O13" s="51"/>
+      <c r="P13" s="51"/>
+      <c r="Q13" s="52"/>
+      <c r="R13" s="54"/>
+      <c r="S13" s="50"/>
+      <c r="T13" s="51"/>
+      <c r="U13" s="51"/>
+      <c r="V13" s="52"/>
+      <c r="W13" s="54"/>
+      <c r="X13" s="50"/>
+      <c r="Y13" s="51"/>
+      <c r="Z13" s="51"/>
+      <c r="AA13" s="52"/>
+      <c r="AB13" s="54"/>
+      <c r="AC13" s="50"/>
+      <c r="AD13" s="51"/>
+      <c r="AE13" s="51"/>
+      <c r="AF13" s="52"/>
+      <c r="AG13" s="54"/>
+      <c r="AH13" s="50"/>
+      <c r="AI13" s="51"/>
+      <c r="AJ13" s="51"/>
+      <c r="AK13" s="52"/>
+      <c r="AL13" s="54"/>
+      <c r="AM13" s="50"/>
+      <c r="AN13" s="51"/>
+      <c r="AO13" s="51"/>
+      <c r="AP13" s="52"/>
+      <c r="AQ13" s="54"/>
+      <c r="AR13" s="50"/>
+      <c r="AS13" s="51"/>
+      <c r="AT13" s="51"/>
+      <c r="AU13" s="52"/>
+      <c r="AV13" s="54"/>
+      <c r="AW13" s="50"/>
+      <c r="AX13" s="51"/>
+      <c r="AY13" s="51"/>
+      <c r="AZ13" s="52"/>
+      <c r="BA13" s="54"/>
+      <c r="BB13" s="50"/>
+      <c r="BC13" s="51"/>
+      <c r="BD13" s="51"/>
+      <c r="BE13" s="52"/>
+      <c r="BF13" s="54"/>
+      <c r="BG13" s="50"/>
+      <c r="BH13" s="51"/>
+      <c r="BI13" s="51"/>
+      <c r="BJ13" s="52"/>
+      <c r="BK13" s="54"/>
+      <c r="BL13" s="50"/>
+      <c r="BM13" s="51"/>
+      <c r="BN13" s="51"/>
+      <c r="BO13" s="52"/>
+      <c r="BP13" s="54"/>
+      <c r="BQ13" s="50"/>
+      <c r="BR13" s="51"/>
+      <c r="BS13" s="51"/>
+      <c r="BT13" s="52"/>
+      <c r="BU13" s="54"/>
     </row>
     <row r="14" spans="1:73" ht="62.2" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B14" s="49"/>
+      <c r="B14" s="88"/>
       <c r="C14" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="65"/>
-      <c r="E14" s="66"/>
-      <c r="F14" s="66"/>
-      <c r="G14" s="67"/>
-      <c r="H14" s="69"/>
-      <c r="I14" s="65"/>
-      <c r="J14" s="66"/>
-      <c r="K14" s="66"/>
-      <c r="L14" s="67"/>
-      <c r="M14" s="69"/>
-      <c r="N14" s="65"/>
-      <c r="O14" s="66"/>
-      <c r="P14" s="66"/>
-      <c r="Q14" s="67"/>
-      <c r="R14" s="69"/>
-      <c r="S14" s="65"/>
-      <c r="T14" s="66"/>
-      <c r="U14" s="66"/>
-      <c r="V14" s="67"/>
-      <c r="W14" s="69"/>
-      <c r="X14" s="65"/>
-      <c r="Y14" s="66"/>
-      <c r="Z14" s="66"/>
-      <c r="AA14" s="67"/>
-      <c r="AB14" s="69"/>
-      <c r="AC14" s="65"/>
-      <c r="AD14" s="66"/>
-      <c r="AE14" s="66"/>
-      <c r="AF14" s="67"/>
-      <c r="AG14" s="69"/>
-      <c r="AH14" s="65"/>
-      <c r="AI14" s="66"/>
-      <c r="AJ14" s="66"/>
-      <c r="AK14" s="67"/>
-      <c r="AL14" s="69"/>
-      <c r="AM14" s="65"/>
-      <c r="AN14" s="66"/>
-      <c r="AO14" s="66"/>
-      <c r="AP14" s="67"/>
-      <c r="AQ14" s="69"/>
-      <c r="AR14" s="65"/>
-      <c r="AS14" s="66"/>
-      <c r="AT14" s="66"/>
-      <c r="AU14" s="67"/>
-      <c r="AV14" s="69"/>
-      <c r="AW14" s="65"/>
-      <c r="AX14" s="66"/>
-      <c r="AY14" s="66"/>
-      <c r="AZ14" s="67"/>
-      <c r="BA14" s="69"/>
-      <c r="BB14" s="65"/>
-      <c r="BC14" s="66"/>
-      <c r="BD14" s="66"/>
-      <c r="BE14" s="67"/>
-      <c r="BF14" s="69"/>
-      <c r="BG14" s="65"/>
-      <c r="BH14" s="66"/>
-      <c r="BI14" s="66"/>
-      <c r="BJ14" s="67"/>
-      <c r="BK14" s="69"/>
-      <c r="BL14" s="65"/>
-      <c r="BM14" s="66"/>
-      <c r="BN14" s="66"/>
-      <c r="BO14" s="67"/>
-      <c r="BP14" s="69"/>
-      <c r="BQ14" s="65"/>
-      <c r="BR14" s="66"/>
-      <c r="BS14" s="66"/>
-      <c r="BT14" s="67"/>
-      <c r="BU14" s="69"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="54"/>
+      <c r="I14" s="50"/>
+      <c r="J14" s="51"/>
+      <c r="K14" s="51"/>
+      <c r="L14" s="52"/>
+      <c r="M14" s="54"/>
+      <c r="N14" s="50"/>
+      <c r="O14" s="51"/>
+      <c r="P14" s="51"/>
+      <c r="Q14" s="52"/>
+      <c r="R14" s="54"/>
+      <c r="S14" s="50"/>
+      <c r="T14" s="51"/>
+      <c r="U14" s="51"/>
+      <c r="V14" s="52"/>
+      <c r="W14" s="54"/>
+      <c r="X14" s="50"/>
+      <c r="Y14" s="51"/>
+      <c r="Z14" s="51"/>
+      <c r="AA14" s="52"/>
+      <c r="AB14" s="54"/>
+      <c r="AC14" s="50"/>
+      <c r="AD14" s="51"/>
+      <c r="AE14" s="51"/>
+      <c r="AF14" s="52"/>
+      <c r="AG14" s="54"/>
+      <c r="AH14" s="50"/>
+      <c r="AI14" s="51"/>
+      <c r="AJ14" s="51"/>
+      <c r="AK14" s="52"/>
+      <c r="AL14" s="54"/>
+      <c r="AM14" s="50"/>
+      <c r="AN14" s="51"/>
+      <c r="AO14" s="51"/>
+      <c r="AP14" s="52"/>
+      <c r="AQ14" s="54"/>
+      <c r="AR14" s="50"/>
+      <c r="AS14" s="51"/>
+      <c r="AT14" s="51"/>
+      <c r="AU14" s="52"/>
+      <c r="AV14" s="54"/>
+      <c r="AW14" s="50"/>
+      <c r="AX14" s="51"/>
+      <c r="AY14" s="51"/>
+      <c r="AZ14" s="52"/>
+      <c r="BA14" s="54"/>
+      <c r="BB14" s="50"/>
+      <c r="BC14" s="51"/>
+      <c r="BD14" s="51"/>
+      <c r="BE14" s="52"/>
+      <c r="BF14" s="54"/>
+      <c r="BG14" s="50"/>
+      <c r="BH14" s="51"/>
+      <c r="BI14" s="51"/>
+      <c r="BJ14" s="52"/>
+      <c r="BK14" s="54"/>
+      <c r="BL14" s="50"/>
+      <c r="BM14" s="51"/>
+      <c r="BN14" s="51"/>
+      <c r="BO14" s="52"/>
+      <c r="BP14" s="54"/>
+      <c r="BQ14" s="50"/>
+      <c r="BR14" s="51"/>
+      <c r="BS14" s="51"/>
+      <c r="BT14" s="52"/>
+      <c r="BU14" s="54"/>
     </row>
     <row r="15" spans="1:73" ht="81" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B15" s="49"/>
+      <c r="B15" s="88"/>
       <c r="C15" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="65"/>
-      <c r="E15" s="66"/>
-      <c r="F15" s="66"/>
-      <c r="G15" s="67"/>
-      <c r="H15" s="69"/>
-      <c r="I15" s="65"/>
-      <c r="J15" s="66"/>
-      <c r="K15" s="66"/>
-      <c r="L15" s="67"/>
-      <c r="M15" s="69"/>
-      <c r="N15" s="65"/>
-      <c r="O15" s="66"/>
-      <c r="P15" s="66"/>
-      <c r="Q15" s="67"/>
-      <c r="R15" s="69"/>
-      <c r="S15" s="65"/>
-      <c r="T15" s="66"/>
-      <c r="U15" s="66"/>
-      <c r="V15" s="67"/>
-      <c r="W15" s="69"/>
-      <c r="X15" s="65"/>
-      <c r="Y15" s="66"/>
-      <c r="Z15" s="66"/>
-      <c r="AA15" s="67"/>
-      <c r="AB15" s="69"/>
-      <c r="AC15" s="65"/>
-      <c r="AD15" s="66"/>
-      <c r="AE15" s="66"/>
-      <c r="AF15" s="67"/>
-      <c r="AG15" s="69"/>
-      <c r="AH15" s="65"/>
-      <c r="AI15" s="66"/>
-      <c r="AJ15" s="66"/>
-      <c r="AK15" s="67"/>
-      <c r="AL15" s="69"/>
-      <c r="AM15" s="65"/>
-      <c r="AN15" s="66"/>
-      <c r="AO15" s="66"/>
-      <c r="AP15" s="67"/>
-      <c r="AQ15" s="69"/>
-      <c r="AR15" s="65"/>
-      <c r="AS15" s="66"/>
-      <c r="AT15" s="66"/>
-      <c r="AU15" s="67"/>
-      <c r="AV15" s="69"/>
-      <c r="AW15" s="65"/>
-      <c r="AX15" s="66"/>
-      <c r="AY15" s="66"/>
-      <c r="AZ15" s="67"/>
-      <c r="BA15" s="69"/>
-      <c r="BB15" s="65"/>
-      <c r="BC15" s="66"/>
-      <c r="BD15" s="66"/>
-      <c r="BE15" s="67"/>
-      <c r="BF15" s="69"/>
-      <c r="BG15" s="65"/>
-      <c r="BH15" s="66"/>
-      <c r="BI15" s="66"/>
-      <c r="BJ15" s="67"/>
-      <c r="BK15" s="69"/>
-      <c r="BL15" s="65"/>
-      <c r="BM15" s="66"/>
-      <c r="BN15" s="66"/>
-      <c r="BO15" s="67"/>
-      <c r="BP15" s="69"/>
-      <c r="BQ15" s="65"/>
-      <c r="BR15" s="66"/>
-      <c r="BS15" s="66"/>
-      <c r="BT15" s="67"/>
-      <c r="BU15" s="69"/>
+      <c r="D15" s="50"/>
+      <c r="E15" s="51"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="52"/>
+      <c r="H15" s="54"/>
+      <c r="I15" s="50"/>
+      <c r="J15" s="51"/>
+      <c r="K15" s="51"/>
+      <c r="L15" s="52"/>
+      <c r="M15" s="54"/>
+      <c r="N15" s="50"/>
+      <c r="O15" s="51"/>
+      <c r="P15" s="51"/>
+      <c r="Q15" s="52"/>
+      <c r="R15" s="54"/>
+      <c r="S15" s="50"/>
+      <c r="T15" s="51"/>
+      <c r="U15" s="51"/>
+      <c r="V15" s="52"/>
+      <c r="W15" s="54"/>
+      <c r="X15" s="50"/>
+      <c r="Y15" s="51"/>
+      <c r="Z15" s="51"/>
+      <c r="AA15" s="52"/>
+      <c r="AB15" s="54"/>
+      <c r="AC15" s="50"/>
+      <c r="AD15" s="51"/>
+      <c r="AE15" s="51"/>
+      <c r="AF15" s="52"/>
+      <c r="AG15" s="54"/>
+      <c r="AH15" s="50"/>
+      <c r="AI15" s="51"/>
+      <c r="AJ15" s="51"/>
+      <c r="AK15" s="52"/>
+      <c r="AL15" s="54"/>
+      <c r="AM15" s="50"/>
+      <c r="AN15" s="51"/>
+      <c r="AO15" s="51"/>
+      <c r="AP15" s="52"/>
+      <c r="AQ15" s="54"/>
+      <c r="AR15" s="50"/>
+      <c r="AS15" s="51"/>
+      <c r="AT15" s="51"/>
+      <c r="AU15" s="52"/>
+      <c r="AV15" s="54"/>
+      <c r="AW15" s="50"/>
+      <c r="AX15" s="51"/>
+      <c r="AY15" s="51"/>
+      <c r="AZ15" s="52"/>
+      <c r="BA15" s="54"/>
+      <c r="BB15" s="50"/>
+      <c r="BC15" s="51"/>
+      <c r="BD15" s="51"/>
+      <c r="BE15" s="52"/>
+      <c r="BF15" s="54"/>
+      <c r="BG15" s="50"/>
+      <c r="BH15" s="51"/>
+      <c r="BI15" s="51"/>
+      <c r="BJ15" s="52"/>
+      <c r="BK15" s="54"/>
+      <c r="BL15" s="50"/>
+      <c r="BM15" s="51"/>
+      <c r="BN15" s="51"/>
+      <c r="BO15" s="52"/>
+      <c r="BP15" s="54"/>
+      <c r="BQ15" s="50"/>
+      <c r="BR15" s="51"/>
+      <c r="BS15" s="51"/>
+      <c r="BT15" s="52"/>
+      <c r="BU15" s="54"/>
     </row>
     <row r="16" spans="1:73" ht="91.8" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B16" s="49"/>
+      <c r="B16" s="88"/>
       <c r="C16" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="D16" s="65"/>
-      <c r="E16" s="66"/>
-      <c r="F16" s="66"/>
-      <c r="G16" s="67"/>
-      <c r="H16" s="69"/>
-      <c r="I16" s="65"/>
-      <c r="J16" s="66"/>
-      <c r="K16" s="66"/>
-      <c r="L16" s="67"/>
-      <c r="M16" s="69"/>
-      <c r="N16" s="65"/>
-      <c r="O16" s="66"/>
-      <c r="P16" s="66"/>
-      <c r="Q16" s="67"/>
-      <c r="R16" s="69"/>
-      <c r="S16" s="65"/>
-      <c r="T16" s="66"/>
-      <c r="U16" s="66"/>
-      <c r="V16" s="67"/>
-      <c r="W16" s="69"/>
-      <c r="X16" s="65"/>
-      <c r="Y16" s="66"/>
-      <c r="Z16" s="66"/>
-      <c r="AA16" s="67"/>
-      <c r="AB16" s="69"/>
-      <c r="AC16" s="65"/>
-      <c r="AD16" s="66"/>
-      <c r="AE16" s="66"/>
-      <c r="AF16" s="67"/>
-      <c r="AG16" s="69"/>
-      <c r="AH16" s="65"/>
-      <c r="AI16" s="66"/>
-      <c r="AJ16" s="66"/>
-      <c r="AK16" s="67"/>
-      <c r="AL16" s="69"/>
-      <c r="AM16" s="65"/>
-      <c r="AN16" s="66"/>
-      <c r="AO16" s="66"/>
-      <c r="AP16" s="67"/>
-      <c r="AQ16" s="69"/>
-      <c r="AR16" s="65"/>
-      <c r="AS16" s="66"/>
-      <c r="AT16" s="66"/>
-      <c r="AU16" s="67"/>
-      <c r="AV16" s="69"/>
-      <c r="AW16" s="65"/>
-      <c r="AX16" s="66"/>
-      <c r="AY16" s="66"/>
-      <c r="AZ16" s="67"/>
-      <c r="BA16" s="69"/>
-      <c r="BB16" s="65"/>
-      <c r="BC16" s="66"/>
-      <c r="BD16" s="66"/>
-      <c r="BE16" s="67"/>
-      <c r="BF16" s="69"/>
-      <c r="BG16" s="65"/>
-      <c r="BH16" s="66"/>
-      <c r="BI16" s="66"/>
-      <c r="BJ16" s="67"/>
-      <c r="BK16" s="69"/>
-      <c r="BL16" s="65"/>
-      <c r="BM16" s="66"/>
-      <c r="BN16" s="66"/>
-      <c r="BO16" s="67"/>
-      <c r="BP16" s="69"/>
-      <c r="BQ16" s="65"/>
-      <c r="BR16" s="66"/>
-      <c r="BS16" s="66"/>
-      <c r="BT16" s="67"/>
-      <c r="BU16" s="69"/>
+      <c r="D16" s="50"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="51"/>
+      <c r="G16" s="52"/>
+      <c r="H16" s="54"/>
+      <c r="I16" s="50"/>
+      <c r="J16" s="51"/>
+      <c r="K16" s="51"/>
+      <c r="L16" s="52"/>
+      <c r="M16" s="54"/>
+      <c r="N16" s="50"/>
+      <c r="O16" s="51"/>
+      <c r="P16" s="51"/>
+      <c r="Q16" s="52"/>
+      <c r="R16" s="54"/>
+      <c r="S16" s="50"/>
+      <c r="T16" s="51"/>
+      <c r="U16" s="51"/>
+      <c r="V16" s="52"/>
+      <c r="W16" s="54"/>
+      <c r="X16" s="50"/>
+      <c r="Y16" s="51"/>
+      <c r="Z16" s="51"/>
+      <c r="AA16" s="52"/>
+      <c r="AB16" s="54"/>
+      <c r="AC16" s="50"/>
+      <c r="AD16" s="51"/>
+      <c r="AE16" s="51"/>
+      <c r="AF16" s="52"/>
+      <c r="AG16" s="54"/>
+      <c r="AH16" s="50"/>
+      <c r="AI16" s="51"/>
+      <c r="AJ16" s="51"/>
+      <c r="AK16" s="52"/>
+      <c r="AL16" s="54"/>
+      <c r="AM16" s="50"/>
+      <c r="AN16" s="51"/>
+      <c r="AO16" s="51"/>
+      <c r="AP16" s="52"/>
+      <c r="AQ16" s="54"/>
+      <c r="AR16" s="50"/>
+      <c r="AS16" s="51"/>
+      <c r="AT16" s="51"/>
+      <c r="AU16" s="52"/>
+      <c r="AV16" s="54"/>
+      <c r="AW16" s="50"/>
+      <c r="AX16" s="51"/>
+      <c r="AY16" s="51"/>
+      <c r="AZ16" s="52"/>
+      <c r="BA16" s="54"/>
+      <c r="BB16" s="50"/>
+      <c r="BC16" s="51"/>
+      <c r="BD16" s="51"/>
+      <c r="BE16" s="52"/>
+      <c r="BF16" s="54"/>
+      <c r="BG16" s="50"/>
+      <c r="BH16" s="51"/>
+      <c r="BI16" s="51"/>
+      <c r="BJ16" s="52"/>
+      <c r="BK16" s="54"/>
+      <c r="BL16" s="50"/>
+      <c r="BM16" s="51"/>
+      <c r="BN16" s="51"/>
+      <c r="BO16" s="52"/>
+      <c r="BP16" s="54"/>
+      <c r="BQ16" s="50"/>
+      <c r="BR16" s="51"/>
+      <c r="BS16" s="51"/>
+      <c r="BT16" s="52"/>
+      <c r="BU16" s="54"/>
     </row>
     <row r="17" spans="1:73" ht="31.35" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B17" s="50"/>
+      <c r="B17" s="89"/>
       <c r="C17" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="D17" s="71"/>
-      <c r="E17" s="72"/>
-      <c r="F17" s="72"/>
-      <c r="G17" s="73"/>
-      <c r="H17" s="75"/>
-      <c r="I17" s="71"/>
-      <c r="J17" s="72"/>
-      <c r="K17" s="72"/>
-      <c r="L17" s="73"/>
-      <c r="M17" s="75"/>
-      <c r="N17" s="71"/>
-      <c r="O17" s="72"/>
-      <c r="P17" s="72"/>
-      <c r="Q17" s="73"/>
-      <c r="R17" s="75"/>
-      <c r="S17" s="71"/>
-      <c r="T17" s="72"/>
-      <c r="U17" s="72"/>
-      <c r="V17" s="73"/>
-      <c r="W17" s="75"/>
-      <c r="X17" s="71"/>
-      <c r="Y17" s="72"/>
-      <c r="Z17" s="72"/>
-      <c r="AA17" s="73"/>
-      <c r="AB17" s="75"/>
-      <c r="AC17" s="71"/>
-      <c r="AD17" s="72"/>
-      <c r="AE17" s="72"/>
-      <c r="AF17" s="73"/>
-      <c r="AG17" s="75"/>
-      <c r="AH17" s="71"/>
-      <c r="AI17" s="72"/>
-      <c r="AJ17" s="72"/>
-      <c r="AK17" s="73"/>
-      <c r="AL17" s="75"/>
-      <c r="AM17" s="71"/>
-      <c r="AN17" s="72"/>
-      <c r="AO17" s="72"/>
-      <c r="AP17" s="73"/>
-      <c r="AQ17" s="75"/>
-      <c r="AR17" s="71"/>
-      <c r="AS17" s="72"/>
-      <c r="AT17" s="72"/>
-      <c r="AU17" s="73"/>
-      <c r="AV17" s="75"/>
-      <c r="AW17" s="71"/>
-      <c r="AX17" s="72"/>
-      <c r="AY17" s="72"/>
-      <c r="AZ17" s="73"/>
-      <c r="BA17" s="75"/>
-      <c r="BB17" s="71"/>
-      <c r="BC17" s="72"/>
-      <c r="BD17" s="72"/>
-      <c r="BE17" s="73"/>
-      <c r="BF17" s="75"/>
-      <c r="BG17" s="71"/>
-      <c r="BH17" s="72"/>
-      <c r="BI17" s="72"/>
-      <c r="BJ17" s="73"/>
-      <c r="BK17" s="75"/>
-      <c r="BL17" s="71"/>
-      <c r="BM17" s="72"/>
-      <c r="BN17" s="72"/>
-      <c r="BO17" s="73"/>
-      <c r="BP17" s="75"/>
-      <c r="BQ17" s="71"/>
-      <c r="BR17" s="72"/>
-      <c r="BS17" s="72"/>
-      <c r="BT17" s="73"/>
-      <c r="BU17" s="75"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="58"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="56"/>
+      <c r="J17" s="57"/>
+      <c r="K17" s="57"/>
+      <c r="L17" s="58"/>
+      <c r="M17" s="60"/>
+      <c r="N17" s="56"/>
+      <c r="O17" s="57"/>
+      <c r="P17" s="57"/>
+      <c r="Q17" s="58"/>
+      <c r="R17" s="60"/>
+      <c r="S17" s="56"/>
+      <c r="T17" s="57"/>
+      <c r="U17" s="57"/>
+      <c r="V17" s="58"/>
+      <c r="W17" s="60"/>
+      <c r="X17" s="56"/>
+      <c r="Y17" s="57"/>
+      <c r="Z17" s="57"/>
+      <c r="AA17" s="58"/>
+      <c r="AB17" s="60"/>
+      <c r="AC17" s="56"/>
+      <c r="AD17" s="57"/>
+      <c r="AE17" s="57"/>
+      <c r="AF17" s="58"/>
+      <c r="AG17" s="60"/>
+      <c r="AH17" s="56"/>
+      <c r="AI17" s="57"/>
+      <c r="AJ17" s="57"/>
+      <c r="AK17" s="58"/>
+      <c r="AL17" s="60"/>
+      <c r="AM17" s="56"/>
+      <c r="AN17" s="57"/>
+      <c r="AO17" s="57"/>
+      <c r="AP17" s="58"/>
+      <c r="AQ17" s="60"/>
+      <c r="AR17" s="56"/>
+      <c r="AS17" s="57"/>
+      <c r="AT17" s="57"/>
+      <c r="AU17" s="58"/>
+      <c r="AV17" s="60"/>
+      <c r="AW17" s="56"/>
+      <c r="AX17" s="57"/>
+      <c r="AY17" s="57"/>
+      <c r="AZ17" s="58"/>
+      <c r="BA17" s="60"/>
+      <c r="BB17" s="56"/>
+      <c r="BC17" s="57"/>
+      <c r="BD17" s="57"/>
+      <c r="BE17" s="58"/>
+      <c r="BF17" s="60"/>
+      <c r="BG17" s="56"/>
+      <c r="BH17" s="57"/>
+      <c r="BI17" s="57"/>
+      <c r="BJ17" s="58"/>
+      <c r="BK17" s="60"/>
+      <c r="BL17" s="56"/>
+      <c r="BM17" s="57"/>
+      <c r="BN17" s="57"/>
+      <c r="BO17" s="58"/>
+      <c r="BP17" s="60"/>
+      <c r="BQ17" s="56"/>
+      <c r="BR17" s="57"/>
+      <c r="BS17" s="57"/>
+      <c r="BT17" s="58"/>
+      <c r="BU17" s="60"/>
     </row>
     <row r="18" spans="1:73" ht="30.75" x14ac:dyDescent="0.45">
-      <c r="B18" s="89" t="s">
+      <c r="B18" s="81" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="85" t="s">
+      <c r="C18" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="86"/>
-      <c r="E18" s="87"/>
-      <c r="F18" s="92"/>
-      <c r="G18" s="88"/>
-      <c r="H18" s="93"/>
-      <c r="I18" s="86"/>
-      <c r="J18" s="87"/>
-      <c r="K18" s="92"/>
-      <c r="L18" s="88"/>
-      <c r="M18" s="93"/>
-      <c r="N18" s="86"/>
-      <c r="O18" s="87"/>
-      <c r="P18" s="92"/>
-      <c r="Q18" s="88"/>
-      <c r="R18" s="93"/>
-      <c r="S18" s="86"/>
-      <c r="T18" s="87"/>
-      <c r="U18" s="92"/>
-      <c r="V18" s="88"/>
-      <c r="W18" s="93"/>
-      <c r="X18" s="86"/>
-      <c r="Y18" s="87"/>
-      <c r="Z18" s="92"/>
-      <c r="AA18" s="88"/>
-      <c r="AB18" s="93"/>
-      <c r="AC18" s="86"/>
-      <c r="AD18" s="87"/>
-      <c r="AE18" s="92"/>
-      <c r="AF18" s="88"/>
-      <c r="AG18" s="93"/>
-      <c r="AH18" s="86"/>
-      <c r="AI18" s="87"/>
-      <c r="AJ18" s="92"/>
-      <c r="AK18" s="88"/>
-      <c r="AL18" s="93"/>
-      <c r="AM18" s="86"/>
-      <c r="AN18" s="87"/>
-      <c r="AO18" s="92"/>
-      <c r="AP18" s="88"/>
-      <c r="AQ18" s="93"/>
-      <c r="AR18" s="86"/>
-      <c r="AS18" s="87"/>
-      <c r="AT18" s="92"/>
-      <c r="AU18" s="88"/>
-      <c r="AV18" s="93"/>
-      <c r="AW18" s="86"/>
-      <c r="AX18" s="87"/>
-      <c r="AY18" s="92"/>
-      <c r="AZ18" s="88"/>
-      <c r="BA18" s="93"/>
-      <c r="BB18" s="86"/>
-      <c r="BC18" s="87"/>
-      <c r="BD18" s="92"/>
-      <c r="BE18" s="88"/>
-      <c r="BF18" s="93"/>
-      <c r="BG18" s="86"/>
-      <c r="BH18" s="87"/>
-      <c r="BI18" s="92"/>
-      <c r="BJ18" s="88"/>
-      <c r="BK18" s="93"/>
-      <c r="BL18" s="86"/>
-      <c r="BM18" s="87"/>
-      <c r="BN18" s="92"/>
-      <c r="BO18" s="88"/>
-      <c r="BP18" s="93"/>
-      <c r="BQ18" s="86"/>
-      <c r="BR18" s="87"/>
-      <c r="BS18" s="92"/>
-      <c r="BT18" s="88"/>
-      <c r="BU18" s="93"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="73"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="74"/>
+      <c r="I18" s="69"/>
+      <c r="J18" s="70"/>
+      <c r="K18" s="73"/>
+      <c r="L18" s="71"/>
+      <c r="M18" s="74"/>
+      <c r="N18" s="69"/>
+      <c r="O18" s="70"/>
+      <c r="P18" s="73"/>
+      <c r="Q18" s="71"/>
+      <c r="R18" s="74"/>
+      <c r="S18" s="69"/>
+      <c r="T18" s="70"/>
+      <c r="U18" s="73"/>
+      <c r="V18" s="71"/>
+      <c r="W18" s="74"/>
+      <c r="X18" s="69"/>
+      <c r="Y18" s="70"/>
+      <c r="Z18" s="73"/>
+      <c r="AA18" s="71"/>
+      <c r="AB18" s="74"/>
+      <c r="AC18" s="69"/>
+      <c r="AD18" s="70"/>
+      <c r="AE18" s="73"/>
+      <c r="AF18" s="71"/>
+      <c r="AG18" s="74"/>
+      <c r="AH18" s="69"/>
+      <c r="AI18" s="70"/>
+      <c r="AJ18" s="73"/>
+      <c r="AK18" s="71"/>
+      <c r="AL18" s="74"/>
+      <c r="AM18" s="69"/>
+      <c r="AN18" s="70"/>
+      <c r="AO18" s="73"/>
+      <c r="AP18" s="71"/>
+      <c r="AQ18" s="74"/>
+      <c r="AR18" s="69"/>
+      <c r="AS18" s="70"/>
+      <c r="AT18" s="73"/>
+      <c r="AU18" s="71"/>
+      <c r="AV18" s="74"/>
+      <c r="AW18" s="69"/>
+      <c r="AX18" s="70"/>
+      <c r="AY18" s="73"/>
+      <c r="AZ18" s="71"/>
+      <c r="BA18" s="74"/>
+      <c r="BB18" s="69"/>
+      <c r="BC18" s="70"/>
+      <c r="BD18" s="73"/>
+      <c r="BE18" s="71"/>
+      <c r="BF18" s="74"/>
+      <c r="BG18" s="69"/>
+      <c r="BH18" s="70"/>
+      <c r="BI18" s="73"/>
+      <c r="BJ18" s="71"/>
+      <c r="BK18" s="74"/>
+      <c r="BL18" s="69"/>
+      <c r="BM18" s="70"/>
+      <c r="BN18" s="73"/>
+      <c r="BO18" s="71"/>
+      <c r="BP18" s="74"/>
+      <c r="BQ18" s="69"/>
+      <c r="BR18" s="70"/>
+      <c r="BS18" s="73"/>
+      <c r="BT18" s="71"/>
+      <c r="BU18" s="74"/>
     </row>
     <row r="19" spans="1:73" ht="61.5" x14ac:dyDescent="0.45">
-      <c r="B19" s="51"/>
+      <c r="B19" s="82"/>
       <c r="C19" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D19" s="76"/>
-      <c r="E19" s="77"/>
-      <c r="F19" s="94"/>
-      <c r="G19" s="78"/>
-      <c r="H19" s="95"/>
-      <c r="I19" s="76"/>
-      <c r="J19" s="77"/>
-      <c r="K19" s="94"/>
-      <c r="L19" s="78"/>
-      <c r="M19" s="95"/>
-      <c r="N19" s="76"/>
-      <c r="O19" s="77"/>
-      <c r="P19" s="94"/>
-      <c r="Q19" s="78"/>
-      <c r="R19" s="95"/>
-      <c r="S19" s="76"/>
-      <c r="T19" s="77"/>
-      <c r="U19" s="94"/>
-      <c r="V19" s="78"/>
-      <c r="W19" s="95"/>
-      <c r="X19" s="76"/>
-      <c r="Y19" s="77"/>
-      <c r="Z19" s="94"/>
-      <c r="AA19" s="78"/>
-      <c r="AB19" s="95"/>
-      <c r="AC19" s="76"/>
-      <c r="AD19" s="77"/>
-      <c r="AE19" s="94"/>
-      <c r="AF19" s="78"/>
-      <c r="AG19" s="95"/>
-      <c r="AH19" s="76"/>
-      <c r="AI19" s="77"/>
-      <c r="AJ19" s="94"/>
-      <c r="AK19" s="78"/>
-      <c r="AL19" s="95"/>
-      <c r="AM19" s="76"/>
-      <c r="AN19" s="77"/>
-      <c r="AO19" s="94"/>
-      <c r="AP19" s="78"/>
-      <c r="AQ19" s="95"/>
-      <c r="AR19" s="76"/>
-      <c r="AS19" s="77"/>
-      <c r="AT19" s="94"/>
-      <c r="AU19" s="78"/>
-      <c r="AV19" s="95"/>
-      <c r="AW19" s="76"/>
-      <c r="AX19" s="77"/>
-      <c r="AY19" s="94"/>
-      <c r="AZ19" s="78"/>
-      <c r="BA19" s="95"/>
-      <c r="BB19" s="76"/>
-      <c r="BC19" s="77"/>
-      <c r="BD19" s="94"/>
-      <c r="BE19" s="78"/>
-      <c r="BF19" s="95"/>
-      <c r="BG19" s="76"/>
-      <c r="BH19" s="77"/>
-      <c r="BI19" s="94"/>
-      <c r="BJ19" s="78"/>
-      <c r="BK19" s="95"/>
-      <c r="BL19" s="76"/>
-      <c r="BM19" s="77"/>
-      <c r="BN19" s="94"/>
-      <c r="BO19" s="78"/>
-      <c r="BP19" s="95"/>
-      <c r="BQ19" s="76"/>
-      <c r="BR19" s="77"/>
-      <c r="BS19" s="94"/>
-      <c r="BT19" s="78"/>
-      <c r="BU19" s="95"/>
+      <c r="D19" s="61"/>
+      <c r="E19" s="62"/>
+      <c r="F19" s="75"/>
+      <c r="G19" s="63"/>
+      <c r="H19" s="76"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="62"/>
+      <c r="K19" s="75"/>
+      <c r="L19" s="63"/>
+      <c r="M19" s="76"/>
+      <c r="N19" s="61"/>
+      <c r="O19" s="62"/>
+      <c r="P19" s="75"/>
+      <c r="Q19" s="63"/>
+      <c r="R19" s="76"/>
+      <c r="S19" s="61"/>
+      <c r="T19" s="62"/>
+      <c r="U19" s="75"/>
+      <c r="V19" s="63"/>
+      <c r="W19" s="76"/>
+      <c r="X19" s="61"/>
+      <c r="Y19" s="62"/>
+      <c r="Z19" s="75"/>
+      <c r="AA19" s="63"/>
+      <c r="AB19" s="76"/>
+      <c r="AC19" s="61"/>
+      <c r="AD19" s="62"/>
+      <c r="AE19" s="75"/>
+      <c r="AF19" s="63"/>
+      <c r="AG19" s="76"/>
+      <c r="AH19" s="61"/>
+      <c r="AI19" s="62"/>
+      <c r="AJ19" s="75"/>
+      <c r="AK19" s="63"/>
+      <c r="AL19" s="76"/>
+      <c r="AM19" s="61"/>
+      <c r="AN19" s="62"/>
+      <c r="AO19" s="75"/>
+      <c r="AP19" s="63"/>
+      <c r="AQ19" s="76"/>
+      <c r="AR19" s="61"/>
+      <c r="AS19" s="62"/>
+      <c r="AT19" s="75"/>
+      <c r="AU19" s="63"/>
+      <c r="AV19" s="76"/>
+      <c r="AW19" s="61"/>
+      <c r="AX19" s="62"/>
+      <c r="AY19" s="75"/>
+      <c r="AZ19" s="63"/>
+      <c r="BA19" s="76"/>
+      <c r="BB19" s="61"/>
+      <c r="BC19" s="62"/>
+      <c r="BD19" s="75"/>
+      <c r="BE19" s="63"/>
+      <c r="BF19" s="76"/>
+      <c r="BG19" s="61"/>
+      <c r="BH19" s="62"/>
+      <c r="BI19" s="75"/>
+      <c r="BJ19" s="63"/>
+      <c r="BK19" s="76"/>
+      <c r="BL19" s="61"/>
+      <c r="BM19" s="62"/>
+      <c r="BN19" s="75"/>
+      <c r="BO19" s="63"/>
+      <c r="BP19" s="76"/>
+      <c r="BQ19" s="61"/>
+      <c r="BR19" s="62"/>
+      <c r="BS19" s="75"/>
+      <c r="BT19" s="63"/>
+      <c r="BU19" s="76"/>
     </row>
     <row r="20" spans="1:73" x14ac:dyDescent="0.45">
-      <c r="B20" s="90"/>
-      <c r="C20" s="79"/>
-      <c r="D20" s="96"/>
-      <c r="E20" s="80"/>
-      <c r="F20" s="80"/>
-      <c r="G20" s="81"/>
-      <c r="H20" s="82"/>
-      <c r="I20" s="96"/>
-      <c r="J20" s="80"/>
-      <c r="K20" s="80"/>
-      <c r="L20" s="81"/>
-      <c r="M20" s="82"/>
-      <c r="N20" s="96"/>
-      <c r="O20" s="80"/>
-      <c r="P20" s="80"/>
-      <c r="Q20" s="81"/>
-      <c r="R20" s="82"/>
-      <c r="S20" s="96"/>
-      <c r="T20" s="80"/>
-      <c r="U20" s="80"/>
-      <c r="V20" s="81"/>
-      <c r="W20" s="82"/>
-      <c r="X20" s="96"/>
-      <c r="Y20" s="80"/>
-      <c r="Z20" s="80"/>
-      <c r="AA20" s="81"/>
-      <c r="AB20" s="82"/>
-      <c r="AC20" s="96"/>
-      <c r="AD20" s="80"/>
-      <c r="AE20" s="80"/>
-      <c r="AF20" s="81"/>
-      <c r="AG20" s="82"/>
-      <c r="AH20" s="96"/>
-      <c r="AI20" s="80"/>
-      <c r="AJ20" s="80"/>
-      <c r="AK20" s="81"/>
-      <c r="AL20" s="82"/>
-      <c r="AM20" s="96"/>
-      <c r="AN20" s="80"/>
-      <c r="AO20" s="80"/>
-      <c r="AP20" s="81"/>
-      <c r="AQ20" s="82"/>
-      <c r="AR20" s="96"/>
-      <c r="AS20" s="80"/>
-      <c r="AT20" s="80"/>
-      <c r="AU20" s="81"/>
-      <c r="AV20" s="82"/>
-      <c r="AW20" s="96"/>
-      <c r="AX20" s="80"/>
-      <c r="AY20" s="80"/>
-      <c r="AZ20" s="81"/>
-      <c r="BA20" s="82"/>
-      <c r="BB20" s="96"/>
-      <c r="BC20" s="80"/>
-      <c r="BD20" s="80"/>
-      <c r="BE20" s="81"/>
-      <c r="BF20" s="82"/>
-      <c r="BG20" s="96"/>
-      <c r="BH20" s="80"/>
-      <c r="BI20" s="80"/>
-      <c r="BJ20" s="81"/>
-      <c r="BK20" s="82"/>
-      <c r="BL20" s="96"/>
-      <c r="BM20" s="80"/>
-      <c r="BN20" s="80"/>
-      <c r="BO20" s="81"/>
-      <c r="BP20" s="82"/>
-      <c r="BQ20" s="96"/>
-      <c r="BR20" s="80"/>
-      <c r="BS20" s="80"/>
-      <c r="BT20" s="81"/>
-      <c r="BU20" s="82"/>
+      <c r="B20" s="72"/>
+      <c r="C20" s="64"/>
+      <c r="D20" s="77"/>
+      <c r="E20" s="65"/>
+      <c r="F20" s="65"/>
+      <c r="G20" s="66"/>
+      <c r="H20" s="67"/>
+      <c r="I20" s="77"/>
+      <c r="J20" s="65"/>
+      <c r="K20" s="65"/>
+      <c r="L20" s="66"/>
+      <c r="M20" s="67"/>
+      <c r="N20" s="77"/>
+      <c r="O20" s="65"/>
+      <c r="P20" s="65"/>
+      <c r="Q20" s="66"/>
+      <c r="R20" s="67"/>
+      <c r="S20" s="77"/>
+      <c r="T20" s="65"/>
+      <c r="U20" s="65"/>
+      <c r="V20" s="66"/>
+      <c r="W20" s="67"/>
+      <c r="X20" s="77"/>
+      <c r="Y20" s="65"/>
+      <c r="Z20" s="65"/>
+      <c r="AA20" s="66"/>
+      <c r="AB20" s="67"/>
+      <c r="AC20" s="77"/>
+      <c r="AD20" s="65"/>
+      <c r="AE20" s="65"/>
+      <c r="AF20" s="66"/>
+      <c r="AG20" s="67"/>
+      <c r="AH20" s="77"/>
+      <c r="AI20" s="65"/>
+      <c r="AJ20" s="65"/>
+      <c r="AK20" s="66"/>
+      <c r="AL20" s="67"/>
+      <c r="AM20" s="77"/>
+      <c r="AN20" s="65"/>
+      <c r="AO20" s="65"/>
+      <c r="AP20" s="66"/>
+      <c r="AQ20" s="67"/>
+      <c r="AR20" s="77"/>
+      <c r="AS20" s="65"/>
+      <c r="AT20" s="65"/>
+      <c r="AU20" s="66"/>
+      <c r="AV20" s="67"/>
+      <c r="AW20" s="77"/>
+      <c r="AX20" s="65"/>
+      <c r="AY20" s="65"/>
+      <c r="AZ20" s="66"/>
+      <c r="BA20" s="67"/>
+      <c r="BB20" s="77"/>
+      <c r="BC20" s="65"/>
+      <c r="BD20" s="65"/>
+      <c r="BE20" s="66"/>
+      <c r="BF20" s="67"/>
+      <c r="BG20" s="77"/>
+      <c r="BH20" s="65"/>
+      <c r="BI20" s="65"/>
+      <c r="BJ20" s="66"/>
+      <c r="BK20" s="67"/>
+      <c r="BL20" s="77"/>
+      <c r="BM20" s="65"/>
+      <c r="BN20" s="65"/>
+      <c r="BO20" s="66"/>
+      <c r="BP20" s="67"/>
+      <c r="BQ20" s="77"/>
+      <c r="BR20" s="65"/>
+      <c r="BS20" s="65"/>
+      <c r="BT20" s="66"/>
+      <c r="BU20" s="67"/>
     </row>
     <row r="21" spans="1:73" s="3" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A21" s="2"/>
-      <c r="B21" s="91" t="s">
+      <c r="B21" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="C21" s="91"/>
-      <c r="D21" s="83">
+      <c r="C21" s="83"/>
+      <c r="D21" s="93">
         <f>AVERAGE(D4:D20)</f>
         <v>0</v>
       </c>
-      <c r="E21" s="83"/>
-      <c r="F21" s="83"/>
-      <c r="G21" s="83"/>
-      <c r="H21" s="84"/>
-      <c r="I21" s="83">
+      <c r="E21" s="93"/>
+      <c r="F21" s="93"/>
+      <c r="G21" s="93"/>
+      <c r="H21" s="94"/>
+      <c r="I21" s="93">
         <f>AVERAGE(I4:I20)</f>
         <v>0</v>
       </c>
-      <c r="J21" s="83"/>
-      <c r="K21" s="83"/>
-      <c r="L21" s="83"/>
-      <c r="M21" s="84"/>
-      <c r="N21" s="83">
+      <c r="J21" s="93"/>
+      <c r="K21" s="93"/>
+      <c r="L21" s="93"/>
+      <c r="M21" s="94"/>
+      <c r="N21" s="93">
         <f>AVERAGE(N4:N20)</f>
         <v>0</v>
       </c>
-      <c r="O21" s="83"/>
-      <c r="P21" s="83"/>
-      <c r="Q21" s="83"/>
-      <c r="R21" s="84"/>
-      <c r="S21" s="83">
+      <c r="O21" s="93"/>
+      <c r="P21" s="93"/>
+      <c r="Q21" s="93"/>
+      <c r="R21" s="94"/>
+      <c r="S21" s="93">
         <f>AVERAGE(S4:S20)</f>
         <v>0</v>
       </c>
-      <c r="T21" s="83"/>
-      <c r="U21" s="83"/>
-      <c r="V21" s="83"/>
-      <c r="W21" s="84"/>
-      <c r="X21" s="83">
+      <c r="T21" s="93"/>
+      <c r="U21" s="93"/>
+      <c r="V21" s="93"/>
+      <c r="W21" s="94"/>
+      <c r="X21" s="93">
         <f>AVERAGE(X4:X20)</f>
         <v>0</v>
       </c>
-      <c r="Y21" s="83"/>
-      <c r="Z21" s="83"/>
-      <c r="AA21" s="83"/>
-      <c r="AB21" s="84"/>
-      <c r="AC21" s="83">
+      <c r="Y21" s="93"/>
+      <c r="Z21" s="93"/>
+      <c r="AA21" s="93"/>
+      <c r="AB21" s="94"/>
+      <c r="AC21" s="93">
         <f>AVERAGE(AC4:AC20)</f>
         <v>0</v>
       </c>
-      <c r="AD21" s="83"/>
-      <c r="AE21" s="83"/>
-      <c r="AF21" s="83"/>
-      <c r="AG21" s="84"/>
-      <c r="AH21" s="83">
+      <c r="AD21" s="93"/>
+      <c r="AE21" s="93"/>
+      <c r="AF21" s="93"/>
+      <c r="AG21" s="94"/>
+      <c r="AH21" s="93">
         <f>AVERAGE(AH4:AH20)</f>
         <v>0</v>
       </c>
-      <c r="AI21" s="83"/>
-      <c r="AJ21" s="83"/>
-      <c r="AK21" s="83"/>
-      <c r="AL21" s="84"/>
-      <c r="AM21" s="83">
+      <c r="AI21" s="93"/>
+      <c r="AJ21" s="93"/>
+      <c r="AK21" s="93"/>
+      <c r="AL21" s="94"/>
+      <c r="AM21" s="93">
         <f>AVERAGE(AM4:AM20)</f>
         <v>0</v>
       </c>
-      <c r="AN21" s="83"/>
-      <c r="AO21" s="83"/>
-      <c r="AP21" s="83"/>
-      <c r="AQ21" s="84"/>
-      <c r="AR21" s="83">
+      <c r="AN21" s="93"/>
+      <c r="AO21" s="93"/>
+      <c r="AP21" s="93"/>
+      <c r="AQ21" s="94"/>
+      <c r="AR21" s="93">
         <f>AVERAGE(AR4:AR20)</f>
         <v>0</v>
       </c>
-      <c r="AS21" s="83"/>
-      <c r="AT21" s="83"/>
-      <c r="AU21" s="83"/>
-      <c r="AV21" s="84"/>
-      <c r="AW21" s="83">
+      <c r="AS21" s="93"/>
+      <c r="AT21" s="93"/>
+      <c r="AU21" s="93"/>
+      <c r="AV21" s="94"/>
+      <c r="AW21" s="93">
         <f>AVERAGE(AW4:AW20)</f>
         <v>0</v>
       </c>
-      <c r="AX21" s="83"/>
-      <c r="AY21" s="83"/>
-      <c r="AZ21" s="83"/>
-      <c r="BA21" s="84"/>
-      <c r="BB21" s="83">
+      <c r="AX21" s="93"/>
+      <c r="AY21" s="93"/>
+      <c r="AZ21" s="93"/>
+      <c r="BA21" s="94"/>
+      <c r="BB21" s="93">
         <f>AVERAGE(BB4:BB20)</f>
         <v>0</v>
       </c>
-      <c r="BC21" s="83"/>
-      <c r="BD21" s="83"/>
-      <c r="BE21" s="83"/>
-      <c r="BF21" s="84"/>
-      <c r="BG21" s="83">
+      <c r="BC21" s="93"/>
+      <c r="BD21" s="93"/>
+      <c r="BE21" s="93"/>
+      <c r="BF21" s="94"/>
+      <c r="BG21" s="93">
         <f>AVERAGE(BG4:BG20)</f>
         <v>0</v>
       </c>
-      <c r="BH21" s="83"/>
-      <c r="BI21" s="83"/>
-      <c r="BJ21" s="83"/>
-      <c r="BK21" s="84"/>
-      <c r="BL21" s="83">
+      <c r="BH21" s="93"/>
+      <c r="BI21" s="93"/>
+      <c r="BJ21" s="93"/>
+      <c r="BK21" s="94"/>
+      <c r="BL21" s="93">
         <f>AVERAGE(BL4:BL20)</f>
         <v>0</v>
       </c>
-      <c r="BM21" s="83"/>
-      <c r="BN21" s="83"/>
-      <c r="BO21" s="83"/>
-      <c r="BP21" s="84"/>
-      <c r="BQ21" s="83">
+      <c r="BM21" s="93"/>
+      <c r="BN21" s="93"/>
+      <c r="BO21" s="93"/>
+      <c r="BP21" s="94"/>
+      <c r="BQ21" s="93">
         <f>AVERAGE(BQ4:BQ20)</f>
         <v>0</v>
       </c>
-      <c r="BR21" s="83"/>
-      <c r="BS21" s="83"/>
-      <c r="BT21" s="83"/>
-      <c r="BU21" s="84"/>
+      <c r="BR21" s="93"/>
+      <c r="BS21" s="93"/>
+      <c r="BT21" s="93"/>
+      <c r="BU21" s="94"/>
     </row>
     <row r="22" spans="1:73" s="9" customFormat="1" x14ac:dyDescent="0.45">
       <c r="C22" s="12"/>
@@ -7513,12 +7513,18 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B4:B10"/>
-    <mergeCell ref="B11:B17"/>
+    <mergeCell ref="AH21:AL21"/>
+    <mergeCell ref="BL21:BP21"/>
+    <mergeCell ref="AM21:AQ21"/>
+    <mergeCell ref="AR21:AV21"/>
+    <mergeCell ref="AW21:BA21"/>
+    <mergeCell ref="BB21:BF21"/>
+    <mergeCell ref="BG21:BK21"/>
+    <mergeCell ref="N2:R2"/>
+    <mergeCell ref="N21:R21"/>
+    <mergeCell ref="S21:W21"/>
+    <mergeCell ref="X21:AB21"/>
+    <mergeCell ref="AC21:AG21"/>
     <mergeCell ref="BQ2:BU2"/>
     <mergeCell ref="BQ21:BU21"/>
     <mergeCell ref="D2:H2"/>
@@ -7535,18 +7541,12 @@
     <mergeCell ref="AH2:AL2"/>
     <mergeCell ref="AC2:AG2"/>
     <mergeCell ref="S2:W2"/>
-    <mergeCell ref="N2:R2"/>
-    <mergeCell ref="N21:R21"/>
-    <mergeCell ref="S21:W21"/>
-    <mergeCell ref="X21:AB21"/>
-    <mergeCell ref="AC21:AG21"/>
-    <mergeCell ref="AH21:AL21"/>
-    <mergeCell ref="BL21:BP21"/>
-    <mergeCell ref="AM21:AQ21"/>
-    <mergeCell ref="AR21:AV21"/>
-    <mergeCell ref="AW21:BA21"/>
-    <mergeCell ref="BB21:BF21"/>
-    <mergeCell ref="BG21:BK21"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B4:B10"/>
+    <mergeCell ref="B11:B17"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
